--- a/Income And Expenses Forecast Demo.xlsx
+++ b/Income And Expenses Forecast Demo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="22160"/>
+    <workbookView windowHeight="22160" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Cover Page" sheetId="18" r:id="rId1"/>
@@ -256,7 +256,7 @@
     <t>Sosim</t>
   </si>
   <si>
-    <t>(SHIT COMPANY) Birdie Sim Card</t>
+    <t>Birdie Sim Card</t>
   </si>
   <si>
     <t>Total Expenses</t>
@@ -5458,7 +5458,7 @@
     <row r="51" ht="24.75" customHeight="1" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
-        <v>(SHIT COMPANY) Birdie Sim Card</v>
+        <v>Birdie Sim Card</v>
       </c>
       <c r="B51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65")))</f>
@@ -8822,7 +8822,7 @@
     <row r="51" ht="24.75" customHeight="1" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
-        <v>(SHIT COMPANY) Birdie Sim Card</v>
+        <v>Birdie Sim Card</v>
       </c>
       <c r="B51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65")))</f>
@@ -12186,7 +12186,7 @@
     <row r="51" ht="24.75" customHeight="1" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
-        <v>(SHIT COMPANY) Birdie Sim Card</v>
+        <v>Birdie Sim Card</v>
       </c>
       <c r="B51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65")))</f>
@@ -15544,7 +15544,7 @@
     <row r="51" ht="24.75" customHeight="1" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
-        <v>(SHIT COMPANY) Birdie Sim Card</v>
+        <v>Birdie Sim Card</v>
       </c>
       <c r="B51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65")))</f>
@@ -18909,7 +18909,7 @@
     <row r="51" ht="24.75" customHeight="1" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
-        <v>(SHIT COMPANY) Birdie Sim Card</v>
+        <v>Birdie Sim Card</v>
       </c>
       <c r="B51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65")))</f>
@@ -22267,7 +22267,7 @@
     <row r="51" ht="24.75" customHeight="1" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
-        <v>(SHIT COMPANY) Birdie Sim Card</v>
+        <v>Birdie Sim Card</v>
       </c>
       <c r="B51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65")))</f>
@@ -25635,7 +25635,7 @@
     <row r="51" ht="24.75" customHeight="1" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
-        <v>(SHIT COMPANY) Birdie Sim Card</v>
+        <v>Birdie Sim Card</v>
       </c>
       <c r="B51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65")))</f>
@@ -28980,7 +28980,7 @@
     <row r="51" ht="24.75" customHeight="1" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
-        <v>(SHIT COMPANY) Birdie Sim Card</v>
+        <v>Birdie Sim Card</v>
       </c>
       <c r="B51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65")))</f>
@@ -32331,7 +32331,7 @@
     <row r="51" ht="24.75" customHeight="1" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
-        <v>(SHIT COMPANY) Birdie Sim Card</v>
+        <v>Birdie Sim Card</v>
       </c>
       <c r="B51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65")))</f>
@@ -36709,7 +36709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" ht="34" spans="1:3">
+    <row r="65" spans="1:3">
       <c r="A65" s="51" t="s">
         <v>60</v>
       </c>
@@ -39206,7 +39206,7 @@
     <row r="51" ht="34" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
-        <v>(SHIT COMPANY) Birdie Sim Card</v>
+        <v>Birdie Sim Card</v>
       </c>
       <c r="B51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65")))</f>
@@ -42575,7 +42575,7 @@
     <row r="51" ht="45" customHeight="1" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
-        <v>(SHIT COMPANY) Birdie Sim Card</v>
+        <v>Birdie Sim Card</v>
       </c>
       <c r="B51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65")))</f>
@@ -45994,7 +45994,7 @@
     <row r="51" ht="24.75" customHeight="1" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
-        <v>(SHIT COMPANY) Birdie Sim Card</v>
+        <v>Birdie Sim Card</v>
       </c>
       <c r="B51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65")))</f>
@@ -49425,7 +49425,7 @@
     <row r="51" ht="24.75" customHeight="1" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
-        <v>(SHIT COMPANY) Birdie Sim Card</v>
+        <v>Birdie Sim Card</v>
       </c>
       <c r="B51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65")))</f>
@@ -52812,7 +52812,7 @@
     <row r="51" ht="24.75" customHeight="1" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
-        <v>(SHIT COMPANY) Birdie Sim Card</v>
+        <v>Birdie Sim Card</v>
       </c>
       <c r="B51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65")))</f>
@@ -56192,7 +56192,7 @@
     <row r="51" ht="24.75" customHeight="1" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
-        <v>(SHIT COMPANY) Birdie Sim Card</v>
+        <v>Birdie Sim Card</v>
       </c>
       <c r="B51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65")))</f>

--- a/Income And Expenses Forecast Demo.xlsx
+++ b/Income And Expenses Forecast Demo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="22160" activeTab="2"/>
+    <workbookView windowHeight="22160"/>
   </bookViews>
   <sheets>
     <sheet name="Cover Page" sheetId="18" r:id="rId1"/>
@@ -39203,7 +39203,7 @@
       <c r="H50" s="14"/>
       <c r="I50" s="48"/>
     </row>
-    <row r="51" ht="34" spans="1:9">
+    <row r="51" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
         <v>Birdie Sim Card</v>

--- a/Income And Expenses Forecast Demo.xlsx
+++ b/Income And Expenses Forecast Demo.xlsx
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="127">
   <si>
     <t>Income Forecast</t>
   </si>
@@ -256,7 +256,7 @@
     <t>Sosim</t>
   </si>
   <si>
-    <t>Birdie Sim Card</t>
+    <t>(SHIT COMPANY) Birdie Sim Card</t>
   </si>
   <si>
     <t>Total Expenses</t>
@@ -298,7 +298,7 @@
     <t>Entertainment</t>
   </si>
   <si>
-    <t>Sportify Music Paid For 7th of Each Month</t>
+    <t>Sportify Music Paid For 7th of Each Month. Switch to Apple Music on the 8th of July 2025.</t>
   </si>
   <si>
     <t>Hair Cutting</t>
@@ -428,7 +428,7 @@
 ~Shu Shi (Chuk Yuen Plaza) ~ $98</t>
   </si>
   <si>
-    <t>~ Payback $570 to Mom Plus Additional $300</t>
+    <t xml:space="preserve">~ Payback $570 to Mom </t>
   </si>
   <si>
     <t>~ Payback $676.03 to Mom (Amazon Books) Hold Till Receive Half Month Allowances</t>
@@ -440,6 +440,9 @@
   </si>
   <si>
     <t>~ Buy Cigarette Buds ~ $800</t>
+  </si>
+  <si>
+    <t>~ Apple Music one month</t>
   </si>
   <si>
     <t>Balance Brought Forward From July 2024</t>
@@ -508,7 +511,7 @@
     <numFmt numFmtId="179" formatCode="mmm\-yy"/>
     <numFmt numFmtId="180" formatCode="[$-409]d\-mmm\-yyyy;@"/>
   </numFmts>
-  <fonts count="47">
+  <fonts count="48">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -639,6 +642,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color rgb="FF27292E"/>
+      <name val="Helvetica Neue"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1088,7 +1098,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="48">
+  <borders count="49">
     <border>
       <left/>
       <right/>
@@ -1548,6 +1558,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -1662,31 +1687,28 @@
   </borders>
   <cellStyleXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="39" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="40" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1695,140 +1717,143 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="41" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="41" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="42" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="42" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="13" borderId="43" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="43" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="13" borderId="42" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="13" borderId="44" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="14" borderId="44" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="13" borderId="43" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="45" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="14" borderId="45" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="46" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="47" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="43" fillId="3" borderId="47">
+    <xf numFmtId="0" fontId="42" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="44" fillId="3" borderId="48">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyBorder="0" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="44" fillId="0" borderId="0" applyProtection="0">
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="0" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" applyProtection="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="45" fillId="9" borderId="0" applyProtection="0">
+    <xf numFmtId="49" fontId="46" fillId="9" borderId="0" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="46" fillId="5" borderId="0" applyBorder="0" applyProtection="0">
+    <xf numFmtId="49" fontId="47" fillId="5" borderId="0" applyBorder="0" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="244">
+  <cellXfs count="245">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2477,22 +2502,23 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="19" xfId="51" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="4" fontId="20" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="180" fontId="10" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2510,7 +2536,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2537,10 +2563,10 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2979,1744 +3005,1744 @@
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="17.6"/>
   <sheetData>
     <row r="1" spans="1:26">
-      <c r="A1" s="242" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="242"/>
-      <c r="C1" s="242"/>
-      <c r="D1" s="242"/>
-      <c r="E1" s="242"/>
-      <c r="F1" s="242"/>
-      <c r="G1" s="242"/>
-      <c r="H1" s="242"/>
-      <c r="I1" s="242"/>
-      <c r="J1" s="242"/>
-      <c r="K1" s="242"/>
-      <c r="L1" s="242"/>
-      <c r="M1" s="242"/>
-      <c r="N1" s="242"/>
-      <c r="O1" s="242"/>
-      <c r="P1" s="242"/>
-      <c r="Q1" s="242"/>
-      <c r="R1" s="242"/>
-      <c r="S1" s="242"/>
-      <c r="T1" s="242"/>
-      <c r="U1" s="242"/>
-      <c r="V1" s="242"/>
-      <c r="W1" s="242"/>
-      <c r="X1" s="242"/>
-      <c r="Y1" s="242"/>
-      <c r="Z1" s="242"/>
+      <c r="A1" s="243" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="243"/>
+      <c r="C1" s="243"/>
+      <c r="D1" s="243"/>
+      <c r="E1" s="243"/>
+      <c r="F1" s="243"/>
+      <c r="G1" s="243"/>
+      <c r="H1" s="243"/>
+      <c r="I1" s="243"/>
+      <c r="J1" s="243"/>
+      <c r="K1" s="243"/>
+      <c r="L1" s="243"/>
+      <c r="M1" s="243"/>
+      <c r="N1" s="243"/>
+      <c r="O1" s="243"/>
+      <c r="P1" s="243"/>
+      <c r="Q1" s="243"/>
+      <c r="R1" s="243"/>
+      <c r="S1" s="243"/>
+      <c r="T1" s="243"/>
+      <c r="U1" s="243"/>
+      <c r="V1" s="243"/>
+      <c r="W1" s="243"/>
+      <c r="X1" s="243"/>
+      <c r="Y1" s="243"/>
+      <c r="Z1" s="243"/>
     </row>
     <row r="2" spans="1:26">
-      <c r="A2" s="242"/>
-      <c r="B2" s="242"/>
-      <c r="C2" s="242"/>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="242"/>
-      <c r="H2" s="242"/>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
-      <c r="M2" s="242"/>
-      <c r="N2" s="242"/>
-      <c r="O2" s="242"/>
-      <c r="P2" s="242"/>
-      <c r="Q2" s="242"/>
-      <c r="R2" s="242"/>
-      <c r="S2" s="242"/>
-      <c r="T2" s="242"/>
-      <c r="U2" s="242"/>
-      <c r="V2" s="242"/>
-      <c r="W2" s="242"/>
-      <c r="X2" s="242"/>
-      <c r="Y2" s="242"/>
-      <c r="Z2" s="242"/>
+      <c r="A2" s="243"/>
+      <c r="B2" s="243"/>
+      <c r="C2" s="243"/>
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
+      <c r="G2" s="243"/>
+      <c r="H2" s="243"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
+      <c r="M2" s="243"/>
+      <c r="N2" s="243"/>
+      <c r="O2" s="243"/>
+      <c r="P2" s="243"/>
+      <c r="Q2" s="243"/>
+      <c r="R2" s="243"/>
+      <c r="S2" s="243"/>
+      <c r="T2" s="243"/>
+      <c r="U2" s="243"/>
+      <c r="V2" s="243"/>
+      <c r="W2" s="243"/>
+      <c r="X2" s="243"/>
+      <c r="Y2" s="243"/>
+      <c r="Z2" s="243"/>
     </row>
     <row r="3" spans="1:26">
-      <c r="A3" s="242"/>
-      <c r="B3" s="242"/>
-      <c r="C3" s="242"/>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
-      <c r="G3" s="242"/>
-      <c r="H3" s="242"/>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="242"/>
-      <c r="L3" s="242"/>
-      <c r="M3" s="242"/>
-      <c r="N3" s="242"/>
-      <c r="O3" s="242"/>
-      <c r="P3" s="242"/>
-      <c r="Q3" s="242"/>
-      <c r="R3" s="242"/>
-      <c r="S3" s="242"/>
-      <c r="T3" s="242"/>
-      <c r="U3" s="242"/>
-      <c r="V3" s="242"/>
-      <c r="W3" s="242"/>
-      <c r="X3" s="242"/>
-      <c r="Y3" s="242"/>
-      <c r="Z3" s="242"/>
+      <c r="A3" s="243"/>
+      <c r="B3" s="243"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
+      <c r="G3" s="243"/>
+      <c r="H3" s="243"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
+      <c r="L3" s="243"/>
+      <c r="M3" s="243"/>
+      <c r="N3" s="243"/>
+      <c r="O3" s="243"/>
+      <c r="P3" s="243"/>
+      <c r="Q3" s="243"/>
+      <c r="R3" s="243"/>
+      <c r="S3" s="243"/>
+      <c r="T3" s="243"/>
+      <c r="U3" s="243"/>
+      <c r="V3" s="243"/>
+      <c r="W3" s="243"/>
+      <c r="X3" s="243"/>
+      <c r="Y3" s="243"/>
+      <c r="Z3" s="243"/>
     </row>
     <row r="4" spans="1:26">
-      <c r="A4" s="242"/>
-      <c r="B4" s="242"/>
-      <c r="C4" s="242"/>
-      <c r="D4" s="242"/>
-      <c r="E4" s="242"/>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
-      <c r="H4" s="242"/>
-      <c r="I4" s="242"/>
-      <c r="J4" s="242"/>
-      <c r="K4" s="242"/>
-      <c r="L4" s="242"/>
-      <c r="M4" s="242"/>
-      <c r="N4" s="242"/>
-      <c r="O4" s="242"/>
-      <c r="P4" s="242"/>
-      <c r="Q4" s="242"/>
-      <c r="R4" s="242"/>
-      <c r="S4" s="242"/>
-      <c r="T4" s="242"/>
-      <c r="U4" s="242"/>
-      <c r="V4" s="242"/>
-      <c r="W4" s="242"/>
-      <c r="X4" s="242"/>
-      <c r="Y4" s="242"/>
-      <c r="Z4" s="242"/>
+      <c r="A4" s="243"/>
+      <c r="B4" s="243"/>
+      <c r="C4" s="243"/>
+      <c r="D4" s="243"/>
+      <c r="E4" s="243"/>
+      <c r="F4" s="243"/>
+      <c r="G4" s="243"/>
+      <c r="H4" s="243"/>
+      <c r="I4" s="243"/>
+      <c r="J4" s="243"/>
+      <c r="K4" s="243"/>
+      <c r="L4" s="243"/>
+      <c r="M4" s="243"/>
+      <c r="N4" s="243"/>
+      <c r="O4" s="243"/>
+      <c r="P4" s="243"/>
+      <c r="Q4" s="243"/>
+      <c r="R4" s="243"/>
+      <c r="S4" s="243"/>
+      <c r="T4" s="243"/>
+      <c r="U4" s="243"/>
+      <c r="V4" s="243"/>
+      <c r="W4" s="243"/>
+      <c r="X4" s="243"/>
+      <c r="Y4" s="243"/>
+      <c r="Z4" s="243"/>
     </row>
     <row r="5" spans="1:26">
-      <c r="A5" s="242"/>
-      <c r="B5" s="242"/>
-      <c r="C5" s="242"/>
-      <c r="D5" s="242"/>
-      <c r="E5" s="242"/>
-      <c r="F5" s="242"/>
-      <c r="G5" s="242"/>
-      <c r="H5" s="242"/>
-      <c r="I5" s="242"/>
-      <c r="J5" s="242"/>
-      <c r="K5" s="242"/>
-      <c r="L5" s="242"/>
-      <c r="M5" s="242"/>
-      <c r="N5" s="242"/>
-      <c r="O5" s="242"/>
-      <c r="P5" s="242"/>
-      <c r="Q5" s="242"/>
-      <c r="R5" s="242"/>
-      <c r="S5" s="242"/>
-      <c r="T5" s="242"/>
-      <c r="U5" s="242"/>
-      <c r="V5" s="242"/>
-      <c r="W5" s="242"/>
-      <c r="X5" s="242"/>
-      <c r="Y5" s="242"/>
-      <c r="Z5" s="242"/>
+      <c r="A5" s="243"/>
+      <c r="B5" s="243"/>
+      <c r="C5" s="243"/>
+      <c r="D5" s="243"/>
+      <c r="E5" s="243"/>
+      <c r="F5" s="243"/>
+      <c r="G5" s="243"/>
+      <c r="H5" s="243"/>
+      <c r="I5" s="243"/>
+      <c r="J5" s="243"/>
+      <c r="K5" s="243"/>
+      <c r="L5" s="243"/>
+      <c r="M5" s="243"/>
+      <c r="N5" s="243"/>
+      <c r="O5" s="243"/>
+      <c r="P5" s="243"/>
+      <c r="Q5" s="243"/>
+      <c r="R5" s="243"/>
+      <c r="S5" s="243"/>
+      <c r="T5" s="243"/>
+      <c r="U5" s="243"/>
+      <c r="V5" s="243"/>
+      <c r="W5" s="243"/>
+      <c r="X5" s="243"/>
+      <c r="Y5" s="243"/>
+      <c r="Z5" s="243"/>
     </row>
     <row r="6" spans="1:26">
-      <c r="A6" s="242"/>
-      <c r="B6" s="242"/>
-      <c r="C6" s="242"/>
-      <c r="D6" s="242"/>
-      <c r="E6" s="242"/>
-      <c r="F6" s="242"/>
-      <c r="G6" s="242"/>
-      <c r="H6" s="242"/>
-      <c r="I6" s="242"/>
-      <c r="J6" s="242"/>
-      <c r="K6" s="242"/>
-      <c r="L6" s="242"/>
-      <c r="M6" s="242"/>
-      <c r="N6" s="242"/>
-      <c r="O6" s="242"/>
-      <c r="P6" s="242"/>
-      <c r="Q6" s="242"/>
-      <c r="R6" s="242"/>
-      <c r="S6" s="242"/>
-      <c r="T6" s="242"/>
-      <c r="U6" s="242"/>
-      <c r="V6" s="242"/>
-      <c r="W6" s="242"/>
-      <c r="X6" s="242"/>
-      <c r="Y6" s="242"/>
-      <c r="Z6" s="242"/>
+      <c r="A6" s="243"/>
+      <c r="B6" s="243"/>
+      <c r="C6" s="243"/>
+      <c r="D6" s="243"/>
+      <c r="E6" s="243"/>
+      <c r="F6" s="243"/>
+      <c r="G6" s="243"/>
+      <c r="H6" s="243"/>
+      <c r="I6" s="243"/>
+      <c r="J6" s="243"/>
+      <c r="K6" s="243"/>
+      <c r="L6" s="243"/>
+      <c r="M6" s="243"/>
+      <c r="N6" s="243"/>
+      <c r="O6" s="243"/>
+      <c r="P6" s="243"/>
+      <c r="Q6" s="243"/>
+      <c r="R6" s="243"/>
+      <c r="S6" s="243"/>
+      <c r="T6" s="243"/>
+      <c r="U6" s="243"/>
+      <c r="V6" s="243"/>
+      <c r="W6" s="243"/>
+      <c r="X6" s="243"/>
+      <c r="Y6" s="243"/>
+      <c r="Z6" s="243"/>
     </row>
     <row r="7" spans="1:26">
-      <c r="A7" s="242"/>
-      <c r="B7" s="242"/>
-      <c r="C7" s="242"/>
-      <c r="D7" s="242"/>
-      <c r="E7" s="242"/>
-      <c r="F7" s="242"/>
-      <c r="G7" s="242"/>
-      <c r="H7" s="242"/>
-      <c r="I7" s="242"/>
-      <c r="J7" s="242"/>
-      <c r="K7" s="242"/>
-      <c r="L7" s="242"/>
-      <c r="M7" s="242"/>
-      <c r="N7" s="242"/>
-      <c r="O7" s="242"/>
-      <c r="P7" s="242"/>
-      <c r="Q7" s="242"/>
-      <c r="R7" s="242"/>
-      <c r="S7" s="242"/>
-      <c r="T7" s="242"/>
-      <c r="U7" s="242"/>
-      <c r="V7" s="242"/>
-      <c r="W7" s="242"/>
-      <c r="X7" s="242"/>
-      <c r="Y7" s="242"/>
-      <c r="Z7" s="242"/>
+      <c r="A7" s="243"/>
+      <c r="B7" s="243"/>
+      <c r="C7" s="243"/>
+      <c r="D7" s="243"/>
+      <c r="E7" s="243"/>
+      <c r="F7" s="243"/>
+      <c r="G7" s="243"/>
+      <c r="H7" s="243"/>
+      <c r="I7" s="243"/>
+      <c r="J7" s="243"/>
+      <c r="K7" s="243"/>
+      <c r="L7" s="243"/>
+      <c r="M7" s="243"/>
+      <c r="N7" s="243"/>
+      <c r="O7" s="243"/>
+      <c r="P7" s="243"/>
+      <c r="Q7" s="243"/>
+      <c r="R7" s="243"/>
+      <c r="S7" s="243"/>
+      <c r="T7" s="243"/>
+      <c r="U7" s="243"/>
+      <c r="V7" s="243"/>
+      <c r="W7" s="243"/>
+      <c r="X7" s="243"/>
+      <c r="Y7" s="243"/>
+      <c r="Z7" s="243"/>
     </row>
     <row r="8" spans="1:26">
-      <c r="A8" s="242"/>
-      <c r="B8" s="242"/>
-      <c r="C8" s="242"/>
-      <c r="D8" s="242"/>
-      <c r="E8" s="242"/>
-      <c r="F8" s="242"/>
-      <c r="G8" s="242"/>
-      <c r="H8" s="242"/>
-      <c r="I8" s="242"/>
-      <c r="J8" s="242"/>
-      <c r="K8" s="242"/>
-      <c r="L8" s="242"/>
-      <c r="M8" s="242"/>
-      <c r="N8" s="242"/>
-      <c r="O8" s="242"/>
-      <c r="P8" s="242"/>
-      <c r="Q8" s="242"/>
-      <c r="R8" s="242"/>
-      <c r="S8" s="242"/>
-      <c r="T8" s="242"/>
-      <c r="U8" s="242"/>
-      <c r="V8" s="242"/>
-      <c r="W8" s="242"/>
-      <c r="X8" s="242"/>
-      <c r="Y8" s="242"/>
-      <c r="Z8" s="242"/>
+      <c r="A8" s="243"/>
+      <c r="B8" s="243"/>
+      <c r="C8" s="243"/>
+      <c r="D8" s="243"/>
+      <c r="E8" s="243"/>
+      <c r="F8" s="243"/>
+      <c r="G8" s="243"/>
+      <c r="H8" s="243"/>
+      <c r="I8" s="243"/>
+      <c r="J8" s="243"/>
+      <c r="K8" s="243"/>
+      <c r="L8" s="243"/>
+      <c r="M8" s="243"/>
+      <c r="N8" s="243"/>
+      <c r="O8" s="243"/>
+      <c r="P8" s="243"/>
+      <c r="Q8" s="243"/>
+      <c r="R8" s="243"/>
+      <c r="S8" s="243"/>
+      <c r="T8" s="243"/>
+      <c r="U8" s="243"/>
+      <c r="V8" s="243"/>
+      <c r="W8" s="243"/>
+      <c r="X8" s="243"/>
+      <c r="Y8" s="243"/>
+      <c r="Z8" s="243"/>
     </row>
     <row r="9" spans="1:26">
-      <c r="A9" s="242"/>
-      <c r="B9" s="242"/>
-      <c r="C9" s="242"/>
-      <c r="D9" s="242"/>
-      <c r="E9" s="242"/>
-      <c r="F9" s="242"/>
-      <c r="G9" s="242"/>
-      <c r="H9" s="242"/>
-      <c r="I9" s="242"/>
-      <c r="J9" s="242"/>
-      <c r="K9" s="242"/>
-      <c r="L9" s="242"/>
-      <c r="M9" s="242"/>
-      <c r="N9" s="242"/>
-      <c r="O9" s="242"/>
-      <c r="P9" s="242"/>
-      <c r="Q9" s="242"/>
-      <c r="R9" s="242"/>
-      <c r="S9" s="242"/>
-      <c r="T9" s="242"/>
-      <c r="U9" s="242"/>
-      <c r="V9" s="242"/>
-      <c r="W9" s="242"/>
-      <c r="X9" s="242"/>
-      <c r="Y9" s="242"/>
-      <c r="Z9" s="242"/>
+      <c r="A9" s="243"/>
+      <c r="B9" s="243"/>
+      <c r="C9" s="243"/>
+      <c r="D9" s="243"/>
+      <c r="E9" s="243"/>
+      <c r="F9" s="243"/>
+      <c r="G9" s="243"/>
+      <c r="H9" s="243"/>
+      <c r="I9" s="243"/>
+      <c r="J9" s="243"/>
+      <c r="K9" s="243"/>
+      <c r="L9" s="243"/>
+      <c r="M9" s="243"/>
+      <c r="N9" s="243"/>
+      <c r="O9" s="243"/>
+      <c r="P9" s="243"/>
+      <c r="Q9" s="243"/>
+      <c r="R9" s="243"/>
+      <c r="S9" s="243"/>
+      <c r="T9" s="243"/>
+      <c r="U9" s="243"/>
+      <c r="V9" s="243"/>
+      <c r="W9" s="243"/>
+      <c r="X9" s="243"/>
+      <c r="Y9" s="243"/>
+      <c r="Z9" s="243"/>
     </row>
     <row r="10" spans="1:26">
-      <c r="A10" s="242"/>
-      <c r="B10" s="242"/>
-      <c r="C10" s="242"/>
-      <c r="D10" s="242"/>
-      <c r="E10" s="242"/>
-      <c r="F10" s="242"/>
-      <c r="G10" s="242"/>
-      <c r="H10" s="242"/>
-      <c r="I10" s="242"/>
-      <c r="J10" s="242"/>
-      <c r="K10" s="242"/>
-      <c r="L10" s="242"/>
-      <c r="M10" s="242"/>
-      <c r="N10" s="242"/>
-      <c r="O10" s="242"/>
-      <c r="P10" s="242"/>
-      <c r="Q10" s="242"/>
-      <c r="R10" s="242"/>
-      <c r="S10" s="242"/>
-      <c r="T10" s="242"/>
-      <c r="U10" s="242"/>
-      <c r="V10" s="242"/>
-      <c r="W10" s="242"/>
-      <c r="X10" s="242"/>
-      <c r="Y10" s="242"/>
-      <c r="Z10" s="242"/>
+      <c r="A10" s="243"/>
+      <c r="B10" s="243"/>
+      <c r="C10" s="243"/>
+      <c r="D10" s="243"/>
+      <c r="E10" s="243"/>
+      <c r="F10" s="243"/>
+      <c r="G10" s="243"/>
+      <c r="H10" s="243"/>
+      <c r="I10" s="243"/>
+      <c r="J10" s="243"/>
+      <c r="K10" s="243"/>
+      <c r="L10" s="243"/>
+      <c r="M10" s="243"/>
+      <c r="N10" s="243"/>
+      <c r="O10" s="243"/>
+      <c r="P10" s="243"/>
+      <c r="Q10" s="243"/>
+      <c r="R10" s="243"/>
+      <c r="S10" s="243"/>
+      <c r="T10" s="243"/>
+      <c r="U10" s="243"/>
+      <c r="V10" s="243"/>
+      <c r="W10" s="243"/>
+      <c r="X10" s="243"/>
+      <c r="Y10" s="243"/>
+      <c r="Z10" s="243"/>
     </row>
     <row r="11" spans="1:26">
-      <c r="A11" s="242"/>
-      <c r="B11" s="242"/>
-      <c r="C11" s="242"/>
-      <c r="D11" s="242"/>
-      <c r="E11" s="242"/>
-      <c r="F11" s="242"/>
-      <c r="G11" s="242"/>
-      <c r="H11" s="242"/>
-      <c r="I11" s="242"/>
-      <c r="J11" s="242"/>
-      <c r="K11" s="242"/>
-      <c r="L11" s="242"/>
-      <c r="M11" s="242"/>
-      <c r="N11" s="242"/>
-      <c r="O11" s="242"/>
-      <c r="P11" s="242"/>
-      <c r="Q11" s="242"/>
-      <c r="R11" s="242"/>
-      <c r="S11" s="242"/>
-      <c r="T11" s="242"/>
-      <c r="U11" s="242"/>
-      <c r="V11" s="242"/>
-      <c r="W11" s="242"/>
-      <c r="X11" s="242"/>
-      <c r="Y11" s="242"/>
-      <c r="Z11" s="242"/>
+      <c r="A11" s="243"/>
+      <c r="B11" s="243"/>
+      <c r="C11" s="243"/>
+      <c r="D11" s="243"/>
+      <c r="E11" s="243"/>
+      <c r="F11" s="243"/>
+      <c r="G11" s="243"/>
+      <c r="H11" s="243"/>
+      <c r="I11" s="243"/>
+      <c r="J11" s="243"/>
+      <c r="K11" s="243"/>
+      <c r="L11" s="243"/>
+      <c r="M11" s="243"/>
+      <c r="N11" s="243"/>
+      <c r="O11" s="243"/>
+      <c r="P11" s="243"/>
+      <c r="Q11" s="243"/>
+      <c r="R11" s="243"/>
+      <c r="S11" s="243"/>
+      <c r="T11" s="243"/>
+      <c r="U11" s="243"/>
+      <c r="V11" s="243"/>
+      <c r="W11" s="243"/>
+      <c r="X11" s="243"/>
+      <c r="Y11" s="243"/>
+      <c r="Z11" s="243"/>
     </row>
     <row r="12" spans="1:26">
-      <c r="A12" s="242"/>
-      <c r="B12" s="242"/>
-      <c r="C12" s="242"/>
-      <c r="D12" s="242"/>
-      <c r="E12" s="242"/>
-      <c r="F12" s="242"/>
-      <c r="G12" s="242"/>
-      <c r="H12" s="242"/>
-      <c r="I12" s="242"/>
-      <c r="J12" s="242"/>
-      <c r="K12" s="242"/>
-      <c r="L12" s="242"/>
-      <c r="M12" s="242"/>
-      <c r="N12" s="242"/>
-      <c r="O12" s="242"/>
-      <c r="P12" s="242"/>
-      <c r="Q12" s="242"/>
-      <c r="R12" s="242"/>
-      <c r="S12" s="242"/>
-      <c r="T12" s="242"/>
-      <c r="U12" s="242"/>
-      <c r="V12" s="242"/>
-      <c r="W12" s="242"/>
-      <c r="X12" s="242"/>
-      <c r="Y12" s="242"/>
-      <c r="Z12" s="242"/>
+      <c r="A12" s="243"/>
+      <c r="B12" s="243"/>
+      <c r="C12" s="243"/>
+      <c r="D12" s="243"/>
+      <c r="E12" s="243"/>
+      <c r="F12" s="243"/>
+      <c r="G12" s="243"/>
+      <c r="H12" s="243"/>
+      <c r="I12" s="243"/>
+      <c r="J12" s="243"/>
+      <c r="K12" s="243"/>
+      <c r="L12" s="243"/>
+      <c r="M12" s="243"/>
+      <c r="N12" s="243"/>
+      <c r="O12" s="243"/>
+      <c r="P12" s="243"/>
+      <c r="Q12" s="243"/>
+      <c r="R12" s="243"/>
+      <c r="S12" s="243"/>
+      <c r="T12" s="243"/>
+      <c r="U12" s="243"/>
+      <c r="V12" s="243"/>
+      <c r="W12" s="243"/>
+      <c r="X12" s="243"/>
+      <c r="Y12" s="243"/>
+      <c r="Z12" s="243"/>
     </row>
     <row r="13" spans="1:26">
-      <c r="A13" s="242"/>
-      <c r="B13" s="242"/>
-      <c r="C13" s="242"/>
-      <c r="D13" s="242"/>
-      <c r="E13" s="242"/>
-      <c r="F13" s="242"/>
-      <c r="G13" s="242"/>
-      <c r="H13" s="242"/>
-      <c r="I13" s="242"/>
-      <c r="J13" s="242"/>
-      <c r="K13" s="242"/>
-      <c r="L13" s="242"/>
-      <c r="M13" s="242"/>
-      <c r="N13" s="242"/>
-      <c r="O13" s="242"/>
-      <c r="P13" s="242"/>
-      <c r="Q13" s="242"/>
-      <c r="R13" s="242"/>
-      <c r="S13" s="242"/>
-      <c r="T13" s="242"/>
-      <c r="U13" s="242"/>
-      <c r="V13" s="242"/>
-      <c r="W13" s="242"/>
-      <c r="X13" s="242"/>
-      <c r="Y13" s="242"/>
-      <c r="Z13" s="242"/>
+      <c r="A13" s="243"/>
+      <c r="B13" s="243"/>
+      <c r="C13" s="243"/>
+      <c r="D13" s="243"/>
+      <c r="E13" s="243"/>
+      <c r="F13" s="243"/>
+      <c r="G13" s="243"/>
+      <c r="H13" s="243"/>
+      <c r="I13" s="243"/>
+      <c r="J13" s="243"/>
+      <c r="K13" s="243"/>
+      <c r="L13" s="243"/>
+      <c r="M13" s="243"/>
+      <c r="N13" s="243"/>
+      <c r="O13" s="243"/>
+      <c r="P13" s="243"/>
+      <c r="Q13" s="243"/>
+      <c r="R13" s="243"/>
+      <c r="S13" s="243"/>
+      <c r="T13" s="243"/>
+      <c r="U13" s="243"/>
+      <c r="V13" s="243"/>
+      <c r="W13" s="243"/>
+      <c r="X13" s="243"/>
+      <c r="Y13" s="243"/>
+      <c r="Z13" s="243"/>
     </row>
     <row r="14" spans="1:26">
-      <c r="A14" s="242"/>
-      <c r="B14" s="242"/>
-      <c r="C14" s="242"/>
-      <c r="D14" s="242"/>
-      <c r="E14" s="242"/>
-      <c r="F14" s="242"/>
-      <c r="G14" s="242"/>
-      <c r="H14" s="242"/>
-      <c r="I14" s="242"/>
-      <c r="J14" s="242"/>
-      <c r="K14" s="242"/>
-      <c r="L14" s="242"/>
-      <c r="M14" s="242"/>
-      <c r="N14" s="242"/>
-      <c r="O14" s="242"/>
-      <c r="P14" s="242"/>
-      <c r="Q14" s="242"/>
-      <c r="R14" s="242"/>
-      <c r="S14" s="242"/>
-      <c r="T14" s="242"/>
-      <c r="U14" s="242"/>
-      <c r="V14" s="242"/>
-      <c r="W14" s="242"/>
-      <c r="X14" s="242"/>
-      <c r="Y14" s="242"/>
-      <c r="Z14" s="242"/>
+      <c r="A14" s="243"/>
+      <c r="B14" s="243"/>
+      <c r="C14" s="243"/>
+      <c r="D14" s="243"/>
+      <c r="E14" s="243"/>
+      <c r="F14" s="243"/>
+      <c r="G14" s="243"/>
+      <c r="H14" s="243"/>
+      <c r="I14" s="243"/>
+      <c r="J14" s="243"/>
+      <c r="K14" s="243"/>
+      <c r="L14" s="243"/>
+      <c r="M14" s="243"/>
+      <c r="N14" s="243"/>
+      <c r="O14" s="243"/>
+      <c r="P14" s="243"/>
+      <c r="Q14" s="243"/>
+      <c r="R14" s="243"/>
+      <c r="S14" s="243"/>
+      <c r="T14" s="243"/>
+      <c r="U14" s="243"/>
+      <c r="V14" s="243"/>
+      <c r="W14" s="243"/>
+      <c r="X14" s="243"/>
+      <c r="Y14" s="243"/>
+      <c r="Z14" s="243"/>
     </row>
     <row r="15" spans="1:26">
-      <c r="A15" s="242"/>
-      <c r="B15" s="242"/>
-      <c r="C15" s="242"/>
-      <c r="D15" s="242"/>
-      <c r="E15" s="242"/>
-      <c r="F15" s="242"/>
-      <c r="G15" s="242"/>
-      <c r="H15" s="242"/>
-      <c r="I15" s="242"/>
-      <c r="J15" s="242"/>
-      <c r="K15" s="242"/>
-      <c r="L15" s="242"/>
-      <c r="M15" s="242"/>
-      <c r="N15" s="242"/>
-      <c r="O15" s="242"/>
-      <c r="P15" s="242"/>
-      <c r="Q15" s="242"/>
-      <c r="R15" s="242"/>
-      <c r="S15" s="242"/>
-      <c r="T15" s="242"/>
-      <c r="U15" s="242"/>
-      <c r="V15" s="242"/>
-      <c r="W15" s="242"/>
-      <c r="X15" s="242"/>
-      <c r="Y15" s="242"/>
-      <c r="Z15" s="242"/>
+      <c r="A15" s="243"/>
+      <c r="B15" s="243"/>
+      <c r="C15" s="243"/>
+      <c r="D15" s="243"/>
+      <c r="E15" s="243"/>
+      <c r="F15" s="243"/>
+      <c r="G15" s="243"/>
+      <c r="H15" s="243"/>
+      <c r="I15" s="243"/>
+      <c r="J15" s="243"/>
+      <c r="K15" s="243"/>
+      <c r="L15" s="243"/>
+      <c r="M15" s="243"/>
+      <c r="N15" s="243"/>
+      <c r="O15" s="243"/>
+      <c r="P15" s="243"/>
+      <c r="Q15" s="243"/>
+      <c r="R15" s="243"/>
+      <c r="S15" s="243"/>
+      <c r="T15" s="243"/>
+      <c r="U15" s="243"/>
+      <c r="V15" s="243"/>
+      <c r="W15" s="243"/>
+      <c r="X15" s="243"/>
+      <c r="Y15" s="243"/>
+      <c r="Z15" s="243"/>
     </row>
     <row r="16" spans="1:26">
-      <c r="A16" s="242"/>
-      <c r="B16" s="242"/>
-      <c r="C16" s="242"/>
-      <c r="D16" s="242"/>
-      <c r="E16" s="242"/>
-      <c r="F16" s="242"/>
-      <c r="G16" s="242"/>
-      <c r="H16" s="242"/>
-      <c r="I16" s="242"/>
-      <c r="J16" s="242"/>
-      <c r="K16" s="242"/>
-      <c r="L16" s="242"/>
-      <c r="M16" s="242"/>
-      <c r="N16" s="242"/>
-      <c r="O16" s="242"/>
-      <c r="P16" s="242"/>
-      <c r="Q16" s="242"/>
-      <c r="R16" s="242"/>
-      <c r="S16" s="242"/>
-      <c r="T16" s="242"/>
-      <c r="U16" s="242"/>
-      <c r="V16" s="242"/>
-      <c r="W16" s="242"/>
-      <c r="X16" s="242"/>
-      <c r="Y16" s="242"/>
-      <c r="Z16" s="242"/>
+      <c r="A16" s="243"/>
+      <c r="B16" s="243"/>
+      <c r="C16" s="243"/>
+      <c r="D16" s="243"/>
+      <c r="E16" s="243"/>
+      <c r="F16" s="243"/>
+      <c r="G16" s="243"/>
+      <c r="H16" s="243"/>
+      <c r="I16" s="243"/>
+      <c r="J16" s="243"/>
+      <c r="K16" s="243"/>
+      <c r="L16" s="243"/>
+      <c r="M16" s="243"/>
+      <c r="N16" s="243"/>
+      <c r="O16" s="243"/>
+      <c r="P16" s="243"/>
+      <c r="Q16" s="243"/>
+      <c r="R16" s="243"/>
+      <c r="S16" s="243"/>
+      <c r="T16" s="243"/>
+      <c r="U16" s="243"/>
+      <c r="V16" s="243"/>
+      <c r="W16" s="243"/>
+      <c r="X16" s="243"/>
+      <c r="Y16" s="243"/>
+      <c r="Z16" s="243"/>
     </row>
     <row r="17" spans="1:26">
-      <c r="A17" s="242"/>
-      <c r="B17" s="242"/>
-      <c r="C17" s="242"/>
-      <c r="D17" s="242"/>
-      <c r="E17" s="242"/>
-      <c r="F17" s="242"/>
-      <c r="G17" s="242"/>
-      <c r="H17" s="242"/>
-      <c r="I17" s="242"/>
-      <c r="J17" s="242"/>
-      <c r="K17" s="242"/>
-      <c r="L17" s="242"/>
-      <c r="M17" s="242"/>
-      <c r="N17" s="242"/>
-      <c r="O17" s="242"/>
-      <c r="P17" s="242"/>
-      <c r="Q17" s="242"/>
-      <c r="R17" s="242"/>
-      <c r="S17" s="242"/>
-      <c r="T17" s="242"/>
-      <c r="U17" s="242"/>
-      <c r="V17" s="242"/>
-      <c r="W17" s="242"/>
-      <c r="X17" s="242"/>
-      <c r="Y17" s="242"/>
-      <c r="Z17" s="242"/>
+      <c r="A17" s="243"/>
+      <c r="B17" s="243"/>
+      <c r="C17" s="243"/>
+      <c r="D17" s="243"/>
+      <c r="E17" s="243"/>
+      <c r="F17" s="243"/>
+      <c r="G17" s="243"/>
+      <c r="H17" s="243"/>
+      <c r="I17" s="243"/>
+      <c r="J17" s="243"/>
+      <c r="K17" s="243"/>
+      <c r="L17" s="243"/>
+      <c r="M17" s="243"/>
+      <c r="N17" s="243"/>
+      <c r="O17" s="243"/>
+      <c r="P17" s="243"/>
+      <c r="Q17" s="243"/>
+      <c r="R17" s="243"/>
+      <c r="S17" s="243"/>
+      <c r="T17" s="243"/>
+      <c r="U17" s="243"/>
+      <c r="V17" s="243"/>
+      <c r="W17" s="243"/>
+      <c r="X17" s="243"/>
+      <c r="Y17" s="243"/>
+      <c r="Z17" s="243"/>
     </row>
     <row r="18" spans="1:26">
-      <c r="A18" s="242"/>
-      <c r="B18" s="242"/>
-      <c r="C18" s="242"/>
-      <c r="D18" s="242"/>
-      <c r="E18" s="242"/>
-      <c r="F18" s="242"/>
-      <c r="G18" s="242"/>
-      <c r="H18" s="242"/>
-      <c r="I18" s="242"/>
-      <c r="J18" s="242"/>
-      <c r="K18" s="242"/>
-      <c r="L18" s="242"/>
-      <c r="M18" s="242"/>
-      <c r="N18" s="242"/>
-      <c r="O18" s="242"/>
-      <c r="P18" s="242"/>
-      <c r="Q18" s="242"/>
-      <c r="R18" s="242"/>
-      <c r="S18" s="242"/>
-      <c r="T18" s="242"/>
-      <c r="U18" s="242"/>
-      <c r="V18" s="242"/>
-      <c r="W18" s="242"/>
-      <c r="X18" s="242"/>
-      <c r="Y18" s="242"/>
-      <c r="Z18" s="242"/>
+      <c r="A18" s="243"/>
+      <c r="B18" s="243"/>
+      <c r="C18" s="243"/>
+      <c r="D18" s="243"/>
+      <c r="E18" s="243"/>
+      <c r="F18" s="243"/>
+      <c r="G18" s="243"/>
+      <c r="H18" s="243"/>
+      <c r="I18" s="243"/>
+      <c r="J18" s="243"/>
+      <c r="K18" s="243"/>
+      <c r="L18" s="243"/>
+      <c r="M18" s="243"/>
+      <c r="N18" s="243"/>
+      <c r="O18" s="243"/>
+      <c r="P18" s="243"/>
+      <c r="Q18" s="243"/>
+      <c r="R18" s="243"/>
+      <c r="S18" s="243"/>
+      <c r="T18" s="243"/>
+      <c r="U18" s="243"/>
+      <c r="V18" s="243"/>
+      <c r="W18" s="243"/>
+      <c r="X18" s="243"/>
+      <c r="Y18" s="243"/>
+      <c r="Z18" s="243"/>
     </row>
     <row r="19" spans="1:26">
-      <c r="A19" s="242"/>
-      <c r="B19" s="242"/>
-      <c r="C19" s="242"/>
-      <c r="D19" s="242"/>
-      <c r="E19" s="242"/>
-      <c r="F19" s="242"/>
-      <c r="G19" s="242"/>
-      <c r="H19" s="242"/>
-      <c r="I19" s="242"/>
-      <c r="J19" s="242"/>
-      <c r="K19" s="242"/>
-      <c r="L19" s="242"/>
-      <c r="M19" s="242"/>
-      <c r="N19" s="242"/>
-      <c r="O19" s="242"/>
-      <c r="P19" s="242"/>
-      <c r="Q19" s="242"/>
-      <c r="R19" s="242"/>
-      <c r="S19" s="242"/>
-      <c r="T19" s="242"/>
-      <c r="U19" s="242"/>
-      <c r="V19" s="242"/>
-      <c r="W19" s="242"/>
-      <c r="X19" s="242"/>
-      <c r="Y19" s="242"/>
-      <c r="Z19" s="242"/>
+      <c r="A19" s="243"/>
+      <c r="B19" s="243"/>
+      <c r="C19" s="243"/>
+      <c r="D19" s="243"/>
+      <c r="E19" s="243"/>
+      <c r="F19" s="243"/>
+      <c r="G19" s="243"/>
+      <c r="H19" s="243"/>
+      <c r="I19" s="243"/>
+      <c r="J19" s="243"/>
+      <c r="K19" s="243"/>
+      <c r="L19" s="243"/>
+      <c r="M19" s="243"/>
+      <c r="N19" s="243"/>
+      <c r="O19" s="243"/>
+      <c r="P19" s="243"/>
+      <c r="Q19" s="243"/>
+      <c r="R19" s="243"/>
+      <c r="S19" s="243"/>
+      <c r="T19" s="243"/>
+      <c r="U19" s="243"/>
+      <c r="V19" s="243"/>
+      <c r="W19" s="243"/>
+      <c r="X19" s="243"/>
+      <c r="Y19" s="243"/>
+      <c r="Z19" s="243"/>
     </row>
     <row r="20" spans="1:26">
-      <c r="A20" s="242"/>
-      <c r="B20" s="242"/>
-      <c r="C20" s="242"/>
-      <c r="D20" s="242"/>
-      <c r="E20" s="242"/>
-      <c r="F20" s="242"/>
-      <c r="G20" s="242"/>
-      <c r="H20" s="242"/>
-      <c r="I20" s="242"/>
-      <c r="J20" s="242"/>
-      <c r="K20" s="242"/>
-      <c r="L20" s="242"/>
-      <c r="M20" s="242"/>
-      <c r="N20" s="242"/>
-      <c r="O20" s="242"/>
-      <c r="P20" s="242"/>
-      <c r="Q20" s="242"/>
-      <c r="R20" s="242"/>
-      <c r="S20" s="242"/>
-      <c r="T20" s="242"/>
-      <c r="U20" s="242"/>
-      <c r="V20" s="242"/>
-      <c r="W20" s="242"/>
-      <c r="X20" s="242"/>
-      <c r="Y20" s="242"/>
-      <c r="Z20" s="242"/>
+      <c r="A20" s="243"/>
+      <c r="B20" s="243"/>
+      <c r="C20" s="243"/>
+      <c r="D20" s="243"/>
+      <c r="E20" s="243"/>
+      <c r="F20" s="243"/>
+      <c r="G20" s="243"/>
+      <c r="H20" s="243"/>
+      <c r="I20" s="243"/>
+      <c r="J20" s="243"/>
+      <c r="K20" s="243"/>
+      <c r="L20" s="243"/>
+      <c r="M20" s="243"/>
+      <c r="N20" s="243"/>
+      <c r="O20" s="243"/>
+      <c r="P20" s="243"/>
+      <c r="Q20" s="243"/>
+      <c r="R20" s="243"/>
+      <c r="S20" s="243"/>
+      <c r="T20" s="243"/>
+      <c r="U20" s="243"/>
+      <c r="V20" s="243"/>
+      <c r="W20" s="243"/>
+      <c r="X20" s="243"/>
+      <c r="Y20" s="243"/>
+      <c r="Z20" s="243"/>
     </row>
     <row r="21" spans="1:26">
-      <c r="A21" s="242"/>
-      <c r="B21" s="242"/>
-      <c r="C21" s="242"/>
-      <c r="D21" s="242"/>
-      <c r="E21" s="242"/>
-      <c r="F21" s="242"/>
-      <c r="G21" s="242"/>
-      <c r="H21" s="242"/>
-      <c r="I21" s="242"/>
-      <c r="J21" s="242"/>
-      <c r="K21" s="242"/>
-      <c r="L21" s="242"/>
-      <c r="M21" s="242"/>
-      <c r="N21" s="242"/>
-      <c r="O21" s="242"/>
-      <c r="P21" s="242"/>
-      <c r="Q21" s="242"/>
-      <c r="R21" s="242"/>
-      <c r="S21" s="242"/>
-      <c r="T21" s="242"/>
-      <c r="U21" s="242"/>
-      <c r="V21" s="242"/>
-      <c r="W21" s="242"/>
-      <c r="X21" s="242"/>
-      <c r="Y21" s="242"/>
-      <c r="Z21" s="242"/>
+      <c r="A21" s="243"/>
+      <c r="B21" s="243"/>
+      <c r="C21" s="243"/>
+      <c r="D21" s="243"/>
+      <c r="E21" s="243"/>
+      <c r="F21" s="243"/>
+      <c r="G21" s="243"/>
+      <c r="H21" s="243"/>
+      <c r="I21" s="243"/>
+      <c r="J21" s="243"/>
+      <c r="K21" s="243"/>
+      <c r="L21" s="243"/>
+      <c r="M21" s="243"/>
+      <c r="N21" s="243"/>
+      <c r="O21" s="243"/>
+      <c r="P21" s="243"/>
+      <c r="Q21" s="243"/>
+      <c r="R21" s="243"/>
+      <c r="S21" s="243"/>
+      <c r="T21" s="243"/>
+      <c r="U21" s="243"/>
+      <c r="V21" s="243"/>
+      <c r="W21" s="243"/>
+      <c r="X21" s="243"/>
+      <c r="Y21" s="243"/>
+      <c r="Z21" s="243"/>
     </row>
     <row r="22" spans="1:26">
-      <c r="A22" s="242"/>
-      <c r="B22" s="242"/>
-      <c r="C22" s="242"/>
-      <c r="D22" s="242"/>
-      <c r="E22" s="242"/>
-      <c r="F22" s="242"/>
-      <c r="G22" s="242"/>
-      <c r="H22" s="242"/>
-      <c r="I22" s="242"/>
-      <c r="J22" s="242"/>
-      <c r="K22" s="242"/>
-      <c r="L22" s="242"/>
-      <c r="M22" s="242"/>
-      <c r="N22" s="242"/>
-      <c r="O22" s="242"/>
-      <c r="P22" s="242"/>
-      <c r="Q22" s="242"/>
-      <c r="R22" s="242"/>
-      <c r="S22" s="242"/>
-      <c r="T22" s="242"/>
-      <c r="U22" s="242"/>
-      <c r="V22" s="242"/>
-      <c r="W22" s="242"/>
-      <c r="X22" s="242"/>
-      <c r="Y22" s="242"/>
-      <c r="Z22" s="242"/>
+      <c r="A22" s="243"/>
+      <c r="B22" s="243"/>
+      <c r="C22" s="243"/>
+      <c r="D22" s="243"/>
+      <c r="E22" s="243"/>
+      <c r="F22" s="243"/>
+      <c r="G22" s="243"/>
+      <c r="H22" s="243"/>
+      <c r="I22" s="243"/>
+      <c r="J22" s="243"/>
+      <c r="K22" s="243"/>
+      <c r="L22" s="243"/>
+      <c r="M22" s="243"/>
+      <c r="N22" s="243"/>
+      <c r="O22" s="243"/>
+      <c r="P22" s="243"/>
+      <c r="Q22" s="243"/>
+      <c r="R22" s="243"/>
+      <c r="S22" s="243"/>
+      <c r="T22" s="243"/>
+      <c r="U22" s="243"/>
+      <c r="V22" s="243"/>
+      <c r="W22" s="243"/>
+      <c r="X22" s="243"/>
+      <c r="Y22" s="243"/>
+      <c r="Z22" s="243"/>
     </row>
     <row r="23" spans="1:26">
-      <c r="A23" s="242"/>
-      <c r="B23" s="242"/>
-      <c r="C23" s="242"/>
-      <c r="D23" s="242"/>
-      <c r="E23" s="242"/>
-      <c r="F23" s="242"/>
-      <c r="G23" s="242"/>
-      <c r="H23" s="242"/>
-      <c r="I23" s="242"/>
-      <c r="J23" s="242"/>
-      <c r="K23" s="242"/>
-      <c r="L23" s="242"/>
-      <c r="M23" s="242"/>
-      <c r="N23" s="242"/>
-      <c r="O23" s="242"/>
-      <c r="P23" s="242"/>
-      <c r="Q23" s="242"/>
-      <c r="R23" s="242"/>
-      <c r="S23" s="242"/>
-      <c r="T23" s="242"/>
-      <c r="U23" s="242"/>
-      <c r="V23" s="242"/>
-      <c r="W23" s="242"/>
-      <c r="X23" s="242"/>
-      <c r="Y23" s="242"/>
-      <c r="Z23" s="242"/>
+      <c r="A23" s="243"/>
+      <c r="B23" s="243"/>
+      <c r="C23" s="243"/>
+      <c r="D23" s="243"/>
+      <c r="E23" s="243"/>
+      <c r="F23" s="243"/>
+      <c r="G23" s="243"/>
+      <c r="H23" s="243"/>
+      <c r="I23" s="243"/>
+      <c r="J23" s="243"/>
+      <c r="K23" s="243"/>
+      <c r="L23" s="243"/>
+      <c r="M23" s="243"/>
+      <c r="N23" s="243"/>
+      <c r="O23" s="243"/>
+      <c r="P23" s="243"/>
+      <c r="Q23" s="243"/>
+      <c r="R23" s="243"/>
+      <c r="S23" s="243"/>
+      <c r="T23" s="243"/>
+      <c r="U23" s="243"/>
+      <c r="V23" s="243"/>
+      <c r="W23" s="243"/>
+      <c r="X23" s="243"/>
+      <c r="Y23" s="243"/>
+      <c r="Z23" s="243"/>
     </row>
     <row r="24" spans="1:26">
-      <c r="A24" s="242"/>
-      <c r="B24" s="242"/>
-      <c r="C24" s="242"/>
-      <c r="D24" s="242"/>
-      <c r="E24" s="242"/>
-      <c r="F24" s="242"/>
-      <c r="G24" s="242"/>
-      <c r="H24" s="242"/>
-      <c r="I24" s="242"/>
-      <c r="J24" s="242"/>
-      <c r="K24" s="242"/>
-      <c r="L24" s="242"/>
-      <c r="M24" s="242"/>
-      <c r="N24" s="242"/>
-      <c r="O24" s="242"/>
-      <c r="P24" s="242"/>
-      <c r="Q24" s="242"/>
-      <c r="R24" s="242"/>
-      <c r="S24" s="242"/>
-      <c r="T24" s="242"/>
-      <c r="U24" s="242"/>
-      <c r="V24" s="242"/>
-      <c r="W24" s="242"/>
-      <c r="X24" s="242"/>
-      <c r="Y24" s="242"/>
-      <c r="Z24" s="242"/>
+      <c r="A24" s="243"/>
+      <c r="B24" s="243"/>
+      <c r="C24" s="243"/>
+      <c r="D24" s="243"/>
+      <c r="E24" s="243"/>
+      <c r="F24" s="243"/>
+      <c r="G24" s="243"/>
+      <c r="H24" s="243"/>
+      <c r="I24" s="243"/>
+      <c r="J24" s="243"/>
+      <c r="K24" s="243"/>
+      <c r="L24" s="243"/>
+      <c r="M24" s="243"/>
+      <c r="N24" s="243"/>
+      <c r="O24" s="243"/>
+      <c r="P24" s="243"/>
+      <c r="Q24" s="243"/>
+      <c r="R24" s="243"/>
+      <c r="S24" s="243"/>
+      <c r="T24" s="243"/>
+      <c r="U24" s="243"/>
+      <c r="V24" s="243"/>
+      <c r="W24" s="243"/>
+      <c r="X24" s="243"/>
+      <c r="Y24" s="243"/>
+      <c r="Z24" s="243"/>
     </row>
     <row r="25" spans="1:26">
-      <c r="A25" s="242"/>
-      <c r="B25" s="242"/>
-      <c r="C25" s="242"/>
-      <c r="D25" s="242"/>
-      <c r="E25" s="242"/>
-      <c r="F25" s="242"/>
-      <c r="G25" s="242"/>
-      <c r="H25" s="242"/>
-      <c r="I25" s="242"/>
-      <c r="J25" s="242"/>
-      <c r="K25" s="242"/>
-      <c r="L25" s="242"/>
-      <c r="M25" s="242"/>
-      <c r="N25" s="242"/>
-      <c r="O25" s="242"/>
-      <c r="P25" s="242"/>
-      <c r="Q25" s="242"/>
-      <c r="R25" s="242"/>
-      <c r="S25" s="242"/>
-      <c r="T25" s="242"/>
-      <c r="U25" s="242"/>
-      <c r="V25" s="242"/>
-      <c r="W25" s="242"/>
-      <c r="X25" s="242"/>
-      <c r="Y25" s="242"/>
-      <c r="Z25" s="242"/>
+      <c r="A25" s="243"/>
+      <c r="B25" s="243"/>
+      <c r="C25" s="243"/>
+      <c r="D25" s="243"/>
+      <c r="E25" s="243"/>
+      <c r="F25" s="243"/>
+      <c r="G25" s="243"/>
+      <c r="H25" s="243"/>
+      <c r="I25" s="243"/>
+      <c r="J25" s="243"/>
+      <c r="K25" s="243"/>
+      <c r="L25" s="243"/>
+      <c r="M25" s="243"/>
+      <c r="N25" s="243"/>
+      <c r="O25" s="243"/>
+      <c r="P25" s="243"/>
+      <c r="Q25" s="243"/>
+      <c r="R25" s="243"/>
+      <c r="S25" s="243"/>
+      <c r="T25" s="243"/>
+      <c r="U25" s="243"/>
+      <c r="V25" s="243"/>
+      <c r="W25" s="243"/>
+      <c r="X25" s="243"/>
+      <c r="Y25" s="243"/>
+      <c r="Z25" s="243"/>
     </row>
     <row r="26" spans="1:26">
-      <c r="A26" s="242"/>
-      <c r="B26" s="242"/>
-      <c r="C26" s="242"/>
-      <c r="D26" s="242"/>
-      <c r="E26" s="242"/>
-      <c r="F26" s="242"/>
-      <c r="G26" s="242"/>
-      <c r="H26" s="242"/>
-      <c r="I26" s="242"/>
-      <c r="J26" s="242"/>
-      <c r="K26" s="242"/>
-      <c r="L26" s="242"/>
-      <c r="M26" s="242"/>
-      <c r="N26" s="242"/>
-      <c r="O26" s="242"/>
-      <c r="P26" s="242"/>
-      <c r="Q26" s="242"/>
-      <c r="R26" s="242"/>
-      <c r="S26" s="242"/>
-      <c r="T26" s="242"/>
-      <c r="U26" s="242"/>
-      <c r="V26" s="242"/>
-      <c r="W26" s="242"/>
-      <c r="X26" s="242"/>
-      <c r="Y26" s="242"/>
-      <c r="Z26" s="242"/>
+      <c r="A26" s="243"/>
+      <c r="B26" s="243"/>
+      <c r="C26" s="243"/>
+      <c r="D26" s="243"/>
+      <c r="E26" s="243"/>
+      <c r="F26" s="243"/>
+      <c r="G26" s="243"/>
+      <c r="H26" s="243"/>
+      <c r="I26" s="243"/>
+      <c r="J26" s="243"/>
+      <c r="K26" s="243"/>
+      <c r="L26" s="243"/>
+      <c r="M26" s="243"/>
+      <c r="N26" s="243"/>
+      <c r="O26" s="243"/>
+      <c r="P26" s="243"/>
+      <c r="Q26" s="243"/>
+      <c r="R26" s="243"/>
+      <c r="S26" s="243"/>
+      <c r="T26" s="243"/>
+      <c r="U26" s="243"/>
+      <c r="V26" s="243"/>
+      <c r="W26" s="243"/>
+      <c r="X26" s="243"/>
+      <c r="Y26" s="243"/>
+      <c r="Z26" s="243"/>
     </row>
     <row r="27" spans="1:26">
-      <c r="A27" s="242"/>
-      <c r="B27" s="242"/>
-      <c r="C27" s="242"/>
-      <c r="D27" s="242"/>
-      <c r="E27" s="242"/>
-      <c r="F27" s="242"/>
-      <c r="G27" s="242"/>
-      <c r="H27" s="242"/>
-      <c r="I27" s="242"/>
-      <c r="J27" s="242"/>
-      <c r="K27" s="242"/>
-      <c r="L27" s="242"/>
-      <c r="M27" s="242"/>
-      <c r="N27" s="242"/>
-      <c r="O27" s="242"/>
-      <c r="P27" s="242"/>
-      <c r="Q27" s="242"/>
-      <c r="R27" s="242"/>
-      <c r="S27" s="242"/>
-      <c r="T27" s="242"/>
-      <c r="U27" s="242"/>
-      <c r="V27" s="242"/>
-      <c r="W27" s="242"/>
-      <c r="X27" s="242"/>
-      <c r="Y27" s="242"/>
-      <c r="Z27" s="242"/>
+      <c r="A27" s="243"/>
+      <c r="B27" s="243"/>
+      <c r="C27" s="243"/>
+      <c r="D27" s="243"/>
+      <c r="E27" s="243"/>
+      <c r="F27" s="243"/>
+      <c r="G27" s="243"/>
+      <c r="H27" s="243"/>
+      <c r="I27" s="243"/>
+      <c r="J27" s="243"/>
+      <c r="K27" s="243"/>
+      <c r="L27" s="243"/>
+      <c r="M27" s="243"/>
+      <c r="N27" s="243"/>
+      <c r="O27" s="243"/>
+      <c r="P27" s="243"/>
+      <c r="Q27" s="243"/>
+      <c r="R27" s="243"/>
+      <c r="S27" s="243"/>
+      <c r="T27" s="243"/>
+      <c r="U27" s="243"/>
+      <c r="V27" s="243"/>
+      <c r="W27" s="243"/>
+      <c r="X27" s="243"/>
+      <c r="Y27" s="243"/>
+      <c r="Z27" s="243"/>
     </row>
     <row r="28" spans="1:26">
-      <c r="A28" s="242"/>
-      <c r="B28" s="242"/>
-      <c r="C28" s="242"/>
-      <c r="D28" s="242"/>
-      <c r="E28" s="242"/>
-      <c r="F28" s="242"/>
-      <c r="G28" s="242"/>
-      <c r="H28" s="242"/>
-      <c r="I28" s="242"/>
-      <c r="J28" s="242"/>
-      <c r="K28" s="242"/>
-      <c r="L28" s="242"/>
-      <c r="M28" s="242"/>
-      <c r="N28" s="242"/>
-      <c r="O28" s="242"/>
-      <c r="P28" s="242"/>
-      <c r="Q28" s="242"/>
-      <c r="R28" s="242"/>
-      <c r="S28" s="242"/>
-      <c r="T28" s="242"/>
-      <c r="U28" s="242"/>
-      <c r="V28" s="242"/>
-      <c r="W28" s="242"/>
-      <c r="X28" s="242"/>
-      <c r="Y28" s="242"/>
-      <c r="Z28" s="242"/>
+      <c r="A28" s="243"/>
+      <c r="B28" s="243"/>
+      <c r="C28" s="243"/>
+      <c r="D28" s="243"/>
+      <c r="E28" s="243"/>
+      <c r="F28" s="243"/>
+      <c r="G28" s="243"/>
+      <c r="H28" s="243"/>
+      <c r="I28" s="243"/>
+      <c r="J28" s="243"/>
+      <c r="K28" s="243"/>
+      <c r="L28" s="243"/>
+      <c r="M28" s="243"/>
+      <c r="N28" s="243"/>
+      <c r="O28" s="243"/>
+      <c r="P28" s="243"/>
+      <c r="Q28" s="243"/>
+      <c r="R28" s="243"/>
+      <c r="S28" s="243"/>
+      <c r="T28" s="243"/>
+      <c r="U28" s="243"/>
+      <c r="V28" s="243"/>
+      <c r="W28" s="243"/>
+      <c r="X28" s="243"/>
+      <c r="Y28" s="243"/>
+      <c r="Z28" s="243"/>
     </row>
     <row r="29" spans="1:26">
-      <c r="A29" s="242"/>
-      <c r="B29" s="242"/>
-      <c r="C29" s="242"/>
-      <c r="D29" s="242"/>
-      <c r="E29" s="242"/>
-      <c r="F29" s="242"/>
-      <c r="G29" s="242"/>
-      <c r="H29" s="242"/>
-      <c r="I29" s="242"/>
-      <c r="J29" s="242"/>
-      <c r="K29" s="242"/>
-      <c r="L29" s="242"/>
-      <c r="M29" s="242"/>
-      <c r="N29" s="242"/>
-      <c r="O29" s="242"/>
-      <c r="P29" s="242"/>
-      <c r="Q29" s="242"/>
-      <c r="R29" s="242"/>
-      <c r="S29" s="242"/>
-      <c r="T29" s="242"/>
-      <c r="U29" s="242"/>
-      <c r="V29" s="242"/>
-      <c r="W29" s="242"/>
-      <c r="X29" s="242"/>
-      <c r="Y29" s="242"/>
-      <c r="Z29" s="242"/>
+      <c r="A29" s="243"/>
+      <c r="B29" s="243"/>
+      <c r="C29" s="243"/>
+      <c r="D29" s="243"/>
+      <c r="E29" s="243"/>
+      <c r="F29" s="243"/>
+      <c r="G29" s="243"/>
+      <c r="H29" s="243"/>
+      <c r="I29" s="243"/>
+      <c r="J29" s="243"/>
+      <c r="K29" s="243"/>
+      <c r="L29" s="243"/>
+      <c r="M29" s="243"/>
+      <c r="N29" s="243"/>
+      <c r="O29" s="243"/>
+      <c r="P29" s="243"/>
+      <c r="Q29" s="243"/>
+      <c r="R29" s="243"/>
+      <c r="S29" s="243"/>
+      <c r="T29" s="243"/>
+      <c r="U29" s="243"/>
+      <c r="V29" s="243"/>
+      <c r="W29" s="243"/>
+      <c r="X29" s="243"/>
+      <c r="Y29" s="243"/>
+      <c r="Z29" s="243"/>
     </row>
     <row r="30" spans="1:26">
-      <c r="A30" s="242"/>
-      <c r="B30" s="242"/>
-      <c r="C30" s="242"/>
-      <c r="D30" s="242"/>
-      <c r="E30" s="242"/>
-      <c r="F30" s="242"/>
-      <c r="G30" s="242"/>
-      <c r="H30" s="242"/>
-      <c r="I30" s="242"/>
-      <c r="J30" s="242"/>
-      <c r="K30" s="242"/>
-      <c r="L30" s="242"/>
-      <c r="M30" s="242"/>
-      <c r="N30" s="242"/>
-      <c r="O30" s="242"/>
-      <c r="P30" s="242"/>
-      <c r="Q30" s="242"/>
-      <c r="R30" s="242"/>
-      <c r="S30" s="242"/>
-      <c r="T30" s="242"/>
-      <c r="U30" s="242"/>
-      <c r="V30" s="242"/>
-      <c r="W30" s="242"/>
-      <c r="X30" s="242"/>
-      <c r="Y30" s="242"/>
-      <c r="Z30" s="242"/>
+      <c r="A30" s="243"/>
+      <c r="B30" s="243"/>
+      <c r="C30" s="243"/>
+      <c r="D30" s="243"/>
+      <c r="E30" s="243"/>
+      <c r="F30" s="243"/>
+      <c r="G30" s="243"/>
+      <c r="H30" s="243"/>
+      <c r="I30" s="243"/>
+      <c r="J30" s="243"/>
+      <c r="K30" s="243"/>
+      <c r="L30" s="243"/>
+      <c r="M30" s="243"/>
+      <c r="N30" s="243"/>
+      <c r="O30" s="243"/>
+      <c r="P30" s="243"/>
+      <c r="Q30" s="243"/>
+      <c r="R30" s="243"/>
+      <c r="S30" s="243"/>
+      <c r="T30" s="243"/>
+      <c r="U30" s="243"/>
+      <c r="V30" s="243"/>
+      <c r="W30" s="243"/>
+      <c r="X30" s="243"/>
+      <c r="Y30" s="243"/>
+      <c r="Z30" s="243"/>
     </row>
     <row r="31" spans="1:26">
-      <c r="A31" s="242"/>
-      <c r="B31" s="242"/>
-      <c r="C31" s="242"/>
-      <c r="D31" s="242"/>
-      <c r="E31" s="242"/>
-      <c r="F31" s="242"/>
-      <c r="G31" s="242"/>
-      <c r="H31" s="242"/>
-      <c r="I31" s="242"/>
-      <c r="J31" s="242"/>
-      <c r="K31" s="242"/>
-      <c r="L31" s="242"/>
-      <c r="M31" s="242"/>
-      <c r="N31" s="242"/>
-      <c r="O31" s="242"/>
-      <c r="P31" s="242"/>
-      <c r="Q31" s="242"/>
-      <c r="R31" s="242"/>
-      <c r="S31" s="242"/>
-      <c r="T31" s="242"/>
-      <c r="U31" s="242"/>
-      <c r="V31" s="242"/>
-      <c r="W31" s="242"/>
-      <c r="X31" s="242"/>
-      <c r="Y31" s="242"/>
-      <c r="Z31" s="242"/>
+      <c r="A31" s="243"/>
+      <c r="B31" s="243"/>
+      <c r="C31" s="243"/>
+      <c r="D31" s="243"/>
+      <c r="E31" s="243"/>
+      <c r="F31" s="243"/>
+      <c r="G31" s="243"/>
+      <c r="H31" s="243"/>
+      <c r="I31" s="243"/>
+      <c r="J31" s="243"/>
+      <c r="K31" s="243"/>
+      <c r="L31" s="243"/>
+      <c r="M31" s="243"/>
+      <c r="N31" s="243"/>
+      <c r="O31" s="243"/>
+      <c r="P31" s="243"/>
+      <c r="Q31" s="243"/>
+      <c r="R31" s="243"/>
+      <c r="S31" s="243"/>
+      <c r="T31" s="243"/>
+      <c r="U31" s="243"/>
+      <c r="V31" s="243"/>
+      <c r="W31" s="243"/>
+      <c r="X31" s="243"/>
+      <c r="Y31" s="243"/>
+      <c r="Z31" s="243"/>
     </row>
     <row r="32" spans="1:26">
-      <c r="A32" s="243" t="s">
+      <c r="A32" s="244" t="s">
         <v>1</v>
       </c>
-      <c r="B32" s="243"/>
-      <c r="C32" s="243"/>
-      <c r="D32" s="243"/>
-      <c r="E32" s="243"/>
-      <c r="F32" s="243"/>
-      <c r="G32" s="243"/>
-      <c r="H32" s="243"/>
-      <c r="I32" s="243"/>
-      <c r="J32" s="243"/>
-      <c r="K32" s="243"/>
-      <c r="L32" s="243"/>
-      <c r="M32" s="243"/>
-      <c r="N32" s="243"/>
-      <c r="O32" s="243"/>
-      <c r="P32" s="243"/>
-      <c r="Q32" s="243"/>
-      <c r="R32" s="243"/>
-      <c r="S32" s="243"/>
-      <c r="T32" s="243"/>
-      <c r="U32" s="243"/>
-      <c r="V32" s="243"/>
-      <c r="W32" s="243"/>
-      <c r="X32" s="243"/>
-      <c r="Y32" s="243"/>
-      <c r="Z32" s="243"/>
+      <c r="B32" s="244"/>
+      <c r="C32" s="244"/>
+      <c r="D32" s="244"/>
+      <c r="E32" s="244"/>
+      <c r="F32" s="244"/>
+      <c r="G32" s="244"/>
+      <c r="H32" s="244"/>
+      <c r="I32" s="244"/>
+      <c r="J32" s="244"/>
+      <c r="K32" s="244"/>
+      <c r="L32" s="244"/>
+      <c r="M32" s="244"/>
+      <c r="N32" s="244"/>
+      <c r="O32" s="244"/>
+      <c r="P32" s="244"/>
+      <c r="Q32" s="244"/>
+      <c r="R32" s="244"/>
+      <c r="S32" s="244"/>
+      <c r="T32" s="244"/>
+      <c r="U32" s="244"/>
+      <c r="V32" s="244"/>
+      <c r="W32" s="244"/>
+      <c r="X32" s="244"/>
+      <c r="Y32" s="244"/>
+      <c r="Z32" s="244"/>
     </row>
     <row r="33" spans="1:26">
-      <c r="A33" s="243"/>
-      <c r="B33" s="243"/>
-      <c r="C33" s="243"/>
-      <c r="D33" s="243"/>
-      <c r="E33" s="243"/>
-      <c r="F33" s="243"/>
-      <c r="G33" s="243"/>
-      <c r="H33" s="243"/>
-      <c r="I33" s="243"/>
-      <c r="J33" s="243"/>
-      <c r="K33" s="243"/>
-      <c r="L33" s="243"/>
-      <c r="M33" s="243"/>
-      <c r="N33" s="243"/>
-      <c r="O33" s="243"/>
-      <c r="P33" s="243"/>
-      <c r="Q33" s="243"/>
-      <c r="R33" s="243"/>
-      <c r="S33" s="243"/>
-      <c r="T33" s="243"/>
-      <c r="U33" s="243"/>
-      <c r="V33" s="243"/>
-      <c r="W33" s="243"/>
-      <c r="X33" s="243"/>
-      <c r="Y33" s="243"/>
-      <c r="Z33" s="243"/>
+      <c r="A33" s="244"/>
+      <c r="B33" s="244"/>
+      <c r="C33" s="244"/>
+      <c r="D33" s="244"/>
+      <c r="E33" s="244"/>
+      <c r="F33" s="244"/>
+      <c r="G33" s="244"/>
+      <c r="H33" s="244"/>
+      <c r="I33" s="244"/>
+      <c r="J33" s="244"/>
+      <c r="K33" s="244"/>
+      <c r="L33" s="244"/>
+      <c r="M33" s="244"/>
+      <c r="N33" s="244"/>
+      <c r="O33" s="244"/>
+      <c r="P33" s="244"/>
+      <c r="Q33" s="244"/>
+      <c r="R33" s="244"/>
+      <c r="S33" s="244"/>
+      <c r="T33" s="244"/>
+      <c r="U33" s="244"/>
+      <c r="V33" s="244"/>
+      <c r="W33" s="244"/>
+      <c r="X33" s="244"/>
+      <c r="Y33" s="244"/>
+      <c r="Z33" s="244"/>
     </row>
     <row r="34" spans="1:26">
-      <c r="A34" s="243"/>
-      <c r="B34" s="243"/>
-      <c r="C34" s="243"/>
-      <c r="D34" s="243"/>
-      <c r="E34" s="243"/>
-      <c r="F34" s="243"/>
-      <c r="G34" s="243"/>
-      <c r="H34" s="243"/>
-      <c r="I34" s="243"/>
-      <c r="J34" s="243"/>
-      <c r="K34" s="243"/>
-      <c r="L34" s="243"/>
-      <c r="M34" s="243"/>
-      <c r="N34" s="243"/>
-      <c r="O34" s="243"/>
-      <c r="P34" s="243"/>
-      <c r="Q34" s="243"/>
-      <c r="R34" s="243"/>
-      <c r="S34" s="243"/>
-      <c r="T34" s="243"/>
-      <c r="U34" s="243"/>
-      <c r="V34" s="243"/>
-      <c r="W34" s="243"/>
-      <c r="X34" s="243"/>
-      <c r="Y34" s="243"/>
-      <c r="Z34" s="243"/>
+      <c r="A34" s="244"/>
+      <c r="B34" s="244"/>
+      <c r="C34" s="244"/>
+      <c r="D34" s="244"/>
+      <c r="E34" s="244"/>
+      <c r="F34" s="244"/>
+      <c r="G34" s="244"/>
+      <c r="H34" s="244"/>
+      <c r="I34" s="244"/>
+      <c r="J34" s="244"/>
+      <c r="K34" s="244"/>
+      <c r="L34" s="244"/>
+      <c r="M34" s="244"/>
+      <c r="N34" s="244"/>
+      <c r="O34" s="244"/>
+      <c r="P34" s="244"/>
+      <c r="Q34" s="244"/>
+      <c r="R34" s="244"/>
+      <c r="S34" s="244"/>
+      <c r="T34" s="244"/>
+      <c r="U34" s="244"/>
+      <c r="V34" s="244"/>
+      <c r="W34" s="244"/>
+      <c r="X34" s="244"/>
+      <c r="Y34" s="244"/>
+      <c r="Z34" s="244"/>
     </row>
     <row r="35" spans="1:26">
-      <c r="A35" s="243"/>
-      <c r="B35" s="243"/>
-      <c r="C35" s="243"/>
-      <c r="D35" s="243"/>
-      <c r="E35" s="243"/>
-      <c r="F35" s="243"/>
-      <c r="G35" s="243"/>
-      <c r="H35" s="243"/>
-      <c r="I35" s="243"/>
-      <c r="J35" s="243"/>
-      <c r="K35" s="243"/>
-      <c r="L35" s="243"/>
-      <c r="M35" s="243"/>
-      <c r="N35" s="243"/>
-      <c r="O35" s="243"/>
-      <c r="P35" s="243"/>
-      <c r="Q35" s="243"/>
-      <c r="R35" s="243"/>
-      <c r="S35" s="243"/>
-      <c r="T35" s="243"/>
-      <c r="U35" s="243"/>
-      <c r="V35" s="243"/>
-      <c r="W35" s="243"/>
-      <c r="X35" s="243"/>
-      <c r="Y35" s="243"/>
-      <c r="Z35" s="243"/>
+      <c r="A35" s="244"/>
+      <c r="B35" s="244"/>
+      <c r="C35" s="244"/>
+      <c r="D35" s="244"/>
+      <c r="E35" s="244"/>
+      <c r="F35" s="244"/>
+      <c r="G35" s="244"/>
+      <c r="H35" s="244"/>
+      <c r="I35" s="244"/>
+      <c r="J35" s="244"/>
+      <c r="K35" s="244"/>
+      <c r="L35" s="244"/>
+      <c r="M35" s="244"/>
+      <c r="N35" s="244"/>
+      <c r="O35" s="244"/>
+      <c r="P35" s="244"/>
+      <c r="Q35" s="244"/>
+      <c r="R35" s="244"/>
+      <c r="S35" s="244"/>
+      <c r="T35" s="244"/>
+      <c r="U35" s="244"/>
+      <c r="V35" s="244"/>
+      <c r="W35" s="244"/>
+      <c r="X35" s="244"/>
+      <c r="Y35" s="244"/>
+      <c r="Z35" s="244"/>
     </row>
     <row r="36" spans="1:26">
-      <c r="A36" s="243"/>
-      <c r="B36" s="243"/>
-      <c r="C36" s="243"/>
-      <c r="D36" s="243"/>
-      <c r="E36" s="243"/>
-      <c r="F36" s="243"/>
-      <c r="G36" s="243"/>
-      <c r="H36" s="243"/>
-      <c r="I36" s="243"/>
-      <c r="J36" s="243"/>
-      <c r="K36" s="243"/>
-      <c r="L36" s="243"/>
-      <c r="M36" s="243"/>
-      <c r="N36" s="243"/>
-      <c r="O36" s="243"/>
-      <c r="P36" s="243"/>
-      <c r="Q36" s="243"/>
-      <c r="R36" s="243"/>
-      <c r="S36" s="243"/>
-      <c r="T36" s="243"/>
-      <c r="U36" s="243"/>
-      <c r="V36" s="243"/>
-      <c r="W36" s="243"/>
-      <c r="X36" s="243"/>
-      <c r="Y36" s="243"/>
-      <c r="Z36" s="243"/>
+      <c r="A36" s="244"/>
+      <c r="B36" s="244"/>
+      <c r="C36" s="244"/>
+      <c r="D36" s="244"/>
+      <c r="E36" s="244"/>
+      <c r="F36" s="244"/>
+      <c r="G36" s="244"/>
+      <c r="H36" s="244"/>
+      <c r="I36" s="244"/>
+      <c r="J36" s="244"/>
+      <c r="K36" s="244"/>
+      <c r="L36" s="244"/>
+      <c r="M36" s="244"/>
+      <c r="N36" s="244"/>
+      <c r="O36" s="244"/>
+      <c r="P36" s="244"/>
+      <c r="Q36" s="244"/>
+      <c r="R36" s="244"/>
+      <c r="S36" s="244"/>
+      <c r="T36" s="244"/>
+      <c r="U36" s="244"/>
+      <c r="V36" s="244"/>
+      <c r="W36" s="244"/>
+      <c r="X36" s="244"/>
+      <c r="Y36" s="244"/>
+      <c r="Z36" s="244"/>
     </row>
     <row r="37" spans="1:26">
-      <c r="A37" s="243"/>
-      <c r="B37" s="243"/>
-      <c r="C37" s="243"/>
-      <c r="D37" s="243"/>
-      <c r="E37" s="243"/>
-      <c r="F37" s="243"/>
-      <c r="G37" s="243"/>
-      <c r="H37" s="243"/>
-      <c r="I37" s="243"/>
-      <c r="J37" s="243"/>
-      <c r="K37" s="243"/>
-      <c r="L37" s="243"/>
-      <c r="M37" s="243"/>
-      <c r="N37" s="243"/>
-      <c r="O37" s="243"/>
-      <c r="P37" s="243"/>
-      <c r="Q37" s="243"/>
-      <c r="R37" s="243"/>
-      <c r="S37" s="243"/>
-      <c r="T37" s="243"/>
-      <c r="U37" s="243"/>
-      <c r="V37" s="243"/>
-      <c r="W37" s="243"/>
-      <c r="X37" s="243"/>
-      <c r="Y37" s="243"/>
-      <c r="Z37" s="243"/>
+      <c r="A37" s="244"/>
+      <c r="B37" s="244"/>
+      <c r="C37" s="244"/>
+      <c r="D37" s="244"/>
+      <c r="E37" s="244"/>
+      <c r="F37" s="244"/>
+      <c r="G37" s="244"/>
+      <c r="H37" s="244"/>
+      <c r="I37" s="244"/>
+      <c r="J37" s="244"/>
+      <c r="K37" s="244"/>
+      <c r="L37" s="244"/>
+      <c r="M37" s="244"/>
+      <c r="N37" s="244"/>
+      <c r="O37" s="244"/>
+      <c r="P37" s="244"/>
+      <c r="Q37" s="244"/>
+      <c r="R37" s="244"/>
+      <c r="S37" s="244"/>
+      <c r="T37" s="244"/>
+      <c r="U37" s="244"/>
+      <c r="V37" s="244"/>
+      <c r="W37" s="244"/>
+      <c r="X37" s="244"/>
+      <c r="Y37" s="244"/>
+      <c r="Z37" s="244"/>
     </row>
     <row r="38" spans="1:26">
-      <c r="A38" s="243"/>
-      <c r="B38" s="243"/>
-      <c r="C38" s="243"/>
-      <c r="D38" s="243"/>
-      <c r="E38" s="243"/>
-      <c r="F38" s="243"/>
-      <c r="G38" s="243"/>
-      <c r="H38" s="243"/>
-      <c r="I38" s="243"/>
-      <c r="J38" s="243"/>
-      <c r="K38" s="243"/>
-      <c r="L38" s="243"/>
-      <c r="M38" s="243"/>
-      <c r="N38" s="243"/>
-      <c r="O38" s="243"/>
-      <c r="P38" s="243"/>
-      <c r="Q38" s="243"/>
-      <c r="R38" s="243"/>
-      <c r="S38" s="243"/>
-      <c r="T38" s="243"/>
-      <c r="U38" s="243"/>
-      <c r="V38" s="243"/>
-      <c r="W38" s="243"/>
-      <c r="X38" s="243"/>
-      <c r="Y38" s="243"/>
-      <c r="Z38" s="243"/>
+      <c r="A38" s="244"/>
+      <c r="B38" s="244"/>
+      <c r="C38" s="244"/>
+      <c r="D38" s="244"/>
+      <c r="E38" s="244"/>
+      <c r="F38" s="244"/>
+      <c r="G38" s="244"/>
+      <c r="H38" s="244"/>
+      <c r="I38" s="244"/>
+      <c r="J38" s="244"/>
+      <c r="K38" s="244"/>
+      <c r="L38" s="244"/>
+      <c r="M38" s="244"/>
+      <c r="N38" s="244"/>
+      <c r="O38" s="244"/>
+      <c r="P38" s="244"/>
+      <c r="Q38" s="244"/>
+      <c r="R38" s="244"/>
+      <c r="S38" s="244"/>
+      <c r="T38" s="244"/>
+      <c r="U38" s="244"/>
+      <c r="V38" s="244"/>
+      <c r="W38" s="244"/>
+      <c r="X38" s="244"/>
+      <c r="Y38" s="244"/>
+      <c r="Z38" s="244"/>
     </row>
     <row r="39" spans="1:26">
-      <c r="A39" s="243"/>
-      <c r="B39" s="243"/>
-      <c r="C39" s="243"/>
-      <c r="D39" s="243"/>
-      <c r="E39" s="243"/>
-      <c r="F39" s="243"/>
-      <c r="G39" s="243"/>
-      <c r="H39" s="243"/>
-      <c r="I39" s="243"/>
-      <c r="J39" s="243"/>
-      <c r="K39" s="243"/>
-      <c r="L39" s="243"/>
-      <c r="M39" s="243"/>
-      <c r="N39" s="243"/>
-      <c r="O39" s="243"/>
-      <c r="P39" s="243"/>
-      <c r="Q39" s="243"/>
-      <c r="R39" s="243"/>
-      <c r="S39" s="243"/>
-      <c r="T39" s="243"/>
-      <c r="U39" s="243"/>
-      <c r="V39" s="243"/>
-      <c r="W39" s="243"/>
-      <c r="X39" s="243"/>
-      <c r="Y39" s="243"/>
-      <c r="Z39" s="243"/>
+      <c r="A39" s="244"/>
+      <c r="B39" s="244"/>
+      <c r="C39" s="244"/>
+      <c r="D39" s="244"/>
+      <c r="E39" s="244"/>
+      <c r="F39" s="244"/>
+      <c r="G39" s="244"/>
+      <c r="H39" s="244"/>
+      <c r="I39" s="244"/>
+      <c r="J39" s="244"/>
+      <c r="K39" s="244"/>
+      <c r="L39" s="244"/>
+      <c r="M39" s="244"/>
+      <c r="N39" s="244"/>
+      <c r="O39" s="244"/>
+      <c r="P39" s="244"/>
+      <c r="Q39" s="244"/>
+      <c r="R39" s="244"/>
+      <c r="S39" s="244"/>
+      <c r="T39" s="244"/>
+      <c r="U39" s="244"/>
+      <c r="V39" s="244"/>
+      <c r="W39" s="244"/>
+      <c r="X39" s="244"/>
+      <c r="Y39" s="244"/>
+      <c r="Z39" s="244"/>
     </row>
     <row r="40" spans="1:26">
-      <c r="A40" s="243"/>
-      <c r="B40" s="243"/>
-      <c r="C40" s="243"/>
-      <c r="D40" s="243"/>
-      <c r="E40" s="243"/>
-      <c r="F40" s="243"/>
-      <c r="G40" s="243"/>
-      <c r="H40" s="243"/>
-      <c r="I40" s="243"/>
-      <c r="J40" s="243"/>
-      <c r="K40" s="243"/>
-      <c r="L40" s="243"/>
-      <c r="M40" s="243"/>
-      <c r="N40" s="243"/>
-      <c r="O40" s="243"/>
-      <c r="P40" s="243"/>
-      <c r="Q40" s="243"/>
-      <c r="R40" s="243"/>
-      <c r="S40" s="243"/>
-      <c r="T40" s="243"/>
-      <c r="U40" s="243"/>
-      <c r="V40" s="243"/>
-      <c r="W40" s="243"/>
-      <c r="X40" s="243"/>
-      <c r="Y40" s="243"/>
-      <c r="Z40" s="243"/>
+      <c r="A40" s="244"/>
+      <c r="B40" s="244"/>
+      <c r="C40" s="244"/>
+      <c r="D40" s="244"/>
+      <c r="E40" s="244"/>
+      <c r="F40" s="244"/>
+      <c r="G40" s="244"/>
+      <c r="H40" s="244"/>
+      <c r="I40" s="244"/>
+      <c r="J40" s="244"/>
+      <c r="K40" s="244"/>
+      <c r="L40" s="244"/>
+      <c r="M40" s="244"/>
+      <c r="N40" s="244"/>
+      <c r="O40" s="244"/>
+      <c r="P40" s="244"/>
+      <c r="Q40" s="244"/>
+      <c r="R40" s="244"/>
+      <c r="S40" s="244"/>
+      <c r="T40" s="244"/>
+      <c r="U40" s="244"/>
+      <c r="V40" s="244"/>
+      <c r="W40" s="244"/>
+      <c r="X40" s="244"/>
+      <c r="Y40" s="244"/>
+      <c r="Z40" s="244"/>
     </row>
     <row r="41" spans="1:26">
-      <c r="A41" s="243"/>
-      <c r="B41" s="243"/>
-      <c r="C41" s="243"/>
-      <c r="D41" s="243"/>
-      <c r="E41" s="243"/>
-      <c r="F41" s="243"/>
-      <c r="G41" s="243"/>
-      <c r="H41" s="243"/>
-      <c r="I41" s="243"/>
-      <c r="J41" s="243"/>
-      <c r="K41" s="243"/>
-      <c r="L41" s="243"/>
-      <c r="M41" s="243"/>
-      <c r="N41" s="243"/>
-      <c r="O41" s="243"/>
-      <c r="P41" s="243"/>
-      <c r="Q41" s="243"/>
-      <c r="R41" s="243"/>
-      <c r="S41" s="243"/>
-      <c r="T41" s="243"/>
-      <c r="U41" s="243"/>
-      <c r="V41" s="243"/>
-      <c r="W41" s="243"/>
-      <c r="X41" s="243"/>
-      <c r="Y41" s="243"/>
-      <c r="Z41" s="243"/>
+      <c r="A41" s="244"/>
+      <c r="B41" s="244"/>
+      <c r="C41" s="244"/>
+      <c r="D41" s="244"/>
+      <c r="E41" s="244"/>
+      <c r="F41" s="244"/>
+      <c r="G41" s="244"/>
+      <c r="H41" s="244"/>
+      <c r="I41" s="244"/>
+      <c r="J41" s="244"/>
+      <c r="K41" s="244"/>
+      <c r="L41" s="244"/>
+      <c r="M41" s="244"/>
+      <c r="N41" s="244"/>
+      <c r="O41" s="244"/>
+      <c r="P41" s="244"/>
+      <c r="Q41" s="244"/>
+      <c r="R41" s="244"/>
+      <c r="S41" s="244"/>
+      <c r="T41" s="244"/>
+      <c r="U41" s="244"/>
+      <c r="V41" s="244"/>
+      <c r="W41" s="244"/>
+      <c r="X41" s="244"/>
+      <c r="Y41" s="244"/>
+      <c r="Z41" s="244"/>
     </row>
     <row r="42" spans="1:26">
-      <c r="A42" s="243"/>
-      <c r="B42" s="243"/>
-      <c r="C42" s="243"/>
-      <c r="D42" s="243"/>
-      <c r="E42" s="243"/>
-      <c r="F42" s="243"/>
-      <c r="G42" s="243"/>
-      <c r="H42" s="243"/>
-      <c r="I42" s="243"/>
-      <c r="J42" s="243"/>
-      <c r="K42" s="243"/>
-      <c r="L42" s="243"/>
-      <c r="M42" s="243"/>
-      <c r="N42" s="243"/>
-      <c r="O42" s="243"/>
-      <c r="P42" s="243"/>
-      <c r="Q42" s="243"/>
-      <c r="R42" s="243"/>
-      <c r="S42" s="243"/>
-      <c r="T42" s="243"/>
-      <c r="U42" s="243"/>
-      <c r="V42" s="243"/>
-      <c r="W42" s="243"/>
-      <c r="X42" s="243"/>
-      <c r="Y42" s="243"/>
-      <c r="Z42" s="243"/>
+      <c r="A42" s="244"/>
+      <c r="B42" s="244"/>
+      <c r="C42" s="244"/>
+      <c r="D42" s="244"/>
+      <c r="E42" s="244"/>
+      <c r="F42" s="244"/>
+      <c r="G42" s="244"/>
+      <c r="H42" s="244"/>
+      <c r="I42" s="244"/>
+      <c r="J42" s="244"/>
+      <c r="K42" s="244"/>
+      <c r="L42" s="244"/>
+      <c r="M42" s="244"/>
+      <c r="N42" s="244"/>
+      <c r="O42" s="244"/>
+      <c r="P42" s="244"/>
+      <c r="Q42" s="244"/>
+      <c r="R42" s="244"/>
+      <c r="S42" s="244"/>
+      <c r="T42" s="244"/>
+      <c r="U42" s="244"/>
+      <c r="V42" s="244"/>
+      <c r="W42" s="244"/>
+      <c r="X42" s="244"/>
+      <c r="Y42" s="244"/>
+      <c r="Z42" s="244"/>
     </row>
     <row r="43" spans="1:26">
-      <c r="A43" s="243"/>
-      <c r="B43" s="243"/>
-      <c r="C43" s="243"/>
-      <c r="D43" s="243"/>
-      <c r="E43" s="243"/>
-      <c r="F43" s="243"/>
-      <c r="G43" s="243"/>
-      <c r="H43" s="243"/>
-      <c r="I43" s="243"/>
-      <c r="J43" s="243"/>
-      <c r="K43" s="243"/>
-      <c r="L43" s="243"/>
-      <c r="M43" s="243"/>
-      <c r="N43" s="243"/>
-      <c r="O43" s="243"/>
-      <c r="P43" s="243"/>
-      <c r="Q43" s="243"/>
-      <c r="R43" s="243"/>
-      <c r="S43" s="243"/>
-      <c r="T43" s="243"/>
-      <c r="U43" s="243"/>
-      <c r="V43" s="243"/>
-      <c r="W43" s="243"/>
-      <c r="X43" s="243"/>
-      <c r="Y43" s="243"/>
-      <c r="Z43" s="243"/>
+      <c r="A43" s="244"/>
+      <c r="B43" s="244"/>
+      <c r="C43" s="244"/>
+      <c r="D43" s="244"/>
+      <c r="E43" s="244"/>
+      <c r="F43" s="244"/>
+      <c r="G43" s="244"/>
+      <c r="H43" s="244"/>
+      <c r="I43" s="244"/>
+      <c r="J43" s="244"/>
+      <c r="K43" s="244"/>
+      <c r="L43" s="244"/>
+      <c r="M43" s="244"/>
+      <c r="N43" s="244"/>
+      <c r="O43" s="244"/>
+      <c r="P43" s="244"/>
+      <c r="Q43" s="244"/>
+      <c r="R43" s="244"/>
+      <c r="S43" s="244"/>
+      <c r="T43" s="244"/>
+      <c r="U43" s="244"/>
+      <c r="V43" s="244"/>
+      <c r="W43" s="244"/>
+      <c r="X43" s="244"/>
+      <c r="Y43" s="244"/>
+      <c r="Z43" s="244"/>
     </row>
     <row r="44" spans="1:26">
-      <c r="A44" s="243"/>
-      <c r="B44" s="243"/>
-      <c r="C44" s="243"/>
-      <c r="D44" s="243"/>
-      <c r="E44" s="243"/>
-      <c r="F44" s="243"/>
-      <c r="G44" s="243"/>
-      <c r="H44" s="243"/>
-      <c r="I44" s="243"/>
-      <c r="J44" s="243"/>
-      <c r="K44" s="243"/>
-      <c r="L44" s="243"/>
-      <c r="M44" s="243"/>
-      <c r="N44" s="243"/>
-      <c r="O44" s="243"/>
-      <c r="P44" s="243"/>
-      <c r="Q44" s="243"/>
-      <c r="R44" s="243"/>
-      <c r="S44" s="243"/>
-      <c r="T44" s="243"/>
-      <c r="U44" s="243"/>
-      <c r="V44" s="243"/>
-      <c r="W44" s="243"/>
-      <c r="X44" s="243"/>
-      <c r="Y44" s="243"/>
-      <c r="Z44" s="243"/>
+      <c r="A44" s="244"/>
+      <c r="B44" s="244"/>
+      <c r="C44" s="244"/>
+      <c r="D44" s="244"/>
+      <c r="E44" s="244"/>
+      <c r="F44" s="244"/>
+      <c r="G44" s="244"/>
+      <c r="H44" s="244"/>
+      <c r="I44" s="244"/>
+      <c r="J44" s="244"/>
+      <c r="K44" s="244"/>
+      <c r="L44" s="244"/>
+      <c r="M44" s="244"/>
+      <c r="N44" s="244"/>
+      <c r="O44" s="244"/>
+      <c r="P44" s="244"/>
+      <c r="Q44" s="244"/>
+      <c r="R44" s="244"/>
+      <c r="S44" s="244"/>
+      <c r="T44" s="244"/>
+      <c r="U44" s="244"/>
+      <c r="V44" s="244"/>
+      <c r="W44" s="244"/>
+      <c r="X44" s="244"/>
+      <c r="Y44" s="244"/>
+      <c r="Z44" s="244"/>
     </row>
     <row r="45" spans="1:26">
-      <c r="A45" s="243"/>
-      <c r="B45" s="243"/>
-      <c r="C45" s="243"/>
-      <c r="D45" s="243"/>
-      <c r="E45" s="243"/>
-      <c r="F45" s="243"/>
-      <c r="G45" s="243"/>
-      <c r="H45" s="243"/>
-      <c r="I45" s="243"/>
-      <c r="J45" s="243"/>
-      <c r="K45" s="243"/>
-      <c r="L45" s="243"/>
-      <c r="M45" s="243"/>
-      <c r="N45" s="243"/>
-      <c r="O45" s="243"/>
-      <c r="P45" s="243"/>
-      <c r="Q45" s="243"/>
-      <c r="R45" s="243"/>
-      <c r="S45" s="243"/>
-      <c r="T45" s="243"/>
-      <c r="U45" s="243"/>
-      <c r="V45" s="243"/>
-      <c r="W45" s="243"/>
-      <c r="X45" s="243"/>
-      <c r="Y45" s="243"/>
-      <c r="Z45" s="243"/>
+      <c r="A45" s="244"/>
+      <c r="B45" s="244"/>
+      <c r="C45" s="244"/>
+      <c r="D45" s="244"/>
+      <c r="E45" s="244"/>
+      <c r="F45" s="244"/>
+      <c r="G45" s="244"/>
+      <c r="H45" s="244"/>
+      <c r="I45" s="244"/>
+      <c r="J45" s="244"/>
+      <c r="K45" s="244"/>
+      <c r="L45" s="244"/>
+      <c r="M45" s="244"/>
+      <c r="N45" s="244"/>
+      <c r="O45" s="244"/>
+      <c r="P45" s="244"/>
+      <c r="Q45" s="244"/>
+      <c r="R45" s="244"/>
+      <c r="S45" s="244"/>
+      <c r="T45" s="244"/>
+      <c r="U45" s="244"/>
+      <c r="V45" s="244"/>
+      <c r="W45" s="244"/>
+      <c r="X45" s="244"/>
+      <c r="Y45" s="244"/>
+      <c r="Z45" s="244"/>
     </row>
     <row r="46" spans="1:26">
-      <c r="A46" s="243"/>
-      <c r="B46" s="243"/>
-      <c r="C46" s="243"/>
-      <c r="D46" s="243"/>
-      <c r="E46" s="243"/>
-      <c r="F46" s="243"/>
-      <c r="G46" s="243"/>
-      <c r="H46" s="243"/>
-      <c r="I46" s="243"/>
-      <c r="J46" s="243"/>
-      <c r="K46" s="243"/>
-      <c r="L46" s="243"/>
-      <c r="M46" s="243"/>
-      <c r="N46" s="243"/>
-      <c r="O46" s="243"/>
-      <c r="P46" s="243"/>
-      <c r="Q46" s="243"/>
-      <c r="R46" s="243"/>
-      <c r="S46" s="243"/>
-      <c r="T46" s="243"/>
-      <c r="U46" s="243"/>
-      <c r="V46" s="243"/>
-      <c r="W46" s="243"/>
-      <c r="X46" s="243"/>
-      <c r="Y46" s="243"/>
-      <c r="Z46" s="243"/>
+      <c r="A46" s="244"/>
+      <c r="B46" s="244"/>
+      <c r="C46" s="244"/>
+      <c r="D46" s="244"/>
+      <c r="E46" s="244"/>
+      <c r="F46" s="244"/>
+      <c r="G46" s="244"/>
+      <c r="H46" s="244"/>
+      <c r="I46" s="244"/>
+      <c r="J46" s="244"/>
+      <c r="K46" s="244"/>
+      <c r="L46" s="244"/>
+      <c r="M46" s="244"/>
+      <c r="N46" s="244"/>
+      <c r="O46" s="244"/>
+      <c r="P46" s="244"/>
+      <c r="Q46" s="244"/>
+      <c r="R46" s="244"/>
+      <c r="S46" s="244"/>
+      <c r="T46" s="244"/>
+      <c r="U46" s="244"/>
+      <c r="V46" s="244"/>
+      <c r="W46" s="244"/>
+      <c r="X46" s="244"/>
+      <c r="Y46" s="244"/>
+      <c r="Z46" s="244"/>
     </row>
     <row r="47" spans="1:26">
-      <c r="A47" s="243"/>
-      <c r="B47" s="243"/>
-      <c r="C47" s="243"/>
-      <c r="D47" s="243"/>
-      <c r="E47" s="243"/>
-      <c r="F47" s="243"/>
-      <c r="G47" s="243"/>
-      <c r="H47" s="243"/>
-      <c r="I47" s="243"/>
-      <c r="J47" s="243"/>
-      <c r="K47" s="243"/>
-      <c r="L47" s="243"/>
-      <c r="M47" s="243"/>
-      <c r="N47" s="243"/>
-      <c r="O47" s="243"/>
-      <c r="P47" s="243"/>
-      <c r="Q47" s="243"/>
-      <c r="R47" s="243"/>
-      <c r="S47" s="243"/>
-      <c r="T47" s="243"/>
-      <c r="U47" s="243"/>
-      <c r="V47" s="243"/>
-      <c r="W47" s="243"/>
-      <c r="X47" s="243"/>
-      <c r="Y47" s="243"/>
-      <c r="Z47" s="243"/>
+      <c r="A47" s="244"/>
+      <c r="B47" s="244"/>
+      <c r="C47" s="244"/>
+      <c r="D47" s="244"/>
+      <c r="E47" s="244"/>
+      <c r="F47" s="244"/>
+      <c r="G47" s="244"/>
+      <c r="H47" s="244"/>
+      <c r="I47" s="244"/>
+      <c r="J47" s="244"/>
+      <c r="K47" s="244"/>
+      <c r="L47" s="244"/>
+      <c r="M47" s="244"/>
+      <c r="N47" s="244"/>
+      <c r="O47" s="244"/>
+      <c r="P47" s="244"/>
+      <c r="Q47" s="244"/>
+      <c r="R47" s="244"/>
+      <c r="S47" s="244"/>
+      <c r="T47" s="244"/>
+      <c r="U47" s="244"/>
+      <c r="V47" s="244"/>
+      <c r="W47" s="244"/>
+      <c r="X47" s="244"/>
+      <c r="Y47" s="244"/>
+      <c r="Z47" s="244"/>
     </row>
     <row r="48" spans="1:26">
-      <c r="A48" s="243"/>
-      <c r="B48" s="243"/>
-      <c r="C48" s="243"/>
-      <c r="D48" s="243"/>
-      <c r="E48" s="243"/>
-      <c r="F48" s="243"/>
-      <c r="G48" s="243"/>
-      <c r="H48" s="243"/>
-      <c r="I48" s="243"/>
-      <c r="J48" s="243"/>
-      <c r="K48" s="243"/>
-      <c r="L48" s="243"/>
-      <c r="M48" s="243"/>
-      <c r="N48" s="243"/>
-      <c r="O48" s="243"/>
-      <c r="P48" s="243"/>
-      <c r="Q48" s="243"/>
-      <c r="R48" s="243"/>
-      <c r="S48" s="243"/>
-      <c r="T48" s="243"/>
-      <c r="U48" s="243"/>
-      <c r="V48" s="243"/>
-      <c r="W48" s="243"/>
-      <c r="X48" s="243"/>
-      <c r="Y48" s="243"/>
-      <c r="Z48" s="243"/>
+      <c r="A48" s="244"/>
+      <c r="B48" s="244"/>
+      <c r="C48" s="244"/>
+      <c r="D48" s="244"/>
+      <c r="E48" s="244"/>
+      <c r="F48" s="244"/>
+      <c r="G48" s="244"/>
+      <c r="H48" s="244"/>
+      <c r="I48" s="244"/>
+      <c r="J48" s="244"/>
+      <c r="K48" s="244"/>
+      <c r="L48" s="244"/>
+      <c r="M48" s="244"/>
+      <c r="N48" s="244"/>
+      <c r="O48" s="244"/>
+      <c r="P48" s="244"/>
+      <c r="Q48" s="244"/>
+      <c r="R48" s="244"/>
+      <c r="S48" s="244"/>
+      <c r="T48" s="244"/>
+      <c r="U48" s="244"/>
+      <c r="V48" s="244"/>
+      <c r="W48" s="244"/>
+      <c r="X48" s="244"/>
+      <c r="Y48" s="244"/>
+      <c r="Z48" s="244"/>
     </row>
     <row r="49" spans="1:26">
-      <c r="A49" s="243"/>
-      <c r="B49" s="243"/>
-      <c r="C49" s="243"/>
-      <c r="D49" s="243"/>
-      <c r="E49" s="243"/>
-      <c r="F49" s="243"/>
-      <c r="G49" s="243"/>
-      <c r="H49" s="243"/>
-      <c r="I49" s="243"/>
-      <c r="J49" s="243"/>
-      <c r="K49" s="243"/>
-      <c r="L49" s="243"/>
-      <c r="M49" s="243"/>
-      <c r="N49" s="243"/>
-      <c r="O49" s="243"/>
-      <c r="P49" s="243"/>
-      <c r="Q49" s="243"/>
-      <c r="R49" s="243"/>
-      <c r="S49" s="243"/>
-      <c r="T49" s="243"/>
-      <c r="U49" s="243"/>
-      <c r="V49" s="243"/>
-      <c r="W49" s="243"/>
-      <c r="X49" s="243"/>
-      <c r="Y49" s="243"/>
-      <c r="Z49" s="243"/>
+      <c r="A49" s="244"/>
+      <c r="B49" s="244"/>
+      <c r="C49" s="244"/>
+      <c r="D49" s="244"/>
+      <c r="E49" s="244"/>
+      <c r="F49" s="244"/>
+      <c r="G49" s="244"/>
+      <c r="H49" s="244"/>
+      <c r="I49" s="244"/>
+      <c r="J49" s="244"/>
+      <c r="K49" s="244"/>
+      <c r="L49" s="244"/>
+      <c r="M49" s="244"/>
+      <c r="N49" s="244"/>
+      <c r="O49" s="244"/>
+      <c r="P49" s="244"/>
+      <c r="Q49" s="244"/>
+      <c r="R49" s="244"/>
+      <c r="S49" s="244"/>
+      <c r="T49" s="244"/>
+      <c r="U49" s="244"/>
+      <c r="V49" s="244"/>
+      <c r="W49" s="244"/>
+      <c r="X49" s="244"/>
+      <c r="Y49" s="244"/>
+      <c r="Z49" s="244"/>
     </row>
     <row r="50" spans="1:26">
-      <c r="A50" s="243"/>
-      <c r="B50" s="243"/>
-      <c r="C50" s="243"/>
-      <c r="D50" s="243"/>
-      <c r="E50" s="243"/>
-      <c r="F50" s="243"/>
-      <c r="G50" s="243"/>
-      <c r="H50" s="243"/>
-      <c r="I50" s="243"/>
-      <c r="J50" s="243"/>
-      <c r="K50" s="243"/>
-      <c r="L50" s="243"/>
-      <c r="M50" s="243"/>
-      <c r="N50" s="243"/>
-      <c r="O50" s="243"/>
-      <c r="P50" s="243"/>
-      <c r="Q50" s="243"/>
-      <c r="R50" s="243"/>
-      <c r="S50" s="243"/>
-      <c r="T50" s="243"/>
-      <c r="U50" s="243"/>
-      <c r="V50" s="243"/>
-      <c r="W50" s="243"/>
-      <c r="X50" s="243"/>
-      <c r="Y50" s="243"/>
-      <c r="Z50" s="243"/>
+      <c r="A50" s="244"/>
+      <c r="B50" s="244"/>
+      <c r="C50" s="244"/>
+      <c r="D50" s="244"/>
+      <c r="E50" s="244"/>
+      <c r="F50" s="244"/>
+      <c r="G50" s="244"/>
+      <c r="H50" s="244"/>
+      <c r="I50" s="244"/>
+      <c r="J50" s="244"/>
+      <c r="K50" s="244"/>
+      <c r="L50" s="244"/>
+      <c r="M50" s="244"/>
+      <c r="N50" s="244"/>
+      <c r="O50" s="244"/>
+      <c r="P50" s="244"/>
+      <c r="Q50" s="244"/>
+      <c r="R50" s="244"/>
+      <c r="S50" s="244"/>
+      <c r="T50" s="244"/>
+      <c r="U50" s="244"/>
+      <c r="V50" s="244"/>
+      <c r="W50" s="244"/>
+      <c r="X50" s="244"/>
+      <c r="Y50" s="244"/>
+      <c r="Z50" s="244"/>
     </row>
     <row r="51" spans="1:26">
-      <c r="A51" s="243"/>
-      <c r="B51" s="243"/>
-      <c r="C51" s="243"/>
-      <c r="D51" s="243"/>
-      <c r="E51" s="243"/>
-      <c r="F51" s="243"/>
-      <c r="G51" s="243"/>
-      <c r="H51" s="243"/>
-      <c r="I51" s="243"/>
-      <c r="J51" s="243"/>
-      <c r="K51" s="243"/>
-      <c r="L51" s="243"/>
-      <c r="M51" s="243"/>
-      <c r="N51" s="243"/>
-      <c r="O51" s="243"/>
-      <c r="P51" s="243"/>
-      <c r="Q51" s="243"/>
-      <c r="R51" s="243"/>
-      <c r="S51" s="243"/>
-      <c r="T51" s="243"/>
-      <c r="U51" s="243"/>
-      <c r="V51" s="243"/>
-      <c r="W51" s="243"/>
-      <c r="X51" s="243"/>
-      <c r="Y51" s="243"/>
-      <c r="Z51" s="243"/>
+      <c r="A51" s="244"/>
+      <c r="B51" s="244"/>
+      <c r="C51" s="244"/>
+      <c r="D51" s="244"/>
+      <c r="E51" s="244"/>
+      <c r="F51" s="244"/>
+      <c r="G51" s="244"/>
+      <c r="H51" s="244"/>
+      <c r="I51" s="244"/>
+      <c r="J51" s="244"/>
+      <c r="K51" s="244"/>
+      <c r="L51" s="244"/>
+      <c r="M51" s="244"/>
+      <c r="N51" s="244"/>
+      <c r="O51" s="244"/>
+      <c r="P51" s="244"/>
+      <c r="Q51" s="244"/>
+      <c r="R51" s="244"/>
+      <c r="S51" s="244"/>
+      <c r="T51" s="244"/>
+      <c r="U51" s="244"/>
+      <c r="V51" s="244"/>
+      <c r="W51" s="244"/>
+      <c r="X51" s="244"/>
+      <c r="Y51" s="244"/>
+      <c r="Z51" s="244"/>
     </row>
     <row r="52" spans="1:26">
-      <c r="A52" s="243"/>
-      <c r="B52" s="243"/>
-      <c r="C52" s="243"/>
-      <c r="D52" s="243"/>
-      <c r="E52" s="243"/>
-      <c r="F52" s="243"/>
-      <c r="G52" s="243"/>
-      <c r="H52" s="243"/>
-      <c r="I52" s="243"/>
-      <c r="J52" s="243"/>
-      <c r="K52" s="243"/>
-      <c r="L52" s="243"/>
-      <c r="M52" s="243"/>
-      <c r="N52" s="243"/>
-      <c r="O52" s="243"/>
-      <c r="P52" s="243"/>
-      <c r="Q52" s="243"/>
-      <c r="R52" s="243"/>
-      <c r="S52" s="243"/>
-      <c r="T52" s="243"/>
-      <c r="U52" s="243"/>
-      <c r="V52" s="243"/>
-      <c r="W52" s="243"/>
-      <c r="X52" s="243"/>
-      <c r="Y52" s="243"/>
-      <c r="Z52" s="243"/>
+      <c r="A52" s="244"/>
+      <c r="B52" s="244"/>
+      <c r="C52" s="244"/>
+      <c r="D52" s="244"/>
+      <c r="E52" s="244"/>
+      <c r="F52" s="244"/>
+      <c r="G52" s="244"/>
+      <c r="H52" s="244"/>
+      <c r="I52" s="244"/>
+      <c r="J52" s="244"/>
+      <c r="K52" s="244"/>
+      <c r="L52" s="244"/>
+      <c r="M52" s="244"/>
+      <c r="N52" s="244"/>
+      <c r="O52" s="244"/>
+      <c r="P52" s="244"/>
+      <c r="Q52" s="244"/>
+      <c r="R52" s="244"/>
+      <c r="S52" s="244"/>
+      <c r="T52" s="244"/>
+      <c r="U52" s="244"/>
+      <c r="V52" s="244"/>
+      <c r="W52" s="244"/>
+      <c r="X52" s="244"/>
+      <c r="Y52" s="244"/>
+      <c r="Z52" s="244"/>
     </row>
     <row r="53" spans="1:26">
-      <c r="A53" s="243"/>
-      <c r="B53" s="243"/>
-      <c r="C53" s="243"/>
-      <c r="D53" s="243"/>
-      <c r="E53" s="243"/>
-      <c r="F53" s="243"/>
-      <c r="G53" s="243"/>
-      <c r="H53" s="243"/>
-      <c r="I53" s="243"/>
-      <c r="J53" s="243"/>
-      <c r="K53" s="243"/>
-      <c r="L53" s="243"/>
-      <c r="M53" s="243"/>
-      <c r="N53" s="243"/>
-      <c r="O53" s="243"/>
-      <c r="P53" s="243"/>
-      <c r="Q53" s="243"/>
-      <c r="R53" s="243"/>
-      <c r="S53" s="243"/>
-      <c r="T53" s="243"/>
-      <c r="U53" s="243"/>
-      <c r="V53" s="243"/>
-      <c r="W53" s="243"/>
-      <c r="X53" s="243"/>
-      <c r="Y53" s="243"/>
-      <c r="Z53" s="243"/>
+      <c r="A53" s="244"/>
+      <c r="B53" s="244"/>
+      <c r="C53" s="244"/>
+      <c r="D53" s="244"/>
+      <c r="E53" s="244"/>
+      <c r="F53" s="244"/>
+      <c r="G53" s="244"/>
+      <c r="H53" s="244"/>
+      <c r="I53" s="244"/>
+      <c r="J53" s="244"/>
+      <c r="K53" s="244"/>
+      <c r="L53" s="244"/>
+      <c r="M53" s="244"/>
+      <c r="N53" s="244"/>
+      <c r="O53" s="244"/>
+      <c r="P53" s="244"/>
+      <c r="Q53" s="244"/>
+      <c r="R53" s="244"/>
+      <c r="S53" s="244"/>
+      <c r="T53" s="244"/>
+      <c r="U53" s="244"/>
+      <c r="V53" s="244"/>
+      <c r="W53" s="244"/>
+      <c r="X53" s="244"/>
+      <c r="Y53" s="244"/>
+      <c r="Z53" s="244"/>
     </row>
     <row r="54" spans="1:26">
-      <c r="A54" s="243"/>
-      <c r="B54" s="243"/>
-      <c r="C54" s="243"/>
-      <c r="D54" s="243"/>
-      <c r="E54" s="243"/>
-      <c r="F54" s="243"/>
-      <c r="G54" s="243"/>
-      <c r="H54" s="243"/>
-      <c r="I54" s="243"/>
-      <c r="J54" s="243"/>
-      <c r="K54" s="243"/>
-      <c r="L54" s="243"/>
-      <c r="M54" s="243"/>
-      <c r="N54" s="243"/>
-      <c r="O54" s="243"/>
-      <c r="P54" s="243"/>
-      <c r="Q54" s="243"/>
-      <c r="R54" s="243"/>
-      <c r="S54" s="243"/>
-      <c r="T54" s="243"/>
-      <c r="U54" s="243"/>
-      <c r="V54" s="243"/>
-      <c r="W54" s="243"/>
-      <c r="X54" s="243"/>
-      <c r="Y54" s="243"/>
-      <c r="Z54" s="243"/>
+      <c r="A54" s="244"/>
+      <c r="B54" s="244"/>
+      <c r="C54" s="244"/>
+      <c r="D54" s="244"/>
+      <c r="E54" s="244"/>
+      <c r="F54" s="244"/>
+      <c r="G54" s="244"/>
+      <c r="H54" s="244"/>
+      <c r="I54" s="244"/>
+      <c r="J54" s="244"/>
+      <c r="K54" s="244"/>
+      <c r="L54" s="244"/>
+      <c r="M54" s="244"/>
+      <c r="N54" s="244"/>
+      <c r="O54" s="244"/>
+      <c r="P54" s="244"/>
+      <c r="Q54" s="244"/>
+      <c r="R54" s="244"/>
+      <c r="S54" s="244"/>
+      <c r="T54" s="244"/>
+      <c r="U54" s="244"/>
+      <c r="V54" s="244"/>
+      <c r="W54" s="244"/>
+      <c r="X54" s="244"/>
+      <c r="Y54" s="244"/>
+      <c r="Z54" s="244"/>
     </row>
     <row r="55" spans="1:26">
-      <c r="A55" s="243"/>
-      <c r="B55" s="243"/>
-      <c r="C55" s="243"/>
-      <c r="D55" s="243"/>
-      <c r="E55" s="243"/>
-      <c r="F55" s="243"/>
-      <c r="G55" s="243"/>
-      <c r="H55" s="243"/>
-      <c r="I55" s="243"/>
-      <c r="J55" s="243"/>
-      <c r="K55" s="243"/>
-      <c r="L55" s="243"/>
-      <c r="M55" s="243"/>
-      <c r="N55" s="243"/>
-      <c r="O55" s="243"/>
-      <c r="P55" s="243"/>
-      <c r="Q55" s="243"/>
-      <c r="R55" s="243"/>
-      <c r="S55" s="243"/>
-      <c r="T55" s="243"/>
-      <c r="U55" s="243"/>
-      <c r="V55" s="243"/>
-      <c r="W55" s="243"/>
-      <c r="X55" s="243"/>
-      <c r="Y55" s="243"/>
-      <c r="Z55" s="243"/>
+      <c r="A55" s="244"/>
+      <c r="B55" s="244"/>
+      <c r="C55" s="244"/>
+      <c r="D55" s="244"/>
+      <c r="E55" s="244"/>
+      <c r="F55" s="244"/>
+      <c r="G55" s="244"/>
+      <c r="H55" s="244"/>
+      <c r="I55" s="244"/>
+      <c r="J55" s="244"/>
+      <c r="K55" s="244"/>
+      <c r="L55" s="244"/>
+      <c r="M55" s="244"/>
+      <c r="N55" s="244"/>
+      <c r="O55" s="244"/>
+      <c r="P55" s="244"/>
+      <c r="Q55" s="244"/>
+      <c r="R55" s="244"/>
+      <c r="S55" s="244"/>
+      <c r="T55" s="244"/>
+      <c r="U55" s="244"/>
+      <c r="V55" s="244"/>
+      <c r="W55" s="244"/>
+      <c r="X55" s="244"/>
+      <c r="Y55" s="244"/>
+      <c r="Z55" s="244"/>
     </row>
     <row r="56" spans="1:26">
-      <c r="A56" s="243"/>
-      <c r="B56" s="243"/>
-      <c r="C56" s="243"/>
-      <c r="D56" s="243"/>
-      <c r="E56" s="243"/>
-      <c r="F56" s="243"/>
-      <c r="G56" s="243"/>
-      <c r="H56" s="243"/>
-      <c r="I56" s="243"/>
-      <c r="J56" s="243"/>
-      <c r="K56" s="243"/>
-      <c r="L56" s="243"/>
-      <c r="M56" s="243"/>
-      <c r="N56" s="243"/>
-      <c r="O56" s="243"/>
-      <c r="P56" s="243"/>
-      <c r="Q56" s="243"/>
-      <c r="R56" s="243"/>
-      <c r="S56" s="243"/>
-      <c r="T56" s="243"/>
-      <c r="U56" s="243"/>
-      <c r="V56" s="243"/>
-      <c r="W56" s="243"/>
-      <c r="X56" s="243"/>
-      <c r="Y56" s="243"/>
-      <c r="Z56" s="243"/>
+      <c r="A56" s="244"/>
+      <c r="B56" s="244"/>
+      <c r="C56" s="244"/>
+      <c r="D56" s="244"/>
+      <c r="E56" s="244"/>
+      <c r="F56" s="244"/>
+      <c r="G56" s="244"/>
+      <c r="H56" s="244"/>
+      <c r="I56" s="244"/>
+      <c r="J56" s="244"/>
+      <c r="K56" s="244"/>
+      <c r="L56" s="244"/>
+      <c r="M56" s="244"/>
+      <c r="N56" s="244"/>
+      <c r="O56" s="244"/>
+      <c r="P56" s="244"/>
+      <c r="Q56" s="244"/>
+      <c r="R56" s="244"/>
+      <c r="S56" s="244"/>
+      <c r="T56" s="244"/>
+      <c r="U56" s="244"/>
+      <c r="V56" s="244"/>
+      <c r="W56" s="244"/>
+      <c r="X56" s="244"/>
+      <c r="Y56" s="244"/>
+      <c r="Z56" s="244"/>
     </row>
     <row r="57" spans="1:26">
-      <c r="A57" s="243"/>
-      <c r="B57" s="243"/>
-      <c r="C57" s="243"/>
-      <c r="D57" s="243"/>
-      <c r="E57" s="243"/>
-      <c r="F57" s="243"/>
-      <c r="G57" s="243"/>
-      <c r="H57" s="243"/>
-      <c r="I57" s="243"/>
-      <c r="J57" s="243"/>
-      <c r="K57" s="243"/>
-      <c r="L57" s="243"/>
-      <c r="M57" s="243"/>
-      <c r="N57" s="243"/>
-      <c r="O57" s="243"/>
-      <c r="P57" s="243"/>
-      <c r="Q57" s="243"/>
-      <c r="R57" s="243"/>
-      <c r="S57" s="243"/>
-      <c r="T57" s="243"/>
-      <c r="U57" s="243"/>
-      <c r="V57" s="243"/>
-      <c r="W57" s="243"/>
-      <c r="X57" s="243"/>
-      <c r="Y57" s="243"/>
-      <c r="Z57" s="243"/>
+      <c r="A57" s="244"/>
+      <c r="B57" s="244"/>
+      <c r="C57" s="244"/>
+      <c r="D57" s="244"/>
+      <c r="E57" s="244"/>
+      <c r="F57" s="244"/>
+      <c r="G57" s="244"/>
+      <c r="H57" s="244"/>
+      <c r="I57" s="244"/>
+      <c r="J57" s="244"/>
+      <c r="K57" s="244"/>
+      <c r="L57" s="244"/>
+      <c r="M57" s="244"/>
+      <c r="N57" s="244"/>
+      <c r="O57" s="244"/>
+      <c r="P57" s="244"/>
+      <c r="Q57" s="244"/>
+      <c r="R57" s="244"/>
+      <c r="S57" s="244"/>
+      <c r="T57" s="244"/>
+      <c r="U57" s="244"/>
+      <c r="V57" s="244"/>
+      <c r="W57" s="244"/>
+      <c r="X57" s="244"/>
+      <c r="Y57" s="244"/>
+      <c r="Z57" s="244"/>
     </row>
     <row r="58" spans="1:26">
-      <c r="A58" s="243"/>
-      <c r="B58" s="243"/>
-      <c r="C58" s="243"/>
-      <c r="D58" s="243"/>
-      <c r="E58" s="243"/>
-      <c r="F58" s="243"/>
-      <c r="G58" s="243"/>
-      <c r="H58" s="243"/>
-      <c r="I58" s="243"/>
-      <c r="J58" s="243"/>
-      <c r="K58" s="243"/>
-      <c r="L58" s="243"/>
-      <c r="M58" s="243"/>
-      <c r="N58" s="243"/>
-      <c r="O58" s="243"/>
-      <c r="P58" s="243"/>
-      <c r="Q58" s="243"/>
-      <c r="R58" s="243"/>
-      <c r="S58" s="243"/>
-      <c r="T58" s="243"/>
-      <c r="U58" s="243"/>
-      <c r="V58" s="243"/>
-      <c r="W58" s="243"/>
-      <c r="X58" s="243"/>
-      <c r="Y58" s="243"/>
-      <c r="Z58" s="243"/>
+      <c r="A58" s="244"/>
+      <c r="B58" s="244"/>
+      <c r="C58" s="244"/>
+      <c r="D58" s="244"/>
+      <c r="E58" s="244"/>
+      <c r="F58" s="244"/>
+      <c r="G58" s="244"/>
+      <c r="H58" s="244"/>
+      <c r="I58" s="244"/>
+      <c r="J58" s="244"/>
+      <c r="K58" s="244"/>
+      <c r="L58" s="244"/>
+      <c r="M58" s="244"/>
+      <c r="N58" s="244"/>
+      <c r="O58" s="244"/>
+      <c r="P58" s="244"/>
+      <c r="Q58" s="244"/>
+      <c r="R58" s="244"/>
+      <c r="S58" s="244"/>
+      <c r="T58" s="244"/>
+      <c r="U58" s="244"/>
+      <c r="V58" s="244"/>
+      <c r="W58" s="244"/>
+      <c r="X58" s="244"/>
+      <c r="Y58" s="244"/>
+      <c r="Z58" s="244"/>
     </row>
     <row r="59" spans="1:26">
-      <c r="A59" s="243"/>
-      <c r="B59" s="243"/>
-      <c r="C59" s="243"/>
-      <c r="D59" s="243"/>
-      <c r="E59" s="243"/>
-      <c r="F59" s="243"/>
-      <c r="G59" s="243"/>
-      <c r="H59" s="243"/>
-      <c r="I59" s="243"/>
-      <c r="J59" s="243"/>
-      <c r="K59" s="243"/>
-      <c r="L59" s="243"/>
-      <c r="M59" s="243"/>
-      <c r="N59" s="243"/>
-      <c r="O59" s="243"/>
-      <c r="P59" s="243"/>
-      <c r="Q59" s="243"/>
-      <c r="R59" s="243"/>
-      <c r="S59" s="243"/>
-      <c r="T59" s="243"/>
-      <c r="U59" s="243"/>
-      <c r="V59" s="243"/>
-      <c r="W59" s="243"/>
-      <c r="X59" s="243"/>
-      <c r="Y59" s="243"/>
-      <c r="Z59" s="243"/>
+      <c r="A59" s="244"/>
+      <c r="B59" s="244"/>
+      <c r="C59" s="244"/>
+      <c r="D59" s="244"/>
+      <c r="E59" s="244"/>
+      <c r="F59" s="244"/>
+      <c r="G59" s="244"/>
+      <c r="H59" s="244"/>
+      <c r="I59" s="244"/>
+      <c r="J59" s="244"/>
+      <c r="K59" s="244"/>
+      <c r="L59" s="244"/>
+      <c r="M59" s="244"/>
+      <c r="N59" s="244"/>
+      <c r="O59" s="244"/>
+      <c r="P59" s="244"/>
+      <c r="Q59" s="244"/>
+      <c r="R59" s="244"/>
+      <c r="S59" s="244"/>
+      <c r="T59" s="244"/>
+      <c r="U59" s="244"/>
+      <c r="V59" s="244"/>
+      <c r="W59" s="244"/>
+      <c r="X59" s="244"/>
+      <c r="Y59" s="244"/>
+      <c r="Z59" s="244"/>
     </row>
     <row r="60" spans="1:26">
-      <c r="A60" s="243"/>
-      <c r="B60" s="243"/>
-      <c r="C60" s="243"/>
-      <c r="D60" s="243"/>
-      <c r="E60" s="243"/>
-      <c r="F60" s="243"/>
-      <c r="G60" s="243"/>
-      <c r="H60" s="243"/>
-      <c r="I60" s="243"/>
-      <c r="J60" s="243"/>
-      <c r="K60" s="243"/>
-      <c r="L60" s="243"/>
-      <c r="M60" s="243"/>
-      <c r="N60" s="243"/>
-      <c r="O60" s="243"/>
-      <c r="P60" s="243"/>
-      <c r="Q60" s="243"/>
-      <c r="R60" s="243"/>
-      <c r="S60" s="243"/>
-      <c r="T60" s="243"/>
-      <c r="U60" s="243"/>
-      <c r="V60" s="243"/>
-      <c r="W60" s="243"/>
-      <c r="X60" s="243"/>
-      <c r="Y60" s="243"/>
-      <c r="Z60" s="243"/>
+      <c r="A60" s="244"/>
+      <c r="B60" s="244"/>
+      <c r="C60" s="244"/>
+      <c r="D60" s="244"/>
+      <c r="E60" s="244"/>
+      <c r="F60" s="244"/>
+      <c r="G60" s="244"/>
+      <c r="H60" s="244"/>
+      <c r="I60" s="244"/>
+      <c r="J60" s="244"/>
+      <c r="K60" s="244"/>
+      <c r="L60" s="244"/>
+      <c r="M60" s="244"/>
+      <c r="N60" s="244"/>
+      <c r="O60" s="244"/>
+      <c r="P60" s="244"/>
+      <c r="Q60" s="244"/>
+      <c r="R60" s="244"/>
+      <c r="S60" s="244"/>
+      <c r="T60" s="244"/>
+      <c r="U60" s="244"/>
+      <c r="V60" s="244"/>
+      <c r="W60" s="244"/>
+      <c r="X60" s="244"/>
+      <c r="Y60" s="244"/>
+      <c r="Z60" s="244"/>
     </row>
     <row r="61" spans="1:26">
-      <c r="A61" s="243"/>
-      <c r="B61" s="243"/>
-      <c r="C61" s="243"/>
-      <c r="D61" s="243"/>
-      <c r="E61" s="243"/>
-      <c r="F61" s="243"/>
-      <c r="G61" s="243"/>
-      <c r="H61" s="243"/>
-      <c r="I61" s="243"/>
-      <c r="J61" s="243"/>
-      <c r="K61" s="243"/>
-      <c r="L61" s="243"/>
-      <c r="M61" s="243"/>
-      <c r="N61" s="243"/>
-      <c r="O61" s="243"/>
-      <c r="P61" s="243"/>
-      <c r="Q61" s="243"/>
-      <c r="R61" s="243"/>
-      <c r="S61" s="243"/>
-      <c r="T61" s="243"/>
-      <c r="U61" s="243"/>
-      <c r="V61" s="243"/>
-      <c r="W61" s="243"/>
-      <c r="X61" s="243"/>
-      <c r="Y61" s="243"/>
-      <c r="Z61" s="243"/>
+      <c r="A61" s="244"/>
+      <c r="B61" s="244"/>
+      <c r="C61" s="244"/>
+      <c r="D61" s="244"/>
+      <c r="E61" s="244"/>
+      <c r="F61" s="244"/>
+      <c r="G61" s="244"/>
+      <c r="H61" s="244"/>
+      <c r="I61" s="244"/>
+      <c r="J61" s="244"/>
+      <c r="K61" s="244"/>
+      <c r="L61" s="244"/>
+      <c r="M61" s="244"/>
+      <c r="N61" s="244"/>
+      <c r="O61" s="244"/>
+      <c r="P61" s="244"/>
+      <c r="Q61" s="244"/>
+      <c r="R61" s="244"/>
+      <c r="S61" s="244"/>
+      <c r="T61" s="244"/>
+      <c r="U61" s="244"/>
+      <c r="V61" s="244"/>
+      <c r="W61" s="244"/>
+      <c r="X61" s="244"/>
+      <c r="Y61" s="244"/>
+      <c r="Z61" s="244"/>
     </row>
     <row r="62" spans="1:26">
-      <c r="A62" s="243"/>
-      <c r="B62" s="243"/>
-      <c r="C62" s="243"/>
-      <c r="D62" s="243"/>
-      <c r="E62" s="243"/>
-      <c r="F62" s="243"/>
-      <c r="G62" s="243"/>
-      <c r="H62" s="243"/>
-      <c r="I62" s="243"/>
-      <c r="J62" s="243"/>
-      <c r="K62" s="243"/>
-      <c r="L62" s="243"/>
-      <c r="M62" s="243"/>
-      <c r="N62" s="243"/>
-      <c r="O62" s="243"/>
-      <c r="P62" s="243"/>
-      <c r="Q62" s="243"/>
-      <c r="R62" s="243"/>
-      <c r="S62" s="243"/>
-      <c r="T62" s="243"/>
-      <c r="U62" s="243"/>
-      <c r="V62" s="243"/>
-      <c r="W62" s="243"/>
-      <c r="X62" s="243"/>
-      <c r="Y62" s="243"/>
-      <c r="Z62" s="243"/>
+      <c r="A62" s="244"/>
+      <c r="B62" s="244"/>
+      <c r="C62" s="244"/>
+      <c r="D62" s="244"/>
+      <c r="E62" s="244"/>
+      <c r="F62" s="244"/>
+      <c r="G62" s="244"/>
+      <c r="H62" s="244"/>
+      <c r="I62" s="244"/>
+      <c r="J62" s="244"/>
+      <c r="K62" s="244"/>
+      <c r="L62" s="244"/>
+      <c r="M62" s="244"/>
+      <c r="N62" s="244"/>
+      <c r="O62" s="244"/>
+      <c r="P62" s="244"/>
+      <c r="Q62" s="244"/>
+      <c r="R62" s="244"/>
+      <c r="S62" s="244"/>
+      <c r="T62" s="244"/>
+      <c r="U62" s="244"/>
+      <c r="V62" s="244"/>
+      <c r="W62" s="244"/>
+      <c r="X62" s="244"/>
+      <c r="Y62" s="244"/>
+      <c r="Z62" s="244"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1"/>
@@ -4780,7 +4806,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>8643.39</v>
+        <v>8468.42000000001</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -4796,7 +4822,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>8721.61</v>
+        <v>8546.64</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -4812,7 +4838,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12">
         <f ca="1">C108</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -5458,7 +5484,7 @@
     <row r="51" ht="24.75" customHeight="1" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
-        <v>Birdie Sim Card</v>
+        <v>(SHIT COMPANY) Birdie Sim Card</v>
       </c>
       <c r="B51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65")))</f>
@@ -6129,7 +6155,7 @@
       </c>
       <c r="B88" s="36" t="str" cm="1">
         <f ca="1" t="array" ref="B88">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B102"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B102")))</f>
-        <v>Sportify Music Paid For 7th of Each Month</v>
+        <v>Sportify Music Paid For 7th of Each Month. Switch to Apple Music on the 8th of July 2025.</v>
       </c>
       <c r="C88" s="87">
         <v>68</v>
@@ -6311,7 +6337,7 @@
       </c>
       <c r="C98" s="37" cm="1">
         <f ca="1" t="array" ref="C98">INDIRECT("'"&amp;INDIRECT("Main!B27")&amp;"'!C98")+SUM(E118+E145+E172)</f>
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="D98" s="14"/>
       <c r="E98" s="96"/>
@@ -6391,7 +6417,7 @@
       </c>
       <c r="C102" s="37" cm="1">
         <f ca="1" t="array" ref="C102">INDIRECT("'"&amp;INDIRECT("Main!B27")&amp;"'!C102")+SUM(E122+E149+E176)</f>
-        <v>0</v>
+        <v>-326149.51</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
@@ -6431,7 +6457,7 @@
       </c>
       <c r="C104" s="37" cm="1">
         <f ca="1" t="array" ref="C104">INDIRECT("'"&amp;INDIRECT("Main!B27")&amp;"'!C104")+SUM(E124+E151+E178)</f>
-        <v>0</v>
+        <v>-676.03</v>
       </c>
       <c r="D104" s="14"/>
       <c r="E104" s="14"/>
@@ -6507,7 +6533,7 @@
       </c>
       <c r="C108" s="37">
         <f ca="1">SUM(C98:C107)</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -6523,7 +6549,7 @@
       </c>
       <c r="C109" s="37">
         <f ca="1">C108-C96</f>
-        <v>-369.99</v>
+        <v>-327495.53</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -6617,7 +6643,7 @@
       <c r="D116" s="58"/>
       <c r="E116" s="71" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B27")&amp;"'!E190")</f>
-        <v>6807.36</v>
+        <v>6632.39</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -6786,7 +6812,7 @@
       <c r="A129" s="63"/>
       <c r="B129" s="64"/>
       <c r="C129" s="73" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D129" s="74"/>
       <c r="E129" s="87">
@@ -6801,7 +6827,7 @@
       <c r="A130" s="63"/>
       <c r="B130" s="64"/>
       <c r="C130" s="74" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D130" s="74"/>
       <c r="E130" s="87">
@@ -6889,7 +6915,7 @@
       <c r="D136" s="82"/>
       <c r="E136" s="89">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>7382.37</v>
+        <v>7207.40000000001</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -6981,7 +7007,7 @@
       <c r="D143" s="58"/>
       <c r="E143" s="89">
         <f ca="1">E136</f>
-        <v>7382.37</v>
+        <v>7207.40000000001</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -7150,7 +7176,7 @@
       <c r="A156" s="63"/>
       <c r="B156" s="64"/>
       <c r="C156" s="73" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D156" s="74"/>
       <c r="E156" s="87">
@@ -7253,7 +7279,7 @@
       <c r="D163" s="82"/>
       <c r="E163" s="92">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>8068.38</v>
+        <v>7893.41000000001</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -7345,7 +7371,7 @@
       <c r="D170" s="58"/>
       <c r="E170" s="92">
         <f ca="1">E163</f>
-        <v>8068.38</v>
+        <v>7893.41000000001</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -7514,7 +7540,7 @@
       <c r="A183" s="63"/>
       <c r="B183" s="64"/>
       <c r="C183" s="73" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D183" s="74"/>
       <c r="E183" s="87">
@@ -7529,7 +7555,7 @@
       <c r="A184" s="63"/>
       <c r="B184" s="64"/>
       <c r="C184" s="74" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D184" s="74"/>
       <c r="E184" s="87">
@@ -7617,7 +7643,7 @@
       <c r="D190" s="82"/>
       <c r="E190" s="92">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>8643.39</v>
+        <v>8468.42000000001</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -8144,7 +8170,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>10750.42</v>
+        <v>10575.45</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -8160,7 +8186,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>10828.64</v>
+        <v>10653.67</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -8176,7 +8202,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12">
         <f ca="1">C108</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -8822,7 +8848,7 @@
     <row r="51" ht="24.75" customHeight="1" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
-        <v>Birdie Sim Card</v>
+        <v>(SHIT COMPANY) Birdie Sim Card</v>
       </c>
       <c r="B51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65")))</f>
@@ -9493,7 +9519,7 @@
       </c>
       <c r="B88" s="36" t="str" cm="1">
         <f ca="1" t="array" ref="B88">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B102"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B102")))</f>
-        <v>Sportify Music Paid For 7th of Each Month</v>
+        <v>Sportify Music Paid For 7th of Each Month. Switch to Apple Music on the 8th of July 2025.</v>
       </c>
       <c r="C88" s="87">
         <v>68</v>
@@ -9675,7 +9701,7 @@
       </c>
       <c r="C98" s="37" cm="1">
         <f ca="1" t="array" ref="C98">INDIRECT("'"&amp;INDIRECT("Main!B30")&amp;"'!C98")+SUM(E118+E145+E172)</f>
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="D98" s="14"/>
       <c r="E98" s="96"/>
@@ -9755,7 +9781,7 @@
       </c>
       <c r="C102" s="37" cm="1">
         <f ca="1" t="array" ref="C102">INDIRECT("'"&amp;INDIRECT("Main!B30")&amp;"'!C102")+SUM(E122+E149+E176)</f>
-        <v>0</v>
+        <v>-326149.51</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
@@ -9795,7 +9821,7 @@
       </c>
       <c r="C104" s="37" cm="1">
         <f ca="1" t="array" ref="C104">INDIRECT("'"&amp;INDIRECT("Main!B30")&amp;"'!C104")+SUM(E124+E151+E178)</f>
-        <v>0</v>
+        <v>-676.03</v>
       </c>
       <c r="D104" s="14"/>
       <c r="E104" s="14"/>
@@ -9871,7 +9897,7 @@
       </c>
       <c r="C108" s="37">
         <f ca="1">SUM(C98:C107)</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -9887,7 +9913,7 @@
       </c>
       <c r="C109" s="37">
         <f ca="1">C108-C96</f>
-        <v>-369.99</v>
+        <v>-327495.53</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -9981,7 +10007,7 @@
       <c r="D116" s="58"/>
       <c r="E116" s="71" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B30")&amp;"'!E190")</f>
-        <v>8643.39</v>
+        <v>8468.42000000001</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -10150,7 +10176,7 @@
       <c r="A129" s="63"/>
       <c r="B129" s="64"/>
       <c r="C129" s="73" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D129" s="74"/>
       <c r="E129" s="87">
@@ -10253,7 +10279,7 @@
       <c r="D136" s="82"/>
       <c r="E136" s="89">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>9489.4</v>
+        <v>9314.43000000001</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -10345,7 +10371,7 @@
       <c r="D143" s="58"/>
       <c r="E143" s="89">
         <f ca="1">E136</f>
-        <v>9489.4</v>
+        <v>9314.43000000001</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -10514,7 +10540,7 @@
       <c r="A156" s="63"/>
       <c r="B156" s="64"/>
       <c r="C156" s="73" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D156" s="74"/>
       <c r="E156" s="87">
@@ -10529,7 +10555,7 @@
       <c r="A157" s="63"/>
       <c r="B157" s="64"/>
       <c r="C157" s="74" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D157" s="74"/>
       <c r="E157" s="87">
@@ -10617,7 +10643,7 @@
       <c r="D163" s="82"/>
       <c r="E163" s="92">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>9904.41</v>
+        <v>9729.44000000001</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -10709,7 +10735,7 @@
       <c r="D170" s="58"/>
       <c r="E170" s="92">
         <f ca="1">E163</f>
-        <v>9904.41</v>
+        <v>9729.44000000001</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -10878,7 +10904,7 @@
       <c r="A183" s="63"/>
       <c r="B183" s="64"/>
       <c r="C183" s="73" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D183" s="74"/>
       <c r="E183" s="87">
@@ -10981,7 +11007,7 @@
       <c r="D190" s="82"/>
       <c r="E190" s="92">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>10750.42</v>
+        <v>10575.45</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -11504,7 +11530,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>15050.42</v>
+        <v>14875.45</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -11520,7 +11546,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>15128.64</v>
+        <v>14953.67</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -11536,7 +11562,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12">
         <f ca="1">C108</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -12186,7 +12212,7 @@
     <row r="51" ht="24.75" customHeight="1" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
-        <v>Birdie Sim Card</v>
+        <v>(SHIT COMPANY) Birdie Sim Card</v>
       </c>
       <c r="B51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65")))</f>
@@ -12857,7 +12883,7 @@
       </c>
       <c r="B88" s="36" t="str" cm="1">
         <f ca="1" t="array" ref="B88">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B102"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B102")))</f>
-        <v>Sportify Music Paid For 7th of Each Month</v>
+        <v>Sportify Music Paid For 7th of Each Month. Switch to Apple Music on the 8th of July 2025.</v>
       </c>
       <c r="C88" s="87">
         <v>0</v>
@@ -13039,7 +13065,7 @@
       </c>
       <c r="C98" s="37" cm="1">
         <f ca="1" t="array" ref="C98">INDIRECT("'"&amp;INDIRECT("Main!B33")&amp;"'!C98")+SUM(E118+E145+E172)</f>
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="D98" s="14"/>
       <c r="E98" s="96"/>
@@ -13119,7 +13145,7 @@
       </c>
       <c r="C102" s="37" cm="1">
         <f ca="1" t="array" ref="C102">INDIRECT("'"&amp;INDIRECT("Main!B33")&amp;"'!C102")+SUM(E122+E149+E176)</f>
-        <v>0</v>
+        <v>-326149.51</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
@@ -13159,7 +13185,7 @@
       </c>
       <c r="C104" s="37" cm="1">
         <f ca="1" t="array" ref="C104">INDIRECT("'"&amp;INDIRECT("Main!B33")&amp;"'!C104")+SUM(E124+E151+E178)</f>
-        <v>0</v>
+        <v>-676.03</v>
       </c>
       <c r="D104" s="14"/>
       <c r="E104" s="14"/>
@@ -13235,7 +13261,7 @@
       </c>
       <c r="C108" s="37">
         <f ca="1">SUM(C98:C107)</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -13251,7 +13277,7 @@
       </c>
       <c r="C109" s="37">
         <f ca="1">C108-C96</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -13345,7 +13371,7 @@
       <c r="D116" s="58"/>
       <c r="E116" s="71" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B33")&amp;"'!E190")</f>
-        <v>10750.42</v>
+        <v>10575.45</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -13514,7 +13540,7 @@
       <c r="A129" s="63"/>
       <c r="B129" s="64"/>
       <c r="C129" s="73" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D129" s="74"/>
       <c r="E129" s="87">
@@ -13617,7 +13643,7 @@
       <c r="D136" s="82"/>
       <c r="E136" s="89">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>11966.42</v>
+        <v>11791.45</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -13709,7 +13735,7 @@
       <c r="D143" s="58"/>
       <c r="E143" s="89">
         <f ca="1">E136</f>
-        <v>11966.42</v>
+        <v>11791.45</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -13878,7 +13904,7 @@
       <c r="A156" s="63"/>
       <c r="B156" s="64"/>
       <c r="C156" s="73" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D156" s="74"/>
       <c r="E156" s="87">
@@ -13893,7 +13919,7 @@
       <c r="A157" s="63"/>
       <c r="B157" s="64"/>
       <c r="C157" s="74" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D157" s="74"/>
       <c r="E157" s="87">
@@ -13981,7 +14007,7 @@
       <c r="D163" s="82"/>
       <c r="E163" s="92">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>13834.42</v>
+        <v>13659.45</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -14073,7 +14099,7 @@
       <c r="D170" s="58"/>
       <c r="E170" s="92">
         <f ca="1">E163</f>
-        <v>13834.42</v>
+        <v>13659.45</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -14242,7 +14268,7 @@
       <c r="A183" s="63"/>
       <c r="B183" s="64"/>
       <c r="C183" s="73" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D183" s="74"/>
       <c r="E183" s="87">
@@ -14345,7 +14371,7 @@
       <c r="D190" s="82"/>
       <c r="E190" s="92">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>15050.42</v>
+        <v>14875.45</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -14866,7 +14892,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>16886.45</v>
+        <v>16711.48</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -14882,7 +14908,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>16964.67</v>
+        <v>16789.7</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -14898,7 +14924,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12">
         <f ca="1">C108</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -15544,7 +15570,7 @@
     <row r="51" ht="24.75" customHeight="1" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
-        <v>Birdie Sim Card</v>
+        <v>(SHIT COMPANY) Birdie Sim Card</v>
       </c>
       <c r="B51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65")))</f>
@@ -16215,7 +16241,7 @@
       </c>
       <c r="B88" s="36" t="str" cm="1">
         <f ca="1" t="array" ref="B88">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B102"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B102")))</f>
-        <v>Sportify Music Paid For 7th of Each Month</v>
+        <v>Sportify Music Paid For 7th of Each Month. Switch to Apple Music on the 8th of July 2025.</v>
       </c>
       <c r="C88" s="87">
         <v>68</v>
@@ -16397,7 +16423,7 @@
       </c>
       <c r="C98" s="37" cm="1">
         <f ca="1" t="array" ref="C98">INDIRECT("'"&amp;INDIRECT("Main!B36")&amp;"'!C98")+SUM(E118+E145+E172)</f>
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="D98" s="14"/>
       <c r="E98" s="96"/>
@@ -16477,7 +16503,7 @@
       </c>
       <c r="C102" s="37" cm="1">
         <f ca="1" t="array" ref="C102">INDIRECT("'"&amp;INDIRECT("Main!B36")&amp;"'!C102")+SUM(E122+E149+E176)</f>
-        <v>0</v>
+        <v>-326149.51</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
@@ -16517,7 +16543,7 @@
       </c>
       <c r="C104" s="37" cm="1">
         <f ca="1" t="array" ref="C104">INDIRECT("'"&amp;INDIRECT("Main!B36")&amp;"'!C104")+SUM(E124+E151+E178)</f>
-        <v>0</v>
+        <v>-676.03</v>
       </c>
       <c r="D104" s="14"/>
       <c r="E104" s="14"/>
@@ -16593,7 +16619,7 @@
       </c>
       <c r="C108" s="37">
         <f ca="1">SUM(C98:C107)</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -16609,7 +16635,7 @@
       </c>
       <c r="C109" s="37">
         <f ca="1">C108-C96</f>
-        <v>-369.99</v>
+        <v>-327495.53</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -16703,7 +16729,7 @@
       <c r="D116" s="58"/>
       <c r="E116" s="71" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B36")&amp;"'!E190")</f>
-        <v>15050.42</v>
+        <v>14875.45</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -16872,7 +16898,7 @@
       <c r="A129" s="63"/>
       <c r="B129" s="64"/>
       <c r="C129" s="73" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D129" s="74"/>
       <c r="E129" s="87">
@@ -16887,7 +16913,7 @@
       <c r="A130" s="63"/>
       <c r="B130" s="64"/>
       <c r="C130" s="74" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D130" s="74"/>
       <c r="E130" s="87">
@@ -16975,7 +17001,7 @@
       <c r="D136" s="82"/>
       <c r="E136" s="89">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>15625.43</v>
+        <v>15450.46</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -17067,7 +17093,7 @@
       <c r="D143" s="58"/>
       <c r="E143" s="89">
         <f ca="1">E136</f>
-        <v>15625.43</v>
+        <v>15450.46</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -17236,7 +17262,7 @@
       <c r="A156" s="63"/>
       <c r="B156" s="64"/>
       <c r="C156" s="73" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D156" s="74"/>
       <c r="E156" s="87">
@@ -17339,7 +17365,7 @@
       <c r="D163" s="82"/>
       <c r="E163" s="92">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>16311.44</v>
+        <v>16136.47</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -17431,7 +17457,7 @@
       <c r="D170" s="58"/>
       <c r="E170" s="92">
         <f ca="1">E163</f>
-        <v>16311.44</v>
+        <v>16136.47</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -17600,7 +17626,7 @@
       <c r="A183" s="63"/>
       <c r="B183" s="64"/>
       <c r="C183" s="73" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D183" s="74"/>
       <c r="E183" s="87">
@@ -17615,7 +17641,7 @@
       <c r="A184" s="63"/>
       <c r="B184" s="64"/>
       <c r="C184" s="74" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D184" s="74"/>
       <c r="E184" s="87">
@@ -17703,7 +17729,7 @@
       <c r="D190" s="82"/>
       <c r="E190" s="92">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>16886.45</v>
+        <v>16711.48</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -18231,7 +18257,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>18993.48</v>
+        <v>18818.51</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -18247,7 +18273,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>19071.7</v>
+        <v>18896.73</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -18263,7 +18289,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12">
         <f ca="1">C108</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -18909,7 +18935,7 @@
     <row r="51" ht="24.75" customHeight="1" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
-        <v>Birdie Sim Card</v>
+        <v>(SHIT COMPANY) Birdie Sim Card</v>
       </c>
       <c r="B51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65")))</f>
@@ -19580,7 +19606,7 @@
       </c>
       <c r="B88" s="36" t="str" cm="1">
         <f ca="1" t="array" ref="B88">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B102"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B102")))</f>
-        <v>Sportify Music Paid For 7th of Each Month</v>
+        <v>Sportify Music Paid For 7th of Each Month. Switch to Apple Music on the 8th of July 2025.</v>
       </c>
       <c r="C88" s="87">
         <v>68</v>
@@ -19762,7 +19788,7 @@
       </c>
       <c r="C98" s="37" cm="1">
         <f ca="1" t="array" ref="C98">INDIRECT("'"&amp;INDIRECT("Main!B39")&amp;"'!C98")+SUM(E118+E145+E172)</f>
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="D98" s="14"/>
       <c r="E98" s="96"/>
@@ -19842,7 +19868,7 @@
       </c>
       <c r="C102" s="37" cm="1">
         <f ca="1" t="array" ref="C102">INDIRECT("'"&amp;INDIRECT("Main!B39")&amp;"'!C102")+SUM(E122+E149+E176)</f>
-        <v>0</v>
+        <v>-326149.51</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
@@ -19882,7 +19908,7 @@
       </c>
       <c r="C104" s="37" cm="1">
         <f ca="1" t="array" ref="C104">INDIRECT("'"&amp;INDIRECT("Main!B39")&amp;"'!C104")+SUM(E124+E151+E178)</f>
-        <v>0</v>
+        <v>-676.03</v>
       </c>
       <c r="D104" s="14"/>
       <c r="E104" s="14"/>
@@ -19958,7 +19984,7 @@
       </c>
       <c r="C108" s="37">
         <f ca="1">SUM(C98:C107)</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -19974,7 +20000,7 @@
       </c>
       <c r="C109" s="37">
         <f ca="1">C108-C96</f>
-        <v>-369.99</v>
+        <v>-327495.53</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -20068,7 +20094,7 @@
       <c r="D116" s="58"/>
       <c r="E116" s="71" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B39")&amp;"'!E190")</f>
-        <v>16886.45</v>
+        <v>16711.48</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -20237,7 +20263,7 @@
       <c r="A129" s="63"/>
       <c r="B129" s="64"/>
       <c r="C129" s="73" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D129" s="74"/>
       <c r="E129" s="87">
@@ -20340,7 +20366,7 @@
       <c r="D136" s="82"/>
       <c r="E136" s="89">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>17732.46</v>
+        <v>17557.49</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -20432,7 +20458,7 @@
       <c r="D143" s="58"/>
       <c r="E143" s="89">
         <f ca="1">E136</f>
-        <v>17732.46</v>
+        <v>17557.49</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -20601,7 +20627,7 @@
       <c r="A156" s="63"/>
       <c r="B156" s="64"/>
       <c r="C156" s="73" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D156" s="74"/>
       <c r="E156" s="87">
@@ -20616,7 +20642,7 @@
       <c r="A157" s="63"/>
       <c r="B157" s="64"/>
       <c r="C157" s="74" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D157" s="74"/>
       <c r="E157" s="87">
@@ -20704,7 +20730,7 @@
       <c r="D163" s="82"/>
       <c r="E163" s="92">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>18147.47</v>
+        <v>17972.5</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -20796,7 +20822,7 @@
       <c r="D170" s="58"/>
       <c r="E170" s="92">
         <f ca="1">E163</f>
-        <v>18147.47</v>
+        <v>17972.5</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -20965,7 +20991,7 @@
       <c r="A183" s="63"/>
       <c r="B183" s="64"/>
       <c r="C183" s="73" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D183" s="74"/>
       <c r="E183" s="87">
@@ -21068,7 +21094,7 @@
       <c r="D190" s="82"/>
       <c r="E190" s="92">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>18993.48</v>
+        <v>18818.51</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -21589,7 +21615,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>20919.51</v>
+        <v>20744.54</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -21605,7 +21631,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>20997.73</v>
+        <v>20822.76</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -21621,7 +21647,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12">
         <f ca="1">C108</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -22267,7 +22293,7 @@
     <row r="51" ht="24.75" customHeight="1" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
-        <v>Birdie Sim Card</v>
+        <v>(SHIT COMPANY) Birdie Sim Card</v>
       </c>
       <c r="B51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65")))</f>
@@ -22938,7 +22964,7 @@
       </c>
       <c r="B88" s="36" t="str" cm="1">
         <f ca="1" t="array" ref="B88">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B102"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B102")))</f>
-        <v>Sportify Music Paid For 7th of Each Month</v>
+        <v>Sportify Music Paid For 7th of Each Month. Switch to Apple Music on the 8th of July 2025.</v>
       </c>
       <c r="C88" s="87">
         <v>68</v>
@@ -23120,7 +23146,7 @@
       </c>
       <c r="C98" s="37" cm="1">
         <f ca="1" t="array" ref="C98">INDIRECT("'"&amp;INDIRECT("Main!B42")&amp;"'!C98")+SUM(E118+E145+E172)</f>
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="D98" s="14"/>
       <c r="E98" s="96"/>
@@ -23200,7 +23226,7 @@
       </c>
       <c r="C102" s="37" cm="1">
         <f ca="1" t="array" ref="C102">INDIRECT("'"&amp;INDIRECT("Main!B42")&amp;"'!C102")+SUM(E122+E149+E176)</f>
-        <v>0</v>
+        <v>-326149.51</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
@@ -23240,7 +23266,7 @@
       </c>
       <c r="C104" s="37" cm="1">
         <f ca="1" t="array" ref="C104">INDIRECT("'"&amp;INDIRECT("Main!B42")&amp;"'!C104")+SUM(E124+E151+E178)</f>
-        <v>0</v>
+        <v>-676.03</v>
       </c>
       <c r="D104" s="14"/>
       <c r="E104" s="14"/>
@@ -23316,7 +23342,7 @@
       </c>
       <c r="C108" s="37">
         <f ca="1">SUM(C98:C107)</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -23332,7 +23358,7 @@
       </c>
       <c r="C109" s="37">
         <f ca="1">C108-C96</f>
-        <v>-369.99</v>
+        <v>-327495.53</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -23426,7 +23452,7 @@
       <c r="D116" s="58"/>
       <c r="E116" s="71" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B42")&amp;"'!E190")</f>
-        <v>18993.48</v>
+        <v>18818.51</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -23595,7 +23621,7 @@
       <c r="A129" s="63"/>
       <c r="B129" s="64"/>
       <c r="C129" s="73" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D129" s="74"/>
       <c r="E129" s="87">
@@ -23610,7 +23636,7 @@
       <c r="A130" s="63"/>
       <c r="B130" s="64"/>
       <c r="C130" s="74" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D130" s="74"/>
       <c r="E130" s="87">
@@ -23698,7 +23724,7 @@
       <c r="D136" s="82"/>
       <c r="E136" s="89">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>19618.49</v>
+        <v>19443.52</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -23790,7 +23816,7 @@
       <c r="D143" s="58"/>
       <c r="E143" s="89">
         <f ca="1">E136</f>
-        <v>19618.49</v>
+        <v>19443.52</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -23959,7 +23985,7 @@
       <c r="A156" s="63"/>
       <c r="B156" s="64"/>
       <c r="C156" s="73" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D156" s="74"/>
       <c r="E156" s="87">
@@ -24062,7 +24088,7 @@
       <c r="D163" s="82"/>
       <c r="E163" s="92">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>20304.5</v>
+        <v>20129.53</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -24154,7 +24180,7 @@
       <c r="D170" s="58"/>
       <c r="E170" s="92">
         <f ca="1">E163</f>
-        <v>20304.5</v>
+        <v>20129.53</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -24323,7 +24349,7 @@
       <c r="A183" s="63"/>
       <c r="B183" s="64"/>
       <c r="C183" s="73" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D183" s="74"/>
       <c r="E183" s="87">
@@ -24338,7 +24364,7 @@
       <c r="A184" s="63"/>
       <c r="B184" s="64"/>
       <c r="C184" s="74" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D184" s="74"/>
       <c r="E184" s="87">
@@ -24426,7 +24452,7 @@
       <c r="D190" s="82"/>
       <c r="E190" s="92">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>20919.51</v>
+        <v>20744.54</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -24953,7 +24979,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>24109.54</v>
+        <v>23934.57</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -24969,7 +24995,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>24187.76</v>
+        <v>24012.79</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -24985,7 +25011,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12">
         <f ca="1">C108</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -25635,7 +25661,7 @@
     <row r="51" ht="24.75" customHeight="1" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
-        <v>Birdie Sim Card</v>
+        <v>(SHIT COMPANY) Birdie Sim Card</v>
       </c>
       <c r="B51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65")))</f>
@@ -26306,7 +26332,7 @@
       </c>
       <c r="B88" s="36" t="str" cm="1">
         <f ca="1" t="array" ref="B88">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B102"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B102")))</f>
-        <v>Sportify Music Paid For 7th of Each Month</v>
+        <v>Sportify Music Paid For 7th of Each Month. Switch to Apple Music on the 8th of July 2025.</v>
       </c>
       <c r="C88" s="37">
         <v>68</v>
@@ -26488,7 +26514,7 @@
       </c>
       <c r="C98" s="37" cm="1">
         <f ca="1" t="array" ref="C98">INDIRECT("'"&amp;INDIRECT("Main!B45")&amp;"'!C98")+SUM(E118+E145+E172)</f>
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="D98" s="14"/>
       <c r="E98" s="96"/>
@@ -26568,7 +26594,7 @@
       </c>
       <c r="C102" s="37" cm="1">
         <f ca="1" t="array" ref="C102">INDIRECT("'"&amp;INDIRECT("Main!B45")&amp;"'!C102")+SUM(E122+E149+E176)</f>
-        <v>0</v>
+        <v>-326149.51</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
@@ -26608,7 +26634,7 @@
       </c>
       <c r="C104" s="37" cm="1">
         <f ca="1" t="array" ref="C104">INDIRECT("'"&amp;INDIRECT("Main!B45")&amp;"'!C104")+SUM(E124+E151+E178)</f>
-        <v>0</v>
+        <v>-676.03</v>
       </c>
       <c r="D104" s="14"/>
       <c r="E104" s="14"/>
@@ -26684,7 +26710,7 @@
       </c>
       <c r="C108" s="37">
         <f ca="1">SUM(C98:C107)</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -26700,7 +26726,7 @@
       </c>
       <c r="C109" s="37">
         <f ca="1">C108-C96</f>
-        <v>-369.99</v>
+        <v>-327495.53</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -26794,7 +26820,7 @@
       <c r="D116" s="58"/>
       <c r="E116" s="71" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B45")&amp;"'!E190")</f>
-        <v>20919.51</v>
+        <v>20744.54</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -26963,7 +26989,7 @@
       <c r="A129" s="63"/>
       <c r="B129" s="64"/>
       <c r="C129" s="73" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D129" s="74"/>
       <c r="E129" s="87">
@@ -27066,7 +27092,7 @@
       <c r="D136" s="82"/>
       <c r="E136" s="89">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>21765.52</v>
+        <v>21590.55</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -27158,7 +27184,7 @@
       <c r="D143" s="58"/>
       <c r="E143" s="89">
         <f ca="1">E136</f>
-        <v>21765.52</v>
+        <v>21590.55</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -27327,7 +27353,7 @@
       <c r="A156" s="63"/>
       <c r="B156" s="64"/>
       <c r="C156" s="73" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D156" s="74"/>
       <c r="E156" s="87">
@@ -27342,7 +27368,7 @@
       <c r="A157" s="63"/>
       <c r="B157" s="64"/>
       <c r="C157" s="74" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D157" s="74"/>
       <c r="E157" s="87">
@@ -27430,7 +27456,7 @@
       <c r="D163" s="82"/>
       <c r="E163" s="92">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>23263.53</v>
+        <v>23088.56</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -27522,7 +27548,7 @@
       <c r="D170" s="58"/>
       <c r="E170" s="92">
         <f ca="1">E163</f>
-        <v>23263.53</v>
+        <v>23088.56</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -27691,7 +27717,7 @@
       <c r="A183" s="63"/>
       <c r="B183" s="64"/>
       <c r="C183" s="73" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D183" s="74"/>
       <c r="E183" s="87">
@@ -27794,7 +27820,7 @@
       <c r="D190" s="82"/>
       <c r="E190" s="92">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>24109.54</v>
+        <v>23934.57</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -28302,7 +28328,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>25995.57</v>
+        <v>25820.6</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -28318,7 +28344,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>26073.79</v>
+        <v>25898.82</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -28334,7 +28360,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12">
         <f ca="1">C108</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -28980,7 +29006,7 @@
     <row r="51" ht="24.75" customHeight="1" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
-        <v>Birdie Sim Card</v>
+        <v>(SHIT COMPANY) Birdie Sim Card</v>
       </c>
       <c r="B51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65")))</f>
@@ -29651,7 +29677,7 @@
       </c>
       <c r="B88" s="36" t="str" cm="1">
         <f ca="1" t="array" ref="B88">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B102"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B102")))</f>
-        <v>Sportify Music Paid For 7th of Each Month</v>
+        <v>Sportify Music Paid For 7th of Each Month. Switch to Apple Music on the 8th of July 2025.</v>
       </c>
       <c r="C88" s="37">
         <v>68</v>
@@ -29833,7 +29859,7 @@
       </c>
       <c r="C98" s="37" cm="1">
         <f ca="1" t="array" ref="C98">INDIRECT("'"&amp;INDIRECT("Main!B48")&amp;"'!C98")+SUM(E118+E145+E172)</f>
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="D98" s="14"/>
       <c r="E98" s="96"/>
@@ -29908,11 +29934,11 @@
         <v>Bankruptcy Department / Bank</v>
       </c>
       <c r="B102" s="38" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C102" s="37" cm="1">
         <f ca="1" t="array" ref="C102">INDIRECT("'"&amp;INDIRECT("Main!B48")&amp;"'!C102")+SUM(E122+E149+E176)</f>
-        <v>0</v>
+        <v>-326149.51</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
@@ -29952,7 +29978,7 @@
       </c>
       <c r="C104" s="37" cm="1">
         <f ca="1" t="array" ref="C104">INDIRECT("'"&amp;INDIRECT("Main!B48")&amp;"'!C104")+SUM(E124+E151+E178)</f>
-        <v>0</v>
+        <v>-676.03</v>
       </c>
       <c r="D104" s="14"/>
       <c r="E104" s="14"/>
@@ -30028,7 +30054,7 @@
       </c>
       <c r="C108" s="37">
         <f ca="1">SUM(C98:C107)</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -30044,7 +30070,7 @@
       </c>
       <c r="C109" s="37">
         <f ca="1">C108-C96</f>
-        <v>-369.99</v>
+        <v>-327495.53</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -30138,7 +30164,7 @@
       <c r="D116" s="58"/>
       <c r="E116" s="71" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B48")&amp;"'!E190")</f>
-        <v>24109.54</v>
+        <v>23934.57</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -30307,7 +30333,7 @@
       <c r="A129" s="63"/>
       <c r="B129" s="64"/>
       <c r="C129" s="73" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D129" s="74"/>
       <c r="E129" s="87">
@@ -30322,7 +30348,7 @@
       <c r="A130" s="63"/>
       <c r="B130" s="64"/>
       <c r="C130" s="74" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D130" s="74"/>
       <c r="E130" s="87">
@@ -30410,7 +30436,7 @@
       <c r="D136" s="82"/>
       <c r="E136" s="89">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>24734.55</v>
+        <v>24559.58</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -30502,7 +30528,7 @@
       <c r="D143" s="58"/>
       <c r="E143" s="89">
         <f ca="1">E136</f>
-        <v>24734.55</v>
+        <v>24559.58</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -30671,7 +30697,7 @@
       <c r="A156" s="63"/>
       <c r="B156" s="64"/>
       <c r="C156" s="73" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D156" s="74"/>
       <c r="E156" s="87">
@@ -30774,7 +30800,7 @@
       <c r="D163" s="82"/>
       <c r="E163" s="92">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>25420.56</v>
+        <v>25245.59</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -30866,7 +30892,7 @@
       <c r="D170" s="58"/>
       <c r="E170" s="92">
         <f ca="1">E163</f>
-        <v>25420.56</v>
+        <v>25245.59</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -31035,7 +31061,7 @@
       <c r="A183" s="63"/>
       <c r="B183" s="64"/>
       <c r="C183" s="73" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D183" s="74"/>
       <c r="E183" s="87">
@@ -31050,7 +31076,7 @@
       <c r="A184" s="63"/>
       <c r="B184" s="64"/>
       <c r="C184" s="74" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D184" s="74"/>
       <c r="E184" s="87">
@@ -31138,7 +31164,7 @@
       <c r="D190" s="82"/>
       <c r="E190" s="92">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>25995.57</v>
+        <v>25820.6</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -31653,7 +31679,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>28102.6</v>
+        <v>27927.63</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -31669,7 +31695,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>28180.82</v>
+        <v>28005.85</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -31685,7 +31711,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12">
         <f ca="1">C108</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -32331,7 +32357,7 @@
     <row r="51" ht="24.75" customHeight="1" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
-        <v>Birdie Sim Card</v>
+        <v>(SHIT COMPANY) Birdie Sim Card</v>
       </c>
       <c r="B51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65")))</f>
@@ -33002,7 +33028,7 @@
       </c>
       <c r="B88" s="36" t="str" cm="1">
         <f ca="1" t="array" ref="B88">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B102"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B102")))</f>
-        <v>Sportify Music Paid For 7th of Each Month</v>
+        <v>Sportify Music Paid For 7th of Each Month. Switch to Apple Music on the 8th of July 2025.</v>
       </c>
       <c r="C88" s="37">
         <v>68</v>
@@ -33184,7 +33210,7 @@
       </c>
       <c r="C98" s="37" cm="1">
         <f ca="1" t="array" ref="C98">INDIRECT("'"&amp;INDIRECT("Main!B51")&amp;"'!C98")+SUM(E118+E145+E172)</f>
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="D98" s="14"/>
       <c r="E98" s="69"/>
@@ -33264,7 +33290,7 @@
       </c>
       <c r="C102" s="37" cm="1">
         <f ca="1" t="array" ref="C102">INDIRECT("'"&amp;INDIRECT("Main!B51")&amp;"'!C102")+SUM(E122+E149+E176)</f>
-        <v>0</v>
+        <v>-326149.51</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
@@ -33304,7 +33330,7 @@
       </c>
       <c r="C104" s="37" cm="1">
         <f ca="1" t="array" ref="C104">INDIRECT("'"&amp;INDIRECT("Main!B51")&amp;"'!C104")+SUM(E124+E151+E178)</f>
-        <v>0</v>
+        <v>-676.03</v>
       </c>
       <c r="D104" s="14"/>
       <c r="E104" s="14"/>
@@ -33380,7 +33406,7 @@
       </c>
       <c r="C108" s="37">
         <f ca="1">SUM(C98:C107)</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -33396,7 +33422,7 @@
       </c>
       <c r="C109" s="37">
         <f ca="1">C108-C96</f>
-        <v>-369.99</v>
+        <v>-327495.53</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -33490,7 +33516,7 @@
       <c r="D116" s="58"/>
       <c r="E116" s="71" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B51")&amp;"'!E190")</f>
-        <v>25995.57</v>
+        <v>25820.6</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -33659,7 +33685,7 @@
       <c r="A129" s="63"/>
       <c r="B129" s="64"/>
       <c r="C129" s="73" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D129" s="74"/>
       <c r="E129" s="87">
@@ -33762,7 +33788,7 @@
       <c r="D136" s="82"/>
       <c r="E136" s="89">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>26841.58</v>
+        <v>26666.61</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -33854,7 +33880,7 @@
       <c r="D143" s="58"/>
       <c r="E143" s="89">
         <f ca="1">E136</f>
-        <v>26841.58</v>
+        <v>26666.61</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -34023,7 +34049,7 @@
       <c r="A156" s="63"/>
       <c r="B156" s="64"/>
       <c r="C156" s="73" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D156" s="74"/>
       <c r="E156" s="87">
@@ -34038,7 +34064,7 @@
       <c r="A157" s="63"/>
       <c r="B157" s="64"/>
       <c r="C157" s="74" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D157" s="74"/>
       <c r="E157" s="87">
@@ -34126,7 +34152,7 @@
       <c r="D163" s="82"/>
       <c r="E163" s="92">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>27256.59</v>
+        <v>27081.62</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -34218,7 +34244,7 @@
       <c r="D170" s="58"/>
       <c r="E170" s="92">
         <f ca="1">E163</f>
-        <v>27256.59</v>
+        <v>27081.62</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -34387,7 +34413,7 @@
       <c r="A183" s="63"/>
       <c r="B183" s="64"/>
       <c r="C183" s="73" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D183" s="74"/>
       <c r="E183" s="87">
@@ -34490,7 +34516,7 @@
       <c r="D190" s="82"/>
       <c r="E190" s="92">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>28102.6</v>
+        <v>27927.63</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -34949,433 +34975,433 @@
   <dimension ref="A1:B134"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="43.25" style="222" customWidth="1"/>
-    <col min="2" max="2" width="34.125" style="222" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="222"/>
+    <col min="1" max="1" width="43.25" style="223" customWidth="1"/>
+    <col min="2" max="2" width="34.125" style="223" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="223"/>
   </cols>
   <sheetData>
     <row r="1" ht="45" customHeight="1" spans="1:2">
-      <c r="A1" s="223" t="s">
+      <c r="A1" s="224" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="224" t="s">
+      <c r="B1" s="225" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:2">
-      <c r="A2" s="225" t="s">
+      <c r="A2" s="226" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="226" t="b">
+      <c r="B2" s="227" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:2">
-      <c r="A3" s="227" t="s">
+      <c r="A3" s="228" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="228">
+      <c r="B3" s="229">
         <v>45677</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1" spans="1:2">
-      <c r="A4" s="223" t="s">
+      <c r="A4" s="224" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="229" t="str">
+      <c r="B4" s="230" t="str">
         <f>IF(B2,TEXT(EDATE(B3,1)-1,"dd-mmm-yyyy"),TEXT(EDATE(B3,1)-1,"dd-mmm-yyyy"))</f>
         <v>19-Feb-2025</v>
       </c>
     </row>
     <row r="5" ht="45" customHeight="1" spans="1:2">
-      <c r="A5" s="225" t="s">
+      <c r="A5" s="226" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="230">
+      <c r="B5" s="231">
         <v>45777</v>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1" spans="1:2">
-      <c r="A6" s="225"/>
-      <c r="B6" s="230"/>
+      <c r="A6" s="226"/>
+      <c r="B6" s="231"/>
     </row>
     <row r="7" ht="24.75" customHeight="1" spans="1:2">
-      <c r="A7" s="231"/>
-      <c r="B7" s="232"/>
+      <c r="A7" s="232"/>
+      <c r="B7" s="233"/>
     </row>
     <row r="8" ht="39.95" customHeight="1" spans="1:2">
-      <c r="A8" s="233" t="s">
+      <c r="A8" s="234" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="233"/>
+      <c r="B8" s="234"/>
     </row>
     <row r="9" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A9" s="234" t="str">
+      <c r="A9" s="235" t="str">
         <f>TEXT(B3,"dd mmmm yyyy")&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,1)-1,"dd mmmm yyyy"),TEXT(B3+B5-B3,"dd mmmm yyyy"))</f>
         <v>20 January 2025 - 19 February 2025</v>
       </c>
-      <c r="B9" s="235" t="s">
+      <c r="B9" s="236" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A10" s="226" t="str">
+      <c r="A10" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,1),"dd mmmm yyyy"),TEXT(B3+(B5-B3)+1,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,2)-1,"dd mmmm yyyy"),TEXT(B3+(B5-B3)*2+1,"dd mmmm yyyy"))</f>
         <v>20 February 2025 - 19 March 2025</v>
       </c>
-      <c r="B10" s="235"/>
+      <c r="B10" s="236"/>
     </row>
     <row r="11" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A11" s="226" t="str">
+      <c r="A11" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,2),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*2)+2,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,3)-1,"dd mmmm yyyy"),TEXT(B3+((B5-B3)*3+2),"dd mmmm yyyy"))</f>
         <v>20 March 2025 - 19 April 2025</v>
       </c>
-      <c r="B11" s="236"/>
+      <c r="B11" s="237"/>
     </row>
     <row r="12" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A12" s="237" t="str">
+      <c r="A12" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,3),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*3)+3,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,4)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*4)+3),"dd mmmm yyyy"))</f>
         <v>20 April 2025 - 19 May 2025</v>
       </c>
-      <c r="B12" s="224" t="s">
+      <c r="B12" s="225" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A13" s="237" t="str">
+      <c r="A13" s="238" t="str">
         <f>IF(B2,TEXT(EDATE(B3,4),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*4)+4,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,5)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*5)+4),"dd mmmm yyyy"))</f>
         <v>20 May 2025 - 19 June 2025</v>
       </c>
-      <c r="B13" s="238"/>
+      <c r="B13" s="239"/>
     </row>
     <row r="14" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A14" s="226" t="str">
+      <c r="A14" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,5),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*5)+5,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,6)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*6)+5),"dd mmmm yyyy"))</f>
         <v>20 June 2025 - 19 July 2025</v>
       </c>
-      <c r="B14" s="239"/>
+      <c r="B14" s="240"/>
     </row>
     <row r="15" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A15" s="226" t="str">
+      <c r="A15" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,6),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*6)+6,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,7)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*7)+6),"dd mmmm yyyy"))</f>
         <v>20 July 2025 - 19 August 2025</v>
       </c>
-      <c r="B15" s="224" t="s">
+      <c r="B15" s="225" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A16" s="226" t="str">
+      <c r="A16" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,7),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*7)+7,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,8)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*8)+7),"dd mmmm yyyy"))</f>
         <v>20 August 2025 - 19 September 2025</v>
       </c>
-      <c r="B16" s="238"/>
+      <c r="B16" s="239"/>
     </row>
     <row r="17" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A17" s="226" t="str">
+      <c r="A17" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,8),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*8)+8,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,9)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*9)+8),"dd mmmm yyyy"))</f>
         <v>20 September 2025 - 19 October 2025</v>
       </c>
-      <c r="B17" s="239"/>
+      <c r="B17" s="240"/>
     </row>
     <row r="18" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A18" s="226" t="str">
+      <c r="A18" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,9),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*9)+9,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,10)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*10)+9),"dd mmmm yyyy"))</f>
         <v>20 October 2025 - 19 November 2025</v>
       </c>
-      <c r="B18" s="224" t="s">
+      <c r="B18" s="225" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="19" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A19" s="226" t="str">
+      <c r="A19" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,10),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*10)+10,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,11)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*11)+10),"dd mmmm yyyy"))</f>
         <v>20 November 2025 - 19 December 2025</v>
       </c>
-      <c r="B19" s="238"/>
+      <c r="B19" s="239"/>
     </row>
     <row r="20" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A20" s="240" t="str">
+      <c r="A20" s="241" t="str">
         <f>IF(B2,TEXT(EDATE(B3,11),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*11)+11,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,12)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*12)+11),"dd mmmm yyyy"))</f>
         <v>20 December 2025 - 19 January 2026</v>
       </c>
-      <c r="B20" s="239"/>
+      <c r="B20" s="240"/>
     </row>
     <row r="21" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A21" s="241" t="str">
+      <c r="A21" s="242" t="str">
         <f>IF(B2,TEXT(EDATE(B3,12),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*12)+12,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,13)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*13)+12),"dd mmmm yyyy"))</f>
         <v>20 January 2026 - 19 February 2026</v>
       </c>
-      <c r="B21" s="226" t="s">
+      <c r="B21" s="227" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="22" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A22" s="241" t="str">
+      <c r="A22" s="242" t="str">
         <f>IF(B2,TEXT(EDATE(B3,13),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*13)+13,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,14)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*14)+13),"dd mmmm yyyy"))</f>
         <v>20 February 2026 - 19 March 2026</v>
       </c>
-      <c r="B22" s="226"/>
+      <c r="B22" s="227"/>
     </row>
     <row r="23" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A23" s="240" t="str">
+      <c r="A23" s="241" t="str">
         <f>IF(B2,TEXT(EDATE(B3,14),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*14)+14,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,15)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*15)+14),"dd mmmm yyyy"))</f>
         <v>20 March 2026 - 19 April 2026</v>
       </c>
-      <c r="B23" s="224"/>
+      <c r="B23" s="225"/>
     </row>
     <row r="24" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A24" s="226" t="str">
+      <c r="A24" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,15),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*15)+15,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,16)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*16)+15),"dd mmmm yyyy"))</f>
         <v>20 April 2026 - 19 May 2026</v>
       </c>
-      <c r="B24" s="226" t="s">
+      <c r="B24" s="227" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="25" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A25" s="226" t="str">
+      <c r="A25" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,16),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*16)+16,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,17)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*17)+16),"dd mmmm yyyy"))</f>
         <v>20 May 2026 - 19 June 2026</v>
       </c>
-      <c r="B25" s="226"/>
+      <c r="B25" s="227"/>
     </row>
     <row r="26" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A26" s="224" t="str">
+      <c r="A26" s="225" t="str">
         <f>IF(B2,TEXT(EDATE(B3,17),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*17)+17,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,18)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*18)+17),"dd mmmm yyyy"))</f>
         <v>20 June 2026 - 19 July 2026</v>
       </c>
-      <c r="B26" s="224"/>
+      <c r="B26" s="225"/>
     </row>
     <row r="27" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A27" s="226" t="str">
+      <c r="A27" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,18),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*18)+18,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,19)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*19)+18),"dd mmmm yyyy"))</f>
         <v>20 July 2026 - 19 August 2026</v>
       </c>
-      <c r="B27" s="226" t="s">
+      <c r="B27" s="227" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="28" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A28" s="226" t="str">
+      <c r="A28" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,19),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*19)+19,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,20)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*20)+19),"dd mmmm yyyy"))</f>
         <v>20 August 2026 - 19 September 2026</v>
       </c>
-      <c r="B28" s="226"/>
+      <c r="B28" s="227"/>
     </row>
     <row r="29" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A29" s="224" t="str">
+      <c r="A29" s="225" t="str">
         <f>IF(B2,TEXT(EDATE(B3,20),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*20)+20,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,21)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*21)+20),"dd mmmm yyyy"))</f>
         <v>20 September 2026 - 19 October 2026</v>
       </c>
-      <c r="B29" s="224"/>
+      <c r="B29" s="225"/>
     </row>
     <row r="30" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A30" s="226" t="str">
+      <c r="A30" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,21),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*21)+21,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,22)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*22)+21),"dd mmmm yyyy"))</f>
         <v>20 October 2026 - 19 November 2026</v>
       </c>
-      <c r="B30" s="226" t="s">
+      <c r="B30" s="227" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="31" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A31" s="226" t="str">
+      <c r="A31" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,22),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*22)+22,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,23)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*23)+22),"dd mmmm yyyy"))</f>
         <v>20 November 2026 - 19 December 2026</v>
       </c>
-      <c r="B31" s="226"/>
+      <c r="B31" s="227"/>
     </row>
     <row r="32" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A32" s="224" t="str">
+      <c r="A32" s="225" t="str">
         <f>IF(B2,TEXT(EDATE(B3,23),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*23)+23,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,24)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*24)+23),"dd mmmm yyyy"))</f>
         <v>20 December 2026 - 19 January 2027</v>
       </c>
-      <c r="B32" s="224"/>
+      <c r="B32" s="225"/>
     </row>
     <row r="33" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A33" s="226" t="str">
+      <c r="A33" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,24),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*24)+24,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,25)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*25)+24),"dd mmmm yyyy"))</f>
         <v>20 January 2027 - 19 February 2027</v>
       </c>
-      <c r="B33" s="226" t="s">
+      <c r="B33" s="227" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="34" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A34" s="226" t="str">
+      <c r="A34" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,25),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*25)+25,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,26)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*26)+25),"dd mmmm yyyy"))</f>
         <v>20 February 2027 - 19 March 2027</v>
       </c>
-      <c r="B34" s="226"/>
+      <c r="B34" s="227"/>
     </row>
     <row r="35" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A35" s="224" t="str">
+      <c r="A35" s="225" t="str">
         <f>IF(B2,TEXT(EDATE(B3,26),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*26)+26,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,27)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*27)+26),"dd mmmm yyyy"))</f>
         <v>20 March 2027 - 19 April 2027</v>
       </c>
-      <c r="B35" s="224"/>
+      <c r="B35" s="225"/>
     </row>
     <row r="36" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A36" s="226" t="str">
+      <c r="A36" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,27),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*27)+27,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,28)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*28)+27),"dd mmmm yyyy"))</f>
         <v>20 April 2027 - 19 May 2027</v>
       </c>
-      <c r="B36" s="226" t="s">
+      <c r="B36" s="227" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="37" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A37" s="226" t="str">
+      <c r="A37" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,28),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*28)+28,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,29)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*29)+28),"dd mmmm yyyy"))</f>
         <v>20 May 2027 - 19 June 2027</v>
       </c>
-      <c r="B37" s="226"/>
+      <c r="B37" s="227"/>
     </row>
     <row r="38" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A38" s="224" t="str">
+      <c r="A38" s="225" t="str">
         <f>IF(B2,TEXT(EDATE(B3,29),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*29)+29,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,30)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*30)+29),"dd mmmm yyyy"))</f>
         <v>20 June 2027 - 19 July 2027</v>
       </c>
-      <c r="B38" s="224"/>
+      <c r="B38" s="225"/>
     </row>
     <row r="39" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A39" s="226" t="str">
+      <c r="A39" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,30),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*30)+30,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,31)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*31)+30),"dd mmmm yyyy"))</f>
         <v>20 July 2027 - 19 August 2027</v>
       </c>
-      <c r="B39" s="226" t="s">
+      <c r="B39" s="227" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="40" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A40" s="226" t="str">
+      <c r="A40" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,31),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*31)+31,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,32)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*32)+31),"dd mmmm yyyy"))</f>
         <v>20 August 2027 - 19 September 2027</v>
       </c>
-      <c r="B40" s="226"/>
+      <c r="B40" s="227"/>
     </row>
     <row r="41" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A41" s="224" t="str">
+      <c r="A41" s="225" t="str">
         <f>IF(B2,TEXT(EDATE(B3,32),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*32)+32,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,33)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*33)+32),"dd mmmm yyyy"))</f>
         <v>20 September 2027 - 19 October 2027</v>
       </c>
-      <c r="B41" s="224"/>
+      <c r="B41" s="225"/>
     </row>
     <row r="42" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A42" s="226" t="str">
+      <c r="A42" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,33),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*33)+33,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,34)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*34)+33),"dd mmmm yyyy"))</f>
         <v>20 October 2027 - 19 November 2027</v>
       </c>
-      <c r="B42" s="226" t="s">
+      <c r="B42" s="227" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="43" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A43" s="226" t="str">
+      <c r="A43" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,34),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*34)+34,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,35)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*35)+34),"dd mmmm yyyy"))</f>
         <v>20 November 2027 - 19 December 2027</v>
       </c>
-      <c r="B43" s="226"/>
+      <c r="B43" s="227"/>
     </row>
     <row r="44" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A44" s="224" t="str">
+      <c r="A44" s="225" t="str">
         <f>IF(B2,TEXT(EDATE(B3,35),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*35)+35,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,36)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*36)+35),"dd mmmm yyyy"))</f>
         <v>20 December 2027 - 19 January 2028</v>
       </c>
-      <c r="B44" s="224"/>
+      <c r="B44" s="225"/>
     </row>
     <row r="45" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A45" s="226" t="str">
+      <c r="A45" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,36),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*36)+36,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,37)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*37)+36),"dd mmmm yyyy"))</f>
         <v>20 January 2028 - 19 February 2028</v>
       </c>
-      <c r="B45" s="226" t="s">
+      <c r="B45" s="227" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="46" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A46" s="226" t="str">
+      <c r="A46" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,37),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*37)+37,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,38)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*38)+37),"dd mmmm yyyy"))</f>
         <v>20 February 2028 - 19 March 2028</v>
       </c>
-      <c r="B46" s="226"/>
+      <c r="B46" s="227"/>
     </row>
     <row r="47" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A47" s="224" t="str">
+      <c r="A47" s="225" t="str">
         <f>IF(B2,TEXT(EDATE(B3,38),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*38)+38,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,39)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*39)+38),"dd mmmm yyyy"))</f>
         <v>20 March 2028 - 19 April 2028</v>
       </c>
-      <c r="B47" s="224"/>
+      <c r="B47" s="225"/>
     </row>
     <row r="48" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A48" s="226" t="str">
+      <c r="A48" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,39),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*39)+39,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,40)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*40)+39),"dd mmmm yyyy"))</f>
         <v>20 April 2028 - 19 May 2028</v>
       </c>
-      <c r="B48" s="226" t="s">
+      <c r="B48" s="227" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="49" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A49" s="226" t="str">
+      <c r="A49" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,40),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*40)+40,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,41)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*41)+40),"dd mmmm yyyy"))</f>
         <v>20 May 2028 - 19 June 2028</v>
       </c>
-      <c r="B49" s="226"/>
+      <c r="B49" s="227"/>
     </row>
     <row r="50" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A50" s="224" t="str">
+      <c r="A50" s="225" t="str">
         <f>IF(B2,TEXT(EDATE(B3,41),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*41)+41,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,42)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*42)+41),"dd mmmm yyyy"))</f>
         <v>20 June 2028 - 19 July 2028</v>
       </c>
-      <c r="B50" s="224"/>
+      <c r="B50" s="225"/>
     </row>
     <row r="51" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A51" s="226" t="str">
+      <c r="A51" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,42),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*42)+42,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,43)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*43)+42),"dd mmmm yyyy"))</f>
         <v>20 July 2028 - 19 August 2028</v>
       </c>
-      <c r="B51" s="226" t="s">
+      <c r="B51" s="227" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="52" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A52" s="226" t="str">
+      <c r="A52" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,43),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*43)+43,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,44)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*44)+43),"dd mmmm yyyy"))</f>
         <v>20 August 2028 - 19 September 2028</v>
       </c>
-      <c r="B52" s="226"/>
+      <c r="B52" s="227"/>
     </row>
     <row r="53" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A53" s="224" t="str">
+      <c r="A53" s="225" t="str">
         <f>IF(B2,TEXT(EDATE(B3,44),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*44)+44,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,45)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*45)+44),"dd mmmm yyyy"))</f>
         <v>20 September 2028 - 19 October 2028</v>
       </c>
-      <c r="B53" s="224"/>
+      <c r="B53" s="225"/>
     </row>
     <row r="54" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A54" s="226" t="str">
+      <c r="A54" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,45),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*45)+45,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,46)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*46)+45),"dd mmmm yyyy"))</f>
         <v>20 October 2028 - 19 November 2028</v>
       </c>
-      <c r="B54" s="226" t="s">
+      <c r="B54" s="227" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="55" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A55" s="226" t="str">
+      <c r="A55" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,46),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*46)+46,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,47)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*47)+46),"dd mmmm yyyy"))</f>
         <v>20 November 2028 - 19 December 2028</v>
       </c>
-      <c r="B55" s="226"/>
+      <c r="B55" s="227"/>
     </row>
     <row r="56" ht="20.25" customHeight="1" spans="1:2">
-      <c r="A56" s="226" t="str">
+      <c r="A56" s="227" t="str">
         <f>IF(B2,TEXT(EDATE(B3,47),"dd mmmm yyyy"),TEXT(B3+((B5-B3)*47)+47,"dd mmmm yyyy"))&amp;" - "&amp;IF(B2,TEXT(EDATE(B3,48)-1,"dd mmmm yyyy"),TEXT(B3+(((B5-B3)*48)+47),"dd mmmm yyyy"))</f>
         <v>20 December 2028 - 19 January 2029</v>
       </c>
-      <c r="B56" s="226"/>
+      <c r="B56" s="227"/>
     </row>
     <row r="57" ht="20.25" customHeight="1"/>
     <row r="58" ht="20.25" customHeight="1"/>
@@ -35385,75 +35411,75 @@
     <row r="62" ht="20.25" customHeight="1"/>
     <row r="63" ht="20.25" customHeight="1"/>
     <row r="64" ht="20.25" customHeight="1"/>
-    <row r="65" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="66" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="67" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="68" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="69" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="70" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="71" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="72" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="73" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="74" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="75" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="76" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="77" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="78" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="79" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="80" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="81" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="82" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="83" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="84" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="85" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="86" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="87" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="88" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="89" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="90" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="91" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="92" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="93" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="94" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="95" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="96" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="97" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="98" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="99" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="100" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="101" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="102" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="103" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="104" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="105" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="106" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="107" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="108" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="109" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="110" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="111" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="112" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="113" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="114" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="115" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="116" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="117" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="118" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="119" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="120" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="121" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="122" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="123" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="124" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="125" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="126" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="127" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="129" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="130" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="131" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="132" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="133" s="222" customFormat="1" ht="20.25" customHeight="1"/>
-    <row r="134" s="222" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="65" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="66" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="67" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="68" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="69" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="70" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="71" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="72" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="73" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="74" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="75" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="76" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="77" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="78" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="79" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="80" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="81" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="82" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="83" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="84" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="85" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="86" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="87" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="88" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="89" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="90" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="91" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="92" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="93" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="94" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="95" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="96" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="97" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="98" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="99" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="100" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="101" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="102" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="103" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="104" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="105" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="106" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="107" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="108" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="109" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="110" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="111" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="112" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="113" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="114" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="115" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="116" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="117" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="118" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="119" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="120" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="121" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="122" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="123" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="124" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="125" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="126" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="127" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="129" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="130" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="131" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="132" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="133" s="223" customFormat="1" ht="20.25" customHeight="1"/>
+    <row r="134" s="223" customFormat="1" ht="20.25" customHeight="1"/>
   </sheetData>
   <sheetProtection formatCells="0"/>
   <mergeCells count="19">
@@ -35578,7 +35604,7 @@
       </c>
       <c r="N3" s="196">
         <f>-C122</f>
-        <v>-7729.03</v>
+        <v>-333878.54</v>
       </c>
     </row>
     <row r="4" ht="35.25" customHeight="1" spans="1:14">
@@ -35610,7 +35636,7 @@
       </c>
       <c r="N4" s="196">
         <f ca="1">'April 2025 - June 2025'!C5</f>
-        <v>-5383</v>
+        <v>-332508.54</v>
       </c>
     </row>
     <row r="5" ht="35.25" customHeight="1" spans="1:14">
@@ -35642,7 +35668,7 @@
       </c>
       <c r="N5" s="196">
         <f ca="1">'July 2025 - September 2025'!C5</f>
-        <v>-2983</v>
+        <v>-330108.54</v>
       </c>
     </row>
     <row r="6" ht="35.25" customHeight="1" spans="1:14">
@@ -35674,7 +35700,7 @@
       </c>
       <c r="N6" s="196">
         <f ca="1">'October 2025 - December 2025'!C5</f>
-        <v>-683</v>
+        <v>-327808.54</v>
       </c>
     </row>
     <row r="7" ht="35.25" customHeight="1" spans="1:14">
@@ -35698,7 +35724,7 @@
       </c>
       <c r="J7" s="196">
         <f ca="1">'April 2025 - June 2025'!E163</f>
-        <v>479.2</v>
+        <v>304.23</v>
       </c>
       <c r="M7" s="201" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,12),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*12+12),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,15)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*15+14),"dd mmmm yyyy"))</f>
@@ -35706,7 +35732,7 @@
       </c>
       <c r="N7" s="196">
         <f ca="1">'January 2026 - March 2026'!C5</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1" spans="1:14">
@@ -35731,7 +35757,7 @@
       </c>
       <c r="J8" s="196">
         <f ca="1">'April 2025 - June 2025'!E190</f>
-        <v>434.21</v>
+        <v>259.240000000001</v>
       </c>
       <c r="M8" s="204" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,15),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*15+15),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,18)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*18+17),"dd mmmm yyyy"))</f>
@@ -35739,7 +35765,7 @@
       </c>
       <c r="N8" s="196">
         <f ca="1">'April 2026 - June 2026'!C5</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
     </row>
     <row r="9" ht="39.75" customHeight="1" spans="1:14">
@@ -35763,7 +35789,7 @@
       </c>
       <c r="J9" s="196">
         <f ca="1">'July 2025 - September 2025'!E136</f>
-        <v>480.220000000001</v>
+        <v>305.250000000001</v>
       </c>
       <c r="M9" s="201" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,18),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*18+18),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,21)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*21+20),"dd mmmm yyyy"))</f>
@@ -35771,7 +35797,7 @@
       </c>
       <c r="N9" s="205">
         <f ca="1">'July 2026 - September 2026'!C5</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
     </row>
     <row r="10" ht="35.25" customHeight="1" spans="1:14">
@@ -35795,7 +35821,7 @@
       </c>
       <c r="J10" s="196">
         <f ca="1">'July 2025 - September 2025'!E163</f>
-        <v>385.230000000001</v>
+        <v>210.260000000001</v>
       </c>
       <c r="M10" s="206" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,21),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*21+21),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,24)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*24+23),"dd mmmm yyyy"))</f>
@@ -35803,7 +35829,7 @@
       </c>
       <c r="N10" s="196">
         <f ca="1">'October 2026 - December 2026'!C5</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
     </row>
     <row r="11" ht="35.25" customHeight="1" spans="1:14">
@@ -35828,7 +35854,7 @@
       </c>
       <c r="J11" s="196">
         <f ca="1">'July 2025 - September 2025'!E190</f>
-        <v>431.240000000001</v>
+        <v>256.270000000001</v>
       </c>
       <c r="M11" s="201" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,24),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*24+24),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,27)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*27+26),"dd mmmm yyyy"))</f>
@@ -35836,7 +35862,7 @@
       </c>
       <c r="N11" s="200">
         <f ca="1">'January 2027 - March 2027'!C5</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
     </row>
     <row r="12" ht="35.25" customHeight="1" spans="1:14">
@@ -35860,7 +35886,7 @@
       </c>
       <c r="J12" s="196">
         <f ca="1">'October 2025 - December 2025'!E136</f>
-        <v>386.250000000001</v>
+        <v>211.280000000002</v>
       </c>
       <c r="M12" s="197" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,27),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*27+27),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,30)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*30+29),"dd mmmm yyyy"))</f>
@@ -35868,7 +35894,7 @@
       </c>
       <c r="N12" s="200">
         <f ca="1">'April 2027 - June 2027'!C5</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
     </row>
     <row r="13" ht="35.25" customHeight="1" spans="1:14">
@@ -35892,7 +35918,7 @@
       </c>
       <c r="J13" s="196">
         <f ca="1">'October 2025 - December 2025'!E163</f>
-        <v>382.260000000002</v>
+        <v>207.290000000002</v>
       </c>
       <c r="M13" s="197" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,30),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*30+30),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,33)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*33+32),"dd mmmm yyyy"))</f>
@@ -35900,7 +35926,7 @@
       </c>
       <c r="N13" s="200">
         <f ca="1">'July 2027 - September 2027'!C5</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
     </row>
     <row r="14" ht="35.25" customHeight="1" spans="1:14">
@@ -35924,7 +35950,7 @@
       </c>
       <c r="J14" s="200">
         <f ca="1">'October 2025 - December 2025'!E190</f>
-        <v>307.270000000002</v>
+        <v>132.300000000002</v>
       </c>
       <c r="M14" s="197" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,33),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*33+33),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,36)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*36+35),"dd mmmm yyyy"))</f>
@@ -35932,7 +35958,7 @@
       </c>
       <c r="N14" s="200">
         <f ca="1">'October 2027 - December 2027'!C5</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
     </row>
     <row r="15" ht="35.25" customHeight="1" spans="1:14">
@@ -35956,7 +35982,7 @@
       </c>
       <c r="J15" s="200">
         <f ca="1">'January 2026 - March 2026'!E136</f>
-        <v>470.280000000002</v>
+        <v>295.310000000002</v>
       </c>
       <c r="M15" s="197" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,36),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*36+36),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,39)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*39+38),"dd mmmm yyyy"))</f>
@@ -35964,7 +35990,7 @@
       </c>
       <c r="N15" s="200">
         <f ca="1">'January 2028 - March 2028'!C5</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
     </row>
     <row r="16" ht="35.25" customHeight="1" spans="1:14">
@@ -35990,7 +36016,7 @@
       </c>
       <c r="J16" s="200">
         <f ca="1">'January 2026 - March 2026'!E163</f>
-        <v>885.290000000002</v>
+        <v>710.320000000002</v>
       </c>
       <c r="M16" s="197" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,39),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*39+39),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,42)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*42+41),"dd mmmm yyyy"))</f>
@@ -35998,7 +36024,7 @@
       </c>
       <c r="N16" s="200">
         <f ca="1">'April 2028 - June 2028'!C5</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
     </row>
     <row r="17" ht="35.25" customHeight="1" spans="9:14">
@@ -36008,7 +36034,7 @@
       </c>
       <c r="J17" s="200">
         <f ca="1">'January 2026 - March 2026'!E190</f>
-        <v>1731.3</v>
+        <v>1556.33</v>
       </c>
       <c r="M17" s="197" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,42),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*42+42),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,45)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*45+44),"dd mmmm yyyy"))</f>
@@ -36016,7 +36042,7 @@
       </c>
       <c r="N17" s="200">
         <f ca="1">'July 2028 - September 2028'!C5</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
     </row>
     <row r="18" ht="35.25" customHeight="1" spans="9:14">
@@ -36026,7 +36052,7 @@
       </c>
       <c r="J18" s="200">
         <f ca="1">'April 2026 - June 2026'!E136</f>
-        <v>2306.31</v>
+        <v>2131.34</v>
       </c>
       <c r="M18" s="197" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,45),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*45+45),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,48)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*48+47),"dd mmmm yyyy"))</f>
@@ -36034,7 +36060,7 @@
       </c>
       <c r="N18" s="196">
         <f ca="1">'October 2028 - December 2028'!C5</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
     </row>
     <row r="19" ht="33" customHeight="1" spans="9:10">
@@ -36044,7 +36070,7 @@
       </c>
       <c r="J19" s="200">
         <f ca="1">'April 2026 - June 2026'!E163</f>
-        <v>4075.32</v>
+        <v>3900.35</v>
       </c>
     </row>
     <row r="20" ht="35.25" customHeight="1" spans="9:10">
@@ -36054,7 +36080,7 @@
       </c>
       <c r="J20" s="200">
         <f ca="1">'April 2026 - June 2026'!E190</f>
-        <v>4700.33</v>
+        <v>4525.36</v>
       </c>
     </row>
     <row r="21" ht="35.25" customHeight="1" spans="9:10">
@@ -36064,7 +36090,7 @@
       </c>
       <c r="J21" s="200">
         <f ca="1">'July 2026 - September 2026'!E136</f>
-        <v>5546.34</v>
+        <v>5371.37</v>
       </c>
     </row>
     <row r="22" ht="24.75" customHeight="1" spans="1:10">
@@ -36084,7 +36110,7 @@
       </c>
       <c r="J22" s="200">
         <f ca="1">'July 2026 - September 2026'!E163</f>
-        <v>5961.35</v>
+        <v>5786.38</v>
       </c>
     </row>
     <row r="23" ht="24.75" customHeight="1" spans="1:10">
@@ -36109,7 +36135,7 @@
       </c>
       <c r="J23" s="200">
         <f ca="1">'July 2026 - September 2026'!E190</f>
-        <v>6807.36</v>
+        <v>6632.39</v>
       </c>
     </row>
     <row r="24" ht="33" customHeight="1" spans="1:10">
@@ -36128,7 +36154,7 @@
       </c>
       <c r="J24" s="200">
         <f ca="1">'October 2026 - December 2026'!E136</f>
-        <v>7382.37</v>
+        <v>7207.40000000001</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:10">
@@ -36147,7 +36173,7 @@
       </c>
       <c r="J25" s="200">
         <f ca="1">'October 2026 - December 2026'!E163</f>
-        <v>8068.38</v>
+        <v>7893.41000000001</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:10">
@@ -36166,7 +36192,7 @@
       </c>
       <c r="J26" s="200">
         <f ca="1">'October 2026 - December 2026'!E190</f>
-        <v>8643.39</v>
+        <v>8468.42000000001</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:10">
@@ -36185,7 +36211,7 @@
       </c>
       <c r="J27" s="200">
         <f ca="1">'January 2027 - March 2027'!E136</f>
-        <v>9489.4</v>
+        <v>9314.43000000001</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:10">
@@ -36204,7 +36230,7 @@
       </c>
       <c r="J28" s="200">
         <f ca="1">'January 2027 - March 2027'!E163</f>
-        <v>9904.41</v>
+        <v>9729.44000000001</v>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1" spans="1:10">
@@ -36223,7 +36249,7 @@
       </c>
       <c r="J29" s="196">
         <f ca="1">'January 2027 - March 2027'!E190</f>
-        <v>10750.42</v>
+        <v>10575.45</v>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1" spans="1:10">
@@ -36245,7 +36271,7 @@
       </c>
       <c r="J30" s="202">
         <f ca="1">'April 2027 - June 2027'!E136</f>
-        <v>11966.42</v>
+        <v>11791.45</v>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1" spans="9:10">
@@ -36255,7 +36281,7 @@
       </c>
       <c r="J31" s="200">
         <f ca="1">'April 2027 - June 2027'!E163</f>
-        <v>13834.42</v>
+        <v>13659.45</v>
       </c>
     </row>
     <row r="32" ht="27.75" customHeight="1" spans="9:10">
@@ -36265,7 +36291,7 @@
       </c>
       <c r="J32" s="200">
         <f ca="1">'April 2027 - June 2027'!E190</f>
-        <v>15050.42</v>
+        <v>14875.45</v>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1" spans="9:10">
@@ -36275,7 +36301,7 @@
       </c>
       <c r="J33" s="200">
         <f ca="1">'July 2027 - September 2027'!E136</f>
-        <v>15625.43</v>
+        <v>15450.46</v>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1" spans="1:10">
@@ -36295,7 +36321,7 @@
       </c>
       <c r="J34" s="200">
         <f ca="1">'July 2027 - September 2027'!E163</f>
-        <v>16311.44</v>
+        <v>16136.47</v>
       </c>
     </row>
     <row r="35" ht="24.75" customHeight="1" spans="1:10">
@@ -36320,7 +36346,7 @@
       </c>
       <c r="J35" s="200">
         <f ca="1">'July 2027 - September 2027'!E190</f>
-        <v>16886.45</v>
+        <v>16711.48</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:10">
@@ -36343,7 +36369,7 @@
       </c>
       <c r="J36" s="200">
         <f ca="1">'October 2027 - December 2027'!E136</f>
-        <v>17732.46</v>
+        <v>17557.49</v>
       </c>
     </row>
     <row r="37" ht="24.75" customHeight="1" spans="1:10">
@@ -36362,7 +36388,7 @@
       </c>
       <c r="J37" s="200">
         <f ca="1">'October 2027 - December 2027'!E163</f>
-        <v>18147.47</v>
+        <v>17972.5</v>
       </c>
     </row>
     <row r="38" ht="20.25" customHeight="1" spans="1:10">
@@ -36381,7 +36407,7 @@
       </c>
       <c r="J38" s="200">
         <f ca="1">'October 2027 - December 2027'!E190</f>
-        <v>18993.48</v>
+        <v>18818.51</v>
       </c>
     </row>
     <row r="39" ht="24.75" customHeight="1" spans="1:10">
@@ -36400,7 +36426,7 @@
       </c>
       <c r="J39" s="200">
         <f ca="1">'January 2028 - March 2028'!E136</f>
-        <v>19618.49</v>
+        <v>19443.52</v>
       </c>
     </row>
     <row r="40" ht="24.75" customHeight="1" spans="1:10">
@@ -36419,7 +36445,7 @@
       </c>
       <c r="J40" s="200">
         <f ca="1">'January 2028 - March 2028'!E163</f>
-        <v>20304.5</v>
+        <v>20129.53</v>
       </c>
     </row>
     <row r="41" ht="24.75" customHeight="1" spans="1:10">
@@ -36438,7 +36464,7 @@
       </c>
       <c r="J41" s="200">
         <f ca="1">'January 2028 - March 2028'!E190</f>
-        <v>20919.51</v>
+        <v>20744.54</v>
       </c>
     </row>
     <row r="42" ht="24.75" customHeight="1" spans="1:10">
@@ -36460,7 +36486,7 @@
       </c>
       <c r="J42" s="200">
         <f ca="1">'April 2028 - June 2028'!E136</f>
-        <v>21765.52</v>
+        <v>21590.55</v>
       </c>
     </row>
     <row r="43" ht="24.75" customHeight="1" spans="9:10">
@@ -36470,7 +36496,7 @@
       </c>
       <c r="J43" s="200">
         <f ca="1">'April 2028 - June 2028'!E163</f>
-        <v>23263.53</v>
+        <v>23088.56</v>
       </c>
     </row>
     <row r="44" ht="24.75" customHeight="1" spans="9:10">
@@ -36480,7 +36506,7 @@
       </c>
       <c r="J44" s="200">
         <f ca="1">'April 2028 - June 2028'!E190</f>
-        <v>24109.54</v>
+        <v>23934.57</v>
       </c>
     </row>
     <row r="45" ht="24.75" customHeight="1" spans="9:10">
@@ -36490,7 +36516,7 @@
       </c>
       <c r="J45" s="200">
         <f ca="1">'July 2028 - September 2028'!E136</f>
-        <v>24734.55</v>
+        <v>24559.58</v>
       </c>
     </row>
     <row r="46" ht="24.75" customHeight="1" spans="1:10">
@@ -36510,7 +36536,7 @@
       </c>
       <c r="J46" s="200">
         <f ca="1">'July 2028 - September 2028'!E163</f>
-        <v>25420.56</v>
+        <v>25245.59</v>
       </c>
     </row>
     <row r="47" ht="24.75" customHeight="1" spans="1:10">
@@ -36535,7 +36561,7 @@
       </c>
       <c r="J47" s="200">
         <f ca="1">'July 2028 - September 2028'!E190</f>
-        <v>25995.57</v>
+        <v>25820.6</v>
       </c>
     </row>
     <row r="48" ht="24.75" customHeight="1" spans="1:10">
@@ -36558,7 +36584,7 @@
       </c>
       <c r="J48" s="200">
         <f ca="1">'October 2028 - December 2028'!E136</f>
-        <v>26841.58</v>
+        <v>26666.61</v>
       </c>
     </row>
     <row r="49" ht="24.75" customHeight="1" spans="1:10">
@@ -36577,7 +36603,7 @@
       </c>
       <c r="J49" s="200">
         <f ca="1">'October 2028 - December 2028'!E163</f>
-        <v>27256.59</v>
+        <v>27081.62</v>
       </c>
     </row>
     <row r="50" ht="24.75" customHeight="1" spans="1:10">
@@ -36596,7 +36622,7 @@
       </c>
       <c r="J50" s="196">
         <f ca="1">'October 2028 - December 2028'!E190</f>
-        <v>28102.6</v>
+        <v>27927.63</v>
       </c>
     </row>
     <row r="51" ht="41.1" customHeight="1" spans="1:7">
@@ -36709,7 +36735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
+    <row r="65" ht="34" spans="1:3">
       <c r="A65" s="51" t="s">
         <v>60</v>
       </c>
@@ -36996,7 +37022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" ht="46" customHeight="1" spans="1:3">
+    <row r="102" ht="66" customHeight="1" spans="1:3">
       <c r="A102" s="52" t="s">
         <v>73</v>
       </c>
@@ -37145,8 +37171,8 @@
         <v>85</v>
       </c>
       <c r="B116" s="184"/>
-      <c r="C116" s="218">
-        <v>0</v>
+      <c r="C116" s="220">
+        <v>326149.51</v>
       </c>
       <c r="D116" s="14"/>
       <c r="E116" s="14"/>
@@ -37225,7 +37251,7 @@
       </c>
       <c r="C122" s="207">
         <f>SUM(C112:C121)</f>
-        <v>7729.03</v>
+        <v>333878.54</v>
       </c>
     </row>
     <row r="123" spans="1:3">
@@ -37235,14 +37261,14 @@
       </c>
       <c r="C123" s="37">
         <f>C122+C110</f>
-        <v>8129.03</v>
+        <v>334278.54</v>
       </c>
     </row>
     <row r="124" spans="5:5">
-      <c r="E124" s="220"/>
+      <c r="E124" s="221"/>
     </row>
     <row r="125" spans="5:5">
-      <c r="E125" s="220"/>
+      <c r="E125" s="221"/>
     </row>
     <row r="127" ht="45" customHeight="1"/>
     <row r="128" ht="45" customHeight="1" spans="1:5">
@@ -37515,8 +37541,8 @@
         <v>Balance Brought Forward From February 2025</v>
       </c>
       <c r="B156" s="57"/>
-      <c r="C156" s="221"/>
-      <c r="D156" s="221"/>
+      <c r="C156" s="222"/>
+      <c r="D156" s="222"/>
       <c r="E156" s="89">
         <f>E149</f>
         <v>941.71</v>
@@ -37770,8 +37796,8 @@
         <v>Balance Brought Forward From March 2025</v>
       </c>
       <c r="B183" s="57"/>
-      <c r="C183" s="221"/>
-      <c r="D183" s="221"/>
+      <c r="C183" s="222"/>
+      <c r="D183" s="222"/>
       <c r="E183" s="92">
         <f>E176</f>
         <v>941.71</v>
@@ -38507,7 +38533,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>434.21</v>
+        <v>259.240000000001</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -38521,7 +38547,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>512.430000000001</v>
+        <v>337.460000000001</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -38537,7 +38563,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12">
         <f ca="1">C108</f>
-        <v>-5383</v>
+        <v>-332508.54</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -38801,7 +38827,7 @@
       </c>
       <c r="E23" s="100"/>
       <c r="F23" s="7">
-        <v>1083</v>
+        <v>0</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="14"/>
@@ -38877,7 +38903,7 @@
       <c r="E28" s="45"/>
       <c r="F28" s="46">
         <f>SUM(F22:G27)</f>
-        <v>3636</v>
+        <v>2553</v>
       </c>
       <c r="G28" s="47"/>
       <c r="H28" s="14"/>
@@ -39203,10 +39229,10 @@
       <c r="H50" s="14"/>
       <c r="I50" s="48"/>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" ht="34" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
-        <v>Birdie Sim Card</v>
+        <v>(SHIT COMPANY) Birdie Sim Card</v>
       </c>
       <c r="B51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65")))</f>
@@ -39881,7 +39907,7 @@
       </c>
       <c r="B88" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B88">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B102"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B102")))</f>
-        <v>Sportify Music Paid For 7th of Each Month</v>
+        <v>Sportify Music Paid For 7th of Each Month. Switch to Apple Music on the 8th of July 2025.</v>
       </c>
       <c r="C88" s="87">
         <v>68</v>
@@ -40064,7 +40090,7 @@
       </c>
       <c r="C98" s="106" cm="1">
         <f ca="1" t="array" ref="C98">(((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!E131")+INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!E158")+INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!E185")))+SUM(E118+E145+E172))-INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!C112")</f>
-        <v>-4300</v>
+        <v>-4600</v>
       </c>
       <c r="D98" s="14"/>
       <c r="E98" s="96"/>
@@ -40143,7 +40169,7 @@
       </c>
       <c r="C102" s="106" cm="1">
         <f ca="1" t="array" ref="C102">(((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!E135")+INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!E162")+INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!E189")))+SUM(E122+E149+E176))-INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!C116")</f>
-        <v>0</v>
+        <v>-326149.51</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="148"/>
@@ -40183,7 +40209,7 @@
       </c>
       <c r="C104" s="106" cm="1">
         <f ca="1" t="array" ref="C104">(((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!E137")+INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!E164")+INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!E191")))+SUM(E124+E151+E178))-INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!C118")</f>
-        <v>0</v>
+        <v>-676.03</v>
       </c>
       <c r="D104" s="14"/>
       <c r="E104" s="14"/>
@@ -40259,7 +40285,7 @@
       </c>
       <c r="C108" s="106">
         <f ca="1">SUM(C98:C107)</f>
-        <v>-5383</v>
+        <v>-332508.54</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -40275,7 +40301,7 @@
       </c>
       <c r="C109" s="106">
         <f ca="1">C108-C96</f>
-        <v>-5802.99</v>
+        <v>-332928.53</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -40763,7 +40789,7 @@
       </c>
       <c r="D145" s="66"/>
       <c r="E145" s="37">
-        <v>870</v>
+        <v>570</v>
       </c>
       <c r="F145" s="14"/>
       <c r="G145" s="14"/>
@@ -40843,7 +40869,7 @@
       </c>
       <c r="D151" s="149"/>
       <c r="E151" s="37">
-        <v>676.03</v>
+        <v>0</v>
       </c>
       <c r="F151" s="14"/>
       <c r="G151" s="14"/>
@@ -40935,10 +40961,12 @@
     <row r="158" ht="24.75" customHeight="1" spans="1:9">
       <c r="A158" s="63"/>
       <c r="B158" s="64"/>
-      <c r="C158" s="74"/>
+      <c r="C158" s="74" t="s">
+        <v>112</v>
+      </c>
       <c r="D158" s="74"/>
       <c r="E158" s="87">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="F158" s="14"/>
       <c r="G158" s="14"/>
@@ -41009,7 +41037,7 @@
       <c r="D163" s="82"/>
       <c r="E163" s="92">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>479.2</v>
+        <v>304.23</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -41093,14 +41121,14 @@
     </row>
     <row r="170" ht="24.75" customHeight="1" spans="1:9">
       <c r="A170" s="56" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B170" s="57"/>
       <c r="C170" s="58"/>
       <c r="D170" s="58"/>
       <c r="E170" s="92">
         <f ca="1">E163</f>
-        <v>479.2</v>
+        <v>304.23</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -41126,7 +41154,7 @@
       <c r="A172" s="63"/>
       <c r="B172" s="64"/>
       <c r="C172" s="74" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D172" s="74"/>
       <c r="E172" s="37">
@@ -41286,7 +41314,7 @@
       <c r="A184" s="63"/>
       <c r="B184" s="64"/>
       <c r="C184" s="74" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D184" s="74"/>
       <c r="E184" s="87">
@@ -41374,7 +41402,7 @@
       <c r="D190" s="82"/>
       <c r="E190" s="92">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>434.21</v>
+        <v>259.240000000001</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -41899,7 +41927,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>431.240000000001</v>
+        <v>256.270000000001</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -41913,7 +41941,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>509.460000000001</v>
+        <v>334.490000000001</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -41929,7 +41957,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12">
         <f ca="1">C108</f>
-        <v>-2983</v>
+        <v>-330108.54</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -42575,7 +42603,7 @@
     <row r="51" ht="45" customHeight="1" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
-        <v>Birdie Sim Card</v>
+        <v>(SHIT COMPANY) Birdie Sim Card</v>
       </c>
       <c r="B51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65")))</f>
@@ -43246,7 +43274,7 @@
       </c>
       <c r="B88" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B88">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B102"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B102")))</f>
-        <v>Sportify Music Paid For 7th of Each Month</v>
+        <v>Sportify Music Paid For 7th of Each Month. Switch to Apple Music on the 8th of July 2025.</v>
       </c>
       <c r="C88" s="87">
         <v>68</v>
@@ -43428,7 +43456,7 @@
       </c>
       <c r="C98" s="37" cm="1">
         <f ca="1" t="array" ref="C98">INDIRECT("'"&amp;INDIRECT("Main!B12")&amp;"'!C98")+SUM(E118+E145+E172)</f>
-        <v>-1900</v>
+        <v>-2200</v>
       </c>
       <c r="D98" s="14"/>
       <c r="E98" s="96"/>
@@ -43477,7 +43505,7 @@
       <c r="H100" s="14"/>
       <c r="I100" s="48"/>
     </row>
-    <row r="101" ht="30" customHeight="1" spans="1:9">
+    <row r="101" ht="42" customHeight="1" spans="1:9">
       <c r="A101" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A101">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A115"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A115")))</f>
         <v>Hong Kong Government Hospital Authority</v>
@@ -43497,7 +43525,7 @@
       <c r="H101" s="14"/>
       <c r="I101" s="48"/>
     </row>
-    <row r="102" ht="30" customHeight="1" spans="1:9">
+    <row r="102" ht="42" customHeight="1" spans="1:9">
       <c r="A102" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A102">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A116"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A116")))</f>
         <v>Bankruptcy Department / Bank</v>
@@ -43508,7 +43536,7 @@
       </c>
       <c r="C102" s="37" cm="1">
         <f ca="1" t="array" ref="C102">INDIRECT("'"&amp;INDIRECT("Main!B12")&amp;"'!C102")+SUM(E122+E149+E176)</f>
-        <v>0</v>
+        <v>-326149.51</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
@@ -43548,7 +43576,7 @@
       </c>
       <c r="C104" s="37" cm="1">
         <f ca="1" t="array" ref="C104">INDIRECT("'"&amp;INDIRECT("Main!B12")&amp;"'!C104")+SUM(E124+E151+E178)</f>
-        <v>0</v>
+        <v>-676.03</v>
       </c>
       <c r="D104" s="14"/>
       <c r="E104" s="14"/>
@@ -43624,7 +43652,7 @@
       </c>
       <c r="C108" s="37">
         <f ca="1">SUM(C98:C107)</f>
-        <v>-2983</v>
+        <v>-330108.54</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -43640,7 +43668,7 @@
       </c>
       <c r="C109" s="37">
         <f ca="1">C108-C96</f>
-        <v>-3352.99</v>
+        <v>-330478.53</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -43734,7 +43762,7 @@
       <c r="D116" s="58"/>
       <c r="E116" s="89" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B12")&amp;"'!E190")</f>
-        <v>434.21</v>
+        <v>259.240000000001</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -43760,7 +43788,7 @@
       <c r="A118" s="63"/>
       <c r="B118" s="64"/>
       <c r="C118" s="74" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D118" s="74"/>
       <c r="E118" s="37">
@@ -43905,7 +43933,7 @@
       <c r="A129" s="63"/>
       <c r="B129" s="64"/>
       <c r="C129" s="73" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D129" s="74"/>
       <c r="E129" s="87">
@@ -44008,7 +44036,7 @@
       <c r="D136" s="82"/>
       <c r="E136" s="89">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>480.220000000001</v>
+        <v>305.250000000001</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -44100,7 +44128,7 @@
       <c r="D143" s="58"/>
       <c r="E143" s="89">
         <f ca="1">E136</f>
-        <v>480.220000000001</v>
+        <v>305.250000000001</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -44126,7 +44154,7 @@
       <c r="A145" s="63"/>
       <c r="B145" s="64"/>
       <c r="C145" s="74" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D145" s="74"/>
       <c r="E145" s="37">
@@ -44271,7 +44299,7 @@
       <c r="A156" s="63"/>
       <c r="B156" s="64"/>
       <c r="C156" s="73" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D156" s="74"/>
       <c r="E156" s="87">
@@ -44286,7 +44314,7 @@
       <c r="A157" s="63"/>
       <c r="B157" s="64"/>
       <c r="C157" s="74" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D157" s="74"/>
       <c r="E157" s="87">
@@ -44374,7 +44402,7 @@
       <c r="D163" s="82"/>
       <c r="E163" s="92">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>385.230000000001</v>
+        <v>210.260000000001</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -44466,7 +44494,7 @@
       <c r="D170" s="58"/>
       <c r="E170" s="92">
         <f ca="1">E163</f>
-        <v>385.230000000001</v>
+        <v>210.260000000001</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -44492,7 +44520,7 @@
       <c r="A172" s="63"/>
       <c r="B172" s="64"/>
       <c r="C172" s="74" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D172" s="74"/>
       <c r="E172" s="37">
@@ -44637,7 +44665,7 @@
       <c r="A183" s="63"/>
       <c r="B183" s="64"/>
       <c r="C183" s="73" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D183" s="74"/>
       <c r="E183" s="87">
@@ -44740,7 +44768,7 @@
       <c r="D190" s="82"/>
       <c r="E190" s="92">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>431.240000000001</v>
+        <v>256.270000000001</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -45316,7 +45344,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>307.270000000002</v>
+        <v>132.300000000002</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -45332,7 +45360,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>385.490000000002</v>
+        <v>210.520000000002</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -45348,7 +45376,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12">
         <f ca="1">C108</f>
-        <v>-683</v>
+        <v>-327808.54</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -45994,7 +46022,7 @@
     <row r="51" ht="24.75" customHeight="1" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
-        <v>Birdie Sim Card</v>
+        <v>(SHIT COMPANY) Birdie Sim Card</v>
       </c>
       <c r="B51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65")))</f>
@@ -46665,7 +46693,7 @@
       </c>
       <c r="B88" s="36" t="str" cm="1">
         <f ca="1" t="array" ref="B88">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B102"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B102")))</f>
-        <v>Sportify Music Paid For 7th of Each Month</v>
+        <v>Sportify Music Paid For 7th of Each Month. Switch to Apple Music on the 8th of July 2025.</v>
       </c>
       <c r="C88" s="87">
         <v>68</v>
@@ -46847,7 +46875,7 @@
       </c>
       <c r="C98" s="37" cm="1">
         <f ca="1" t="array" ref="C98">INDIRECT("'"&amp;INDIRECT("Main!B15")&amp;"'!C98")+SUM(E118+E145+E172)</f>
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="D98" s="14"/>
       <c r="E98" s="96"/>
@@ -46927,7 +46955,7 @@
       </c>
       <c r="C102" s="37" cm="1">
         <f ca="1" t="array" ref="C102">INDIRECT("'"&amp;INDIRECT("Main!B15")&amp;"'!C102")+SUM(E122+E149+E176)</f>
-        <v>0</v>
+        <v>-326149.51</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
@@ -46967,7 +46995,7 @@
       </c>
       <c r="C104" s="37" cm="1">
         <f ca="1" t="array" ref="C104">INDIRECT("'"&amp;INDIRECT("Main!B15")&amp;"'!C104")+SUM(E124+E151+E178)</f>
-        <v>0</v>
+        <v>-676.03</v>
       </c>
       <c r="D104" s="14"/>
       <c r="E104" s="14"/>
@@ -47043,7 +47071,7 @@
       </c>
       <c r="C108" s="37">
         <f ca="1">SUM(C98:C107)</f>
-        <v>-683</v>
+        <v>-327808.54</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -47059,7 +47087,7 @@
       </c>
       <c r="C109" s="37">
         <f ca="1">C108-C96</f>
-        <v>-1052.99</v>
+        <v>-328178.53</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -47153,7 +47181,7 @@
       <c r="D116" s="58"/>
       <c r="E116" s="71" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B15")&amp;"'!E190")</f>
-        <v>431.240000000001</v>
+        <v>256.270000000001</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -47179,7 +47207,7 @@
       <c r="A118" s="63"/>
       <c r="B118" s="64"/>
       <c r="C118" s="74" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D118" s="74"/>
       <c r="E118" s="37">
@@ -47339,7 +47367,7 @@
       <c r="A130" s="63"/>
       <c r="B130" s="64"/>
       <c r="C130" s="74" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D130" s="74"/>
       <c r="E130" s="87">
@@ -47427,7 +47455,7 @@
       <c r="D136" s="82"/>
       <c r="E136" s="89">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>386.250000000001</v>
+        <v>211.280000000002</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -47519,7 +47547,7 @@
       <c r="D143" s="58"/>
       <c r="E143" s="89">
         <f ca="1">E136</f>
-        <v>386.250000000001</v>
+        <v>211.280000000002</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -47545,7 +47573,7 @@
       <c r="A145" s="63"/>
       <c r="B145" s="64"/>
       <c r="C145" s="74" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D145" s="74"/>
       <c r="E145" s="37">
@@ -47793,7 +47821,7 @@
       <c r="D163" s="82"/>
       <c r="E163" s="92">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>382.260000000002</v>
+        <v>207.290000000002</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -47885,7 +47913,7 @@
       <c r="D170" s="58"/>
       <c r="E170" s="92">
         <f ca="1">E163</f>
-        <v>382.260000000002</v>
+        <v>207.290000000002</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -47911,7 +47939,7 @@
       <c r="A172" s="63"/>
       <c r="B172" s="64"/>
       <c r="C172" s="74" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D172" s="74"/>
       <c r="E172" s="37">
@@ -47978,7 +48006,7 @@
       <c r="A177" s="63"/>
       <c r="B177" s="64"/>
       <c r="C177" s="65" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D177" s="66"/>
       <c r="E177" s="37">
@@ -48058,7 +48086,7 @@
       <c r="A183" s="63"/>
       <c r="B183" s="64"/>
       <c r="C183" s="73" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D183" s="74"/>
       <c r="E183" s="87">
@@ -48073,7 +48101,7 @@
       <c r="A184" s="63"/>
       <c r="B184" s="64"/>
       <c r="C184" s="74" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D184" s="74"/>
       <c r="E184" s="87">
@@ -48161,7 +48189,7 @@
       <c r="D190" s="82"/>
       <c r="E190" s="92">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>307.270000000002</v>
+        <v>132.300000000002</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -48747,7 +48775,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>1731.3</v>
+        <v>1556.33</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -48763,7 +48791,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>1809.52</v>
+        <v>1634.55</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -48779,7 +48807,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12">
         <f ca="1">C108</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -49425,7 +49453,7 @@
     <row r="51" ht="24.75" customHeight="1" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
-        <v>Birdie Sim Card</v>
+        <v>(SHIT COMPANY) Birdie Sim Card</v>
       </c>
       <c r="B51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65")))</f>
@@ -50096,7 +50124,7 @@
       </c>
       <c r="B88" s="36" t="str" cm="1">
         <f ca="1" t="array" ref="B88">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B102"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B102")))</f>
-        <v>Sportify Music Paid For 7th of Each Month</v>
+        <v>Sportify Music Paid For 7th of Each Month. Switch to Apple Music on the 8th of July 2025.</v>
       </c>
       <c r="C88" s="87">
         <v>68</v>
@@ -50278,7 +50306,7 @@
       </c>
       <c r="C98" s="37" cm="1">
         <f ca="1" t="array" ref="C98">INDIRECT("'"&amp;INDIRECT("Main!B18")&amp;"'!C98")+SUM(E118+E145+E172)</f>
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="D98" s="14"/>
       <c r="E98" s="96"/>
@@ -50327,7 +50355,7 @@
       <c r="H100" s="14"/>
       <c r="I100" s="48"/>
     </row>
-    <row r="101" ht="24.75" customHeight="1" spans="1:9">
+    <row r="101" ht="43" customHeight="1" spans="1:9">
       <c r="A101" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A101">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A115"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A115")))</f>
         <v>Hong Kong Government Hospital Authority</v>
@@ -50347,7 +50375,7 @@
       <c r="H101" s="14"/>
       <c r="I101" s="48"/>
     </row>
-    <row r="102" ht="24.75" customHeight="1" spans="1:9">
+    <row r="102" ht="45" customHeight="1" spans="1:9">
       <c r="A102" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A102">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A116"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A116")))</f>
         <v>Bankruptcy Department / Bank</v>
@@ -50358,7 +50386,7 @@
       </c>
       <c r="C102" s="37" cm="1">
         <f ca="1" t="array" ref="C102">INDIRECT("'"&amp;INDIRECT("Main!B18")&amp;"'!C102")+SUM(E122+E149+E176)</f>
-        <v>0</v>
+        <v>-326149.51</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
@@ -50398,7 +50426,7 @@
       </c>
       <c r="C104" s="37" cm="1">
         <f ca="1" t="array" ref="C104">INDIRECT("'"&amp;INDIRECT("Main!B18")&amp;"'!C104")+SUM(E124+E151+E178)</f>
-        <v>0</v>
+        <v>-676.03</v>
       </c>
       <c r="D104" s="14"/>
       <c r="E104" s="14"/>
@@ -50474,7 +50502,7 @@
       </c>
       <c r="C108" s="37">
         <f ca="1">SUM(C98:C107)</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -50490,7 +50518,7 @@
       </c>
       <c r="C109" s="37">
         <f ca="1">C108-C96</f>
-        <v>-369.99</v>
+        <v>-327495.53</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -50584,7 +50612,7 @@
       <c r="D116" s="58"/>
       <c r="E116" s="71" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B18")&amp;"'!E190")</f>
-        <v>307.270000000002</v>
+        <v>132.300000000002</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -50675,7 +50703,7 @@
       <c r="A123" s="63"/>
       <c r="B123" s="64"/>
       <c r="C123" s="65" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D123" s="66"/>
       <c r="E123" s="37">
@@ -50755,7 +50783,7 @@
       <c r="A129" s="63"/>
       <c r="B129" s="64"/>
       <c r="C129" s="73" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D129" s="74"/>
       <c r="E129" s="87">
@@ -50858,7 +50886,7 @@
       <c r="D136" s="82"/>
       <c r="E136" s="89">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>470.280000000002</v>
+        <v>295.310000000002</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -50950,7 +50978,7 @@
       <c r="D143" s="58"/>
       <c r="E143" s="89">
         <f ca="1">E136</f>
-        <v>470.280000000002</v>
+        <v>295.310000000002</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -51119,7 +51147,7 @@
       <c r="A156" s="63"/>
       <c r="B156" s="64"/>
       <c r="C156" s="73" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D156" s="74"/>
       <c r="E156" s="87">
@@ -51134,7 +51162,7 @@
       <c r="A157" s="63"/>
       <c r="B157" s="64"/>
       <c r="C157" s="74" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D157" s="74"/>
       <c r="E157" s="87">
@@ -51222,7 +51250,7 @@
       <c r="D163" s="82"/>
       <c r="E163" s="92">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>885.290000000002</v>
+        <v>710.320000000002</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -51314,7 +51342,7 @@
       <c r="D170" s="58"/>
       <c r="E170" s="92">
         <f ca="1">E163</f>
-        <v>885.290000000002</v>
+        <v>710.320000000002</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -51483,7 +51511,7 @@
       <c r="A183" s="63"/>
       <c r="B183" s="64"/>
       <c r="C183" s="73" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D183" s="74"/>
       <c r="E183" s="87">
@@ -51586,7 +51614,7 @@
       <c r="D190" s="82"/>
       <c r="E190" s="92">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>1731.3</v>
+        <v>1556.33</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -52130,7 +52158,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>4700.33</v>
+        <v>4525.36</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -52146,7 +52174,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>4778.55</v>
+        <v>4603.58</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -52162,7 +52190,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12">
         <f ca="1">C108</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -52812,7 +52840,7 @@
     <row r="51" ht="24.75" customHeight="1" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
-        <v>Birdie Sim Card</v>
+        <v>(SHIT COMPANY) Birdie Sim Card</v>
       </c>
       <c r="B51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65")))</f>
@@ -53483,7 +53511,7 @@
       </c>
       <c r="B88" s="36" t="str" cm="1">
         <f ca="1" t="array" ref="B88">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B102"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B102")))</f>
-        <v>Sportify Music Paid For 7th of Each Month</v>
+        <v>Sportify Music Paid For 7th of Each Month. Switch to Apple Music on the 8th of July 2025.</v>
       </c>
       <c r="C88" s="87">
         <v>68</v>
@@ -53665,7 +53693,7 @@
       </c>
       <c r="C98" s="106" cm="1">
         <f ca="1" t="array" ref="C98">INDIRECT("'"&amp;INDIRECT("Main!B21")&amp;"'!C98")+SUM(E118+E145+E172)</f>
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="D98" s="14"/>
       <c r="E98" s="96"/>
@@ -53745,7 +53773,7 @@
       </c>
       <c r="C102" s="106" cm="1">
         <f ca="1" t="array" ref="C102">INDIRECT("'"&amp;INDIRECT("Main!B21")&amp;"'!C102")+SUM(E122+E149+E176)</f>
-        <v>0</v>
+        <v>-326149.51</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
@@ -53785,7 +53813,7 @@
       </c>
       <c r="C104" s="106" cm="1">
         <f ca="1" t="array" ref="C104">INDIRECT("'"&amp;INDIRECT("Main!B21")&amp;"'!C104")+SUM(E124+E151+E178)</f>
-        <v>0</v>
+        <v>-676.03</v>
       </c>
       <c r="D104" s="14"/>
       <c r="E104" s="14"/>
@@ -53861,7 +53889,7 @@
       </c>
       <c r="C108" s="106">
         <f ca="1">SUM(C98:C107)</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -53877,7 +53905,7 @@
       </c>
       <c r="C109" s="106">
         <f ca="1">C108-C96</f>
-        <v>-369.99</v>
+        <v>-327495.53</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -53971,7 +53999,7 @@
       <c r="D116" s="58"/>
       <c r="E116" s="71" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B21")&amp;"'!E190")</f>
-        <v>1731.3</v>
+        <v>1556.33</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -54140,7 +54168,7 @@
       <c r="A129" s="63"/>
       <c r="B129" s="64"/>
       <c r="C129" s="73" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D129" s="74"/>
       <c r="E129" s="87">
@@ -54155,7 +54183,7 @@
       <c r="A130" s="63"/>
       <c r="B130" s="64"/>
       <c r="C130" s="74" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D130" s="74"/>
       <c r="E130" s="87">
@@ -54243,7 +54271,7 @@
       <c r="D136" s="82"/>
       <c r="E136" s="89">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>2306.31</v>
+        <v>2131.34</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -54335,7 +54363,7 @@
       <c r="D143" s="58"/>
       <c r="E143" s="89">
         <f ca="1">E136</f>
-        <v>2306.31</v>
+        <v>2131.34</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -54504,7 +54532,7 @@
       <c r="A156" s="63"/>
       <c r="B156" s="64"/>
       <c r="C156" s="73" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D156" s="74"/>
       <c r="E156" s="87">
@@ -54607,7 +54635,7 @@
       <c r="D163" s="82"/>
       <c r="E163" s="92">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>4075.32</v>
+        <v>3900.35</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -54699,7 +54727,7 @@
       <c r="D170" s="58"/>
       <c r="E170" s="92">
         <f ca="1">E163</f>
-        <v>4075.32</v>
+        <v>3900.35</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -54868,7 +54896,7 @@
       <c r="A183" s="63"/>
       <c r="B183" s="64"/>
       <c r="C183" s="73" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D183" s="74"/>
       <c r="E183" s="87">
@@ -54883,7 +54911,7 @@
       <c r="A184" s="63"/>
       <c r="B184" s="64"/>
       <c r="C184" s="74" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D184" s="74"/>
       <c r="E184" s="87">
@@ -54971,7 +54999,7 @@
       <c r="D190" s="82"/>
       <c r="E190" s="92">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>4700.33</v>
+        <v>4525.36</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -55512,7 +55540,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>6807.36</v>
+        <v>6632.39</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -55528,7 +55556,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>6885.58</v>
+        <v>6710.61000000001</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -55544,7 +55572,7 @@
       <c r="B5" s="11"/>
       <c r="C5" s="12">
         <f ca="1">C108</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -55627,7 +55655,7 @@
     </row>
     <row r="11" ht="24.75" customHeight="1" spans="1:9">
       <c r="A11" s="101" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
@@ -56192,7 +56220,7 @@
     <row r="51" ht="24.75" customHeight="1" spans="1:9">
       <c r="A51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="A51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!A65")))</f>
-        <v>Birdie Sim Card</v>
+        <v>(SHIT COMPANY) Birdie Sim Card</v>
       </c>
       <c r="B51" s="38" t="str" cm="1">
         <f ca="1" t="array" ref="B51">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B65")))</f>
@@ -56863,7 +56891,7 @@
       </c>
       <c r="B88" s="36" t="str" cm="1">
         <f ca="1" t="array" ref="B88">IF((INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B102"))=0,"",(INDIRECT("'"&amp;INDIRECT("Main!B9")&amp;"'!B102")))</f>
-        <v>Sportify Music Paid For 7th of Each Month</v>
+        <v>Sportify Music Paid For 7th of Each Month. Switch to Apple Music on the 8th of July 2025.</v>
       </c>
       <c r="C88" s="87">
         <v>68</v>
@@ -57045,7 +57073,7 @@
       </c>
       <c r="C98" s="106" cm="1">
         <f ca="1" t="array" ref="C98">INDIRECT("'"&amp;INDIRECT("Main!B24")&amp;"'!C98")+SUM(E118+E145+E172)</f>
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="D98" s="14"/>
       <c r="E98" s="96"/>
@@ -57125,7 +57153,7 @@
       </c>
       <c r="C102" s="106" cm="1">
         <f ca="1" t="array" ref="C102">INDIRECT("'"&amp;INDIRECT("Main!B24")&amp;"'!C102")+SUM(E122+E149+E176)</f>
-        <v>0</v>
+        <v>-326149.51</v>
       </c>
       <c r="D102" s="14"/>
       <c r="E102" s="14"/>
@@ -57165,7 +57193,7 @@
       </c>
       <c r="C104" s="106" cm="1">
         <f ca="1" t="array" ref="C104">INDIRECT("'"&amp;INDIRECT("Main!B24")&amp;"'!C104")+SUM(E124+E151+E178)</f>
-        <v>0</v>
+        <v>-676.03</v>
       </c>
       <c r="D104" s="14"/>
       <c r="E104" s="14"/>
@@ -57241,7 +57269,7 @@
       </c>
       <c r="C108" s="106">
         <f ca="1">SUM(C98:C107)</f>
-        <v>0</v>
+        <v>-327125.54</v>
       </c>
       <c r="D108" s="14"/>
       <c r="E108" s="14"/>
@@ -57257,7 +57285,7 @@
       </c>
       <c r="C109" s="106">
         <f ca="1">C108-C96</f>
-        <v>-369.99</v>
+        <v>-327495.53</v>
       </c>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
@@ -57351,7 +57379,7 @@
       <c r="D116" s="58"/>
       <c r="E116" s="71" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B24")&amp;"'!E190")</f>
-        <v>4700.33</v>
+        <v>4525.36</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -57520,7 +57548,7 @@
       <c r="A129" s="63"/>
       <c r="B129" s="64"/>
       <c r="C129" s="73" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D129" s="74"/>
       <c r="E129" s="87">
@@ -57623,7 +57651,7 @@
       <c r="D136" s="82"/>
       <c r="E136" s="89">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>5546.34</v>
+        <v>5371.37</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -57715,7 +57743,7 @@
       <c r="D143" s="58"/>
       <c r="E143" s="89">
         <f ca="1">E136</f>
-        <v>5546.34</v>
+        <v>5371.37</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -57884,7 +57912,7 @@
       <c r="A156" s="63"/>
       <c r="B156" s="64"/>
       <c r="C156" s="73" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D156" s="74"/>
       <c r="E156" s="87">
@@ -57899,7 +57927,7 @@
       <c r="A157" s="63"/>
       <c r="B157" s="64"/>
       <c r="C157" s="74" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D157" s="74"/>
       <c r="E157" s="87">
@@ -57987,7 +58015,7 @@
       <c r="D163" s="82"/>
       <c r="E163" s="92">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>5961.35</v>
+        <v>5786.38</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -58079,7 +58107,7 @@
       <c r="D170" s="58"/>
       <c r="E170" s="92">
         <f ca="1">E163</f>
-        <v>5961.35</v>
+        <v>5786.38</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -58248,7 +58276,7 @@
       <c r="A183" s="63"/>
       <c r="B183" s="64"/>
       <c r="C183" s="73" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D183" s="74"/>
       <c r="E183" s="87">
@@ -58351,7 +58379,7 @@
       <c r="D190" s="82"/>
       <c r="E190" s="92">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>6807.36</v>
+        <v>6632.39</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>

--- a/Income And Expenses Forecast Demo.xlsx
+++ b/Income And Expenses Forecast Demo.xlsx
@@ -425,7 +425,9 @@
 ~Oxford Dictionary $19.99 (Don't Need To Include)
 ~Round Trip to the East Kowloon hospital ~ $4
 ~KFC ~ $31
-~Shu Shi (Chuk Yuen Plaza) ~ $98</t>
+~Shu Shi (Chuk Yuen Plaza) ~ $98
+~ Coin Machine Transaction Fees ~ $2.7
+~ Best Mart 360 ~ $18</t>
   </si>
   <si>
     <t xml:space="preserve">~ Payback $570 to Mom </t>
@@ -4790,7 +4792,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>78.22</v>
+        <v>57.52</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -4806,7 +4808,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>8468.42000000001</v>
+        <v>8447.72</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -4822,7 +4824,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>8546.64</v>
+        <v>8505.24000000001</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -6643,7 +6645,7 @@
       <c r="D116" s="58"/>
       <c r="E116" s="71" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B27")&amp;"'!E190")</f>
-        <v>6632.39</v>
+        <v>6611.69</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -6915,7 +6917,7 @@
       <c r="D136" s="82"/>
       <c r="E136" s="89">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>7207.40000000001</v>
+        <v>7186.7</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -7007,7 +7009,7 @@
       <c r="D143" s="58"/>
       <c r="E143" s="89">
         <f ca="1">E136</f>
-        <v>7207.40000000001</v>
+        <v>7186.7</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -7279,7 +7281,7 @@
       <c r="D163" s="82"/>
       <c r="E163" s="92">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>7893.41000000001</v>
+        <v>7872.71</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -7371,7 +7373,7 @@
       <c r="D170" s="58"/>
       <c r="E170" s="92">
         <f ca="1">E163</f>
-        <v>7893.41000000001</v>
+        <v>7872.71</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -7643,7 +7645,7 @@
       <c r="D190" s="82"/>
       <c r="E190" s="92">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>8468.42000000001</v>
+        <v>8447.72</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -8154,7 +8156,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>78.22</v>
+        <v>57.52</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -8170,7 +8172,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>10575.45</v>
+        <v>10554.75</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -8186,7 +8188,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>10653.67</v>
+        <v>10612.27</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -10007,7 +10009,7 @@
       <c r="D116" s="58"/>
       <c r="E116" s="71" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B30")&amp;"'!E190")</f>
-        <v>8468.42000000001</v>
+        <v>8447.72</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -10279,7 +10281,7 @@
       <c r="D136" s="82"/>
       <c r="E136" s="89">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>9314.43000000001</v>
+        <v>9293.73</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -10371,7 +10373,7 @@
       <c r="D143" s="58"/>
       <c r="E143" s="89">
         <f ca="1">E136</f>
-        <v>9314.43000000001</v>
+        <v>9293.73</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -10643,7 +10645,7 @@
       <c r="D163" s="82"/>
       <c r="E163" s="92">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>9729.44000000001</v>
+        <v>9708.74000000001</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -10735,7 +10737,7 @@
       <c r="D170" s="58"/>
       <c r="E170" s="92">
         <f ca="1">E163</f>
-        <v>9729.44000000001</v>
+        <v>9708.74000000001</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -11007,7 +11009,7 @@
       <c r="D190" s="82"/>
       <c r="E190" s="92">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>10575.45</v>
+        <v>10554.75</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -11514,7 +11516,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>78.22</v>
+        <v>57.52</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -11530,7 +11532,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>14875.45</v>
+        <v>14854.75</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -11546,7 +11548,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>14953.67</v>
+        <v>14912.27</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -13371,7 +13373,7 @@
       <c r="D116" s="58"/>
       <c r="E116" s="71" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B33")&amp;"'!E190")</f>
-        <v>10575.45</v>
+        <v>10554.75</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -13643,7 +13645,7 @@
       <c r="D136" s="82"/>
       <c r="E136" s="89">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>11791.45</v>
+        <v>11770.75</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -13735,7 +13737,7 @@
       <c r="D143" s="58"/>
       <c r="E143" s="89">
         <f ca="1">E136</f>
-        <v>11791.45</v>
+        <v>11770.75</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -14007,7 +14009,7 @@
       <c r="D163" s="82"/>
       <c r="E163" s="92">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>13659.45</v>
+        <v>13638.75</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -14099,7 +14101,7 @@
       <c r="D170" s="58"/>
       <c r="E170" s="92">
         <f ca="1">E163</f>
-        <v>13659.45</v>
+        <v>13638.75</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -14371,7 +14373,7 @@
       <c r="D190" s="82"/>
       <c r="E190" s="92">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>14875.45</v>
+        <v>14854.75</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -14876,7 +14878,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>78.22</v>
+        <v>57.52</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -14892,7 +14894,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>16711.48</v>
+        <v>16690.78</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -14908,7 +14910,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>16789.7</v>
+        <v>16748.3</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -16729,7 +16731,7 @@
       <c r="D116" s="58"/>
       <c r="E116" s="71" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B36")&amp;"'!E190")</f>
-        <v>14875.45</v>
+        <v>14854.75</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -17001,7 +17003,7 @@
       <c r="D136" s="82"/>
       <c r="E136" s="89">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>15450.46</v>
+        <v>15429.76</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -17093,7 +17095,7 @@
       <c r="D143" s="58"/>
       <c r="E143" s="89">
         <f ca="1">E136</f>
-        <v>15450.46</v>
+        <v>15429.76</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -17365,7 +17367,7 @@
       <c r="D163" s="82"/>
       <c r="E163" s="92">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>16136.47</v>
+        <v>16115.77</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -17457,7 +17459,7 @@
       <c r="D170" s="58"/>
       <c r="E170" s="92">
         <f ca="1">E163</f>
-        <v>16136.47</v>
+        <v>16115.77</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -17729,7 +17731,7 @@
       <c r="D190" s="82"/>
       <c r="E190" s="92">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>16711.48</v>
+        <v>16690.78</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -18241,7 +18243,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>78.22</v>
+        <v>57.52</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -18257,7 +18259,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>18818.51</v>
+        <v>18797.81</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -18273,7 +18275,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>18896.73</v>
+        <v>18855.33</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -20094,7 +20096,7 @@
       <c r="D116" s="58"/>
       <c r="E116" s="71" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B39")&amp;"'!E190")</f>
-        <v>16711.48</v>
+        <v>16690.78</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -20366,7 +20368,7 @@
       <c r="D136" s="82"/>
       <c r="E136" s="89">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>17557.49</v>
+        <v>17536.79</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -20458,7 +20460,7 @@
       <c r="D143" s="58"/>
       <c r="E143" s="89">
         <f ca="1">E136</f>
-        <v>17557.49</v>
+        <v>17536.79</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -20730,7 +20732,7 @@
       <c r="D163" s="82"/>
       <c r="E163" s="92">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>17972.5</v>
+        <v>17951.8</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -20822,7 +20824,7 @@
       <c r="D170" s="58"/>
       <c r="E170" s="92">
         <f ca="1">E163</f>
-        <v>17972.5</v>
+        <v>17951.8</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -21094,7 +21096,7 @@
       <c r="D190" s="82"/>
       <c r="E190" s="92">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>18818.51</v>
+        <v>18797.81</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -21599,7 +21601,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>78.22</v>
+        <v>57.52</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -21615,7 +21617,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>20744.54</v>
+        <v>20723.84</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -21631,7 +21633,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>20822.76</v>
+        <v>20781.36</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -23452,7 +23454,7 @@
       <c r="D116" s="58"/>
       <c r="E116" s="71" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B42")&amp;"'!E190")</f>
-        <v>18818.51</v>
+        <v>18797.81</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -23724,7 +23726,7 @@
       <c r="D136" s="82"/>
       <c r="E136" s="89">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>19443.52</v>
+        <v>19422.82</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -23816,7 +23818,7 @@
       <c r="D143" s="58"/>
       <c r="E143" s="89">
         <f ca="1">E136</f>
-        <v>19443.52</v>
+        <v>19422.82</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -24088,7 +24090,7 @@
       <c r="D163" s="82"/>
       <c r="E163" s="92">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>20129.53</v>
+        <v>20108.83</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -24180,7 +24182,7 @@
       <c r="D170" s="58"/>
       <c r="E170" s="92">
         <f ca="1">E163</f>
-        <v>20129.53</v>
+        <v>20108.83</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -24452,7 +24454,7 @@
       <c r="D190" s="82"/>
       <c r="E190" s="92">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>20744.54</v>
+        <v>20723.84</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -24963,7 +24965,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>78.22</v>
+        <v>57.52</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -24979,7 +24981,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>23934.57</v>
+        <v>23913.87</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -24995,7 +24997,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>24012.79</v>
+        <v>23971.39</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -26820,7 +26822,7 @@
       <c r="D116" s="58"/>
       <c r="E116" s="71" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B45")&amp;"'!E190")</f>
-        <v>20744.54</v>
+        <v>20723.84</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -27092,7 +27094,7 @@
       <c r="D136" s="82"/>
       <c r="E136" s="89">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>21590.55</v>
+        <v>21569.85</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -27184,7 +27186,7 @@
       <c r="D143" s="58"/>
       <c r="E143" s="89">
         <f ca="1">E136</f>
-        <v>21590.55</v>
+        <v>21569.85</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -27456,7 +27458,7 @@
       <c r="D163" s="82"/>
       <c r="E163" s="92">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>23088.56</v>
+        <v>23067.86</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -27548,7 +27550,7 @@
       <c r="D170" s="58"/>
       <c r="E170" s="92">
         <f ca="1">E163</f>
-        <v>23088.56</v>
+        <v>23067.86</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -27820,7 +27822,7 @@
       <c r="D190" s="82"/>
       <c r="E190" s="92">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>23934.57</v>
+        <v>23913.87</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -28312,7 +28314,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>78.22</v>
+        <v>57.52</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -28328,7 +28330,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>25820.6</v>
+        <v>25799.9</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -28344,7 +28346,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>25898.82</v>
+        <v>25857.42</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -30164,7 +30166,7 @@
       <c r="D116" s="58"/>
       <c r="E116" s="71" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B48")&amp;"'!E190")</f>
-        <v>23934.57</v>
+        <v>23913.87</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -30436,7 +30438,7 @@
       <c r="D136" s="82"/>
       <c r="E136" s="89">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>24559.58</v>
+        <v>24538.88</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -30528,7 +30530,7 @@
       <c r="D143" s="58"/>
       <c r="E143" s="89">
         <f ca="1">E136</f>
-        <v>24559.58</v>
+        <v>24538.88</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -30800,7 +30802,7 @@
       <c r="D163" s="82"/>
       <c r="E163" s="92">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>25245.59</v>
+        <v>25224.89</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -30892,7 +30894,7 @@
       <c r="D170" s="58"/>
       <c r="E170" s="92">
         <f ca="1">E163</f>
-        <v>25245.59</v>
+        <v>25224.89</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -31164,7 +31166,7 @@
       <c r="D190" s="82"/>
       <c r="E190" s="92">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>25820.6</v>
+        <v>25799.9</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -31663,7 +31665,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>78.22</v>
+        <v>57.52</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -31679,7 +31681,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>27927.63</v>
+        <v>27906.93</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -31695,7 +31697,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>28005.85</v>
+        <v>27964.45</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -33516,7 +33518,7 @@
       <c r="D116" s="58"/>
       <c r="E116" s="71" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B51")&amp;"'!E190")</f>
-        <v>25820.6</v>
+        <v>25799.9</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -33788,7 +33790,7 @@
       <c r="D136" s="82"/>
       <c r="E136" s="89">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>26666.61</v>
+        <v>26645.91</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -33880,7 +33882,7 @@
       <c r="D143" s="58"/>
       <c r="E143" s="89">
         <f ca="1">E136</f>
-        <v>26666.61</v>
+        <v>26645.91</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -34152,7 +34154,7 @@
       <c r="D163" s="82"/>
       <c r="E163" s="92">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>27081.62</v>
+        <v>27060.92</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -34244,7 +34246,7 @@
       <c r="D170" s="58"/>
       <c r="E170" s="92">
         <f ca="1">E163</f>
-        <v>27081.62</v>
+        <v>27060.92</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -34516,7 +34518,7 @@
       <c r="D190" s="82"/>
       <c r="E190" s="92">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>27927.63</v>
+        <v>27906.93</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -35579,7 +35581,7 @@
         <v>35</v>
       </c>
       <c r="C3" s="159">
-        <v>18.4</v>
+        <v>0.4</v>
       </c>
       <c r="D3" s="160" t="s">
         <v>34</v>
@@ -35692,7 +35694,7 @@
       </c>
       <c r="J6" s="196">
         <f ca="1">'April 2025 - June 2025'!E136</f>
-        <v>78.22</v>
+        <v>57.52</v>
       </c>
       <c r="M6" s="201" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,9),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*9+9),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,12)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*12+11),"dd mmmm yyyy"))</f>
@@ -35724,7 +35726,7 @@
       </c>
       <c r="J7" s="196">
         <f ca="1">'April 2025 - June 2025'!E163</f>
-        <v>304.23</v>
+        <v>283.53</v>
       </c>
       <c r="M7" s="201" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,12),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*12+12),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,15)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*15+14),"dd mmmm yyyy"))</f>
@@ -35757,7 +35759,7 @@
       </c>
       <c r="J8" s="196">
         <f ca="1">'April 2025 - June 2025'!E190</f>
-        <v>259.240000000001</v>
+        <v>238.54</v>
       </c>
       <c r="M8" s="204" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,15),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*15+15),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,18)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*18+17),"dd mmmm yyyy"))</f>
@@ -35789,7 +35791,7 @@
       </c>
       <c r="J9" s="196">
         <f ca="1">'July 2025 - September 2025'!E136</f>
-        <v>305.250000000001</v>
+        <v>284.550000000001</v>
       </c>
       <c r="M9" s="201" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,18),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*18+18),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,21)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*21+20),"dd mmmm yyyy"))</f>
@@ -35821,7 +35823,7 @@
       </c>
       <c r="J10" s="196">
         <f ca="1">'July 2025 - September 2025'!E163</f>
-        <v>210.260000000001</v>
+        <v>189.560000000001</v>
       </c>
       <c r="M10" s="206" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,21),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*21+21),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,24)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*24+23),"dd mmmm yyyy"))</f>
@@ -35838,14 +35840,14 @@
         <v>43</v>
       </c>
       <c r="C11" s="159">
-        <v>21.4</v>
+        <v>0</v>
       </c>
       <c r="D11" s="161"/>
       <c r="E11" s="5" t="s">
         <v>43</v>
       </c>
       <c r="F11" s="187">
-        <v>19.4</v>
+        <v>21.4</v>
       </c>
       <c r="H11" s="188"/>
       <c r="I11" s="197" t="str">
@@ -35854,7 +35856,7 @@
       </c>
       <c r="J11" s="196">
         <f ca="1">'July 2025 - September 2025'!E190</f>
-        <v>256.270000000001</v>
+        <v>235.570000000001</v>
       </c>
       <c r="M11" s="201" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,24),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*24+24),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,27)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*27+26),"dd mmmm yyyy"))</f>
@@ -35886,7 +35888,7 @@
       </c>
       <c r="J12" s="196">
         <f ca="1">'October 2025 - December 2025'!E136</f>
-        <v>211.280000000002</v>
+        <v>190.580000000001</v>
       </c>
       <c r="M12" s="197" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,27),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*27+27),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,30)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*30+29),"dd mmmm yyyy"))</f>
@@ -35918,7 +35920,7 @@
       </c>
       <c r="J13" s="196">
         <f ca="1">'October 2025 - December 2025'!E163</f>
-        <v>207.290000000002</v>
+        <v>186.590000000002</v>
       </c>
       <c r="M13" s="197" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,30),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*30+30),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,33)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*33+32),"dd mmmm yyyy"))</f>
@@ -35935,7 +35937,7 @@
         <v>46</v>
       </c>
       <c r="C14" s="159">
-        <v>7.4</v>
+        <v>26.1</v>
       </c>
       <c r="D14" s="161"/>
       <c r="E14" s="189" t="s">
@@ -35950,7 +35952,7 @@
       </c>
       <c r="J14" s="200">
         <f ca="1">'October 2025 - December 2025'!E190</f>
-        <v>132.300000000002</v>
+        <v>111.600000000002</v>
       </c>
       <c r="M14" s="197" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,33),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*33+33),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,36)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*36+35),"dd mmmm yyyy"))</f>
@@ -35982,7 +35984,7 @@
       </c>
       <c r="J15" s="200">
         <f ca="1">'January 2026 - March 2026'!E136</f>
-        <v>295.310000000002</v>
+        <v>274.610000000002</v>
       </c>
       <c r="M15" s="197" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,36),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*36+36),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,39)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*39+38),"dd mmmm yyyy"))</f>
@@ -36000,7 +36002,7 @@
       </c>
       <c r="C16" s="165">
         <f>SUM(C3:C15)</f>
-        <v>78.22</v>
+        <v>57.52</v>
       </c>
       <c r="D16" s="166"/>
       <c r="E16" s="164" t="s">
@@ -36008,7 +36010,7 @@
       </c>
       <c r="F16" s="190">
         <f>SUM(F3:F15)</f>
-        <v>76.22</v>
+        <v>78.22</v>
       </c>
       <c r="I16" s="201" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,13),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*13)+13,"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,14)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*14+13),"dd mmmm yyyy"))</f>
@@ -36016,7 +36018,7 @@
       </c>
       <c r="J16" s="200">
         <f ca="1">'January 2026 - March 2026'!E163</f>
-        <v>710.320000000002</v>
+        <v>689.620000000002</v>
       </c>
       <c r="M16" s="197" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,39),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*39+39),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,42)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*42+41),"dd mmmm yyyy"))</f>
@@ -36034,7 +36036,7 @@
       </c>
       <c r="J17" s="200">
         <f ca="1">'January 2026 - March 2026'!E190</f>
-        <v>1556.33</v>
+        <v>1535.63</v>
       </c>
       <c r="M17" s="197" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,42),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*42+42),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,45)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*45+44),"dd mmmm yyyy"))</f>
@@ -36052,7 +36054,7 @@
       </c>
       <c r="J18" s="200">
         <f ca="1">'April 2026 - June 2026'!E136</f>
-        <v>2131.34</v>
+        <v>2110.64</v>
       </c>
       <c r="M18" s="197" t="str">
         <f>IF(Main!B2,TEXT(EDATE(Main!B3,45),"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*45+45),"dd mmmm yyyy"))&amp;" - "&amp;IF(Main!B2,TEXT(EDATE(Main!B3,48)-1,"dd mmmm yyyy"),TEXT(Main!B3+((Main!B5-Main!B3)*48+47),"dd mmmm yyyy"))</f>
@@ -36070,7 +36072,7 @@
       </c>
       <c r="J19" s="200">
         <f ca="1">'April 2026 - June 2026'!E163</f>
-        <v>3900.35</v>
+        <v>3879.65</v>
       </c>
     </row>
     <row r="20" ht="35.25" customHeight="1" spans="9:10">
@@ -36080,7 +36082,7 @@
       </c>
       <c r="J20" s="200">
         <f ca="1">'April 2026 - June 2026'!E190</f>
-        <v>4525.36</v>
+        <v>4504.66</v>
       </c>
     </row>
     <row r="21" ht="35.25" customHeight="1" spans="9:10">
@@ -36090,7 +36092,7 @@
       </c>
       <c r="J21" s="200">
         <f ca="1">'July 2026 - September 2026'!E136</f>
-        <v>5371.37</v>
+        <v>5350.67</v>
       </c>
     </row>
     <row r="22" ht="24.75" customHeight="1" spans="1:10">
@@ -36110,7 +36112,7 @@
       </c>
       <c r="J22" s="200">
         <f ca="1">'July 2026 - September 2026'!E163</f>
-        <v>5786.38</v>
+        <v>5765.68</v>
       </c>
     </row>
     <row r="23" ht="24.75" customHeight="1" spans="1:10">
@@ -36135,7 +36137,7 @@
       </c>
       <c r="J23" s="200">
         <f ca="1">'July 2026 - September 2026'!E190</f>
-        <v>6632.39</v>
+        <v>6611.69</v>
       </c>
     </row>
     <row r="24" ht="33" customHeight="1" spans="1:10">
@@ -36154,7 +36156,7 @@
       </c>
       <c r="J24" s="200">
         <f ca="1">'October 2026 - December 2026'!E136</f>
-        <v>7207.40000000001</v>
+        <v>7186.7</v>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:10">
@@ -36173,7 +36175,7 @@
       </c>
       <c r="J25" s="200">
         <f ca="1">'October 2026 - December 2026'!E163</f>
-        <v>7893.41000000001</v>
+        <v>7872.71</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="1:10">
@@ -36192,7 +36194,7 @@
       </c>
       <c r="J26" s="200">
         <f ca="1">'October 2026 - December 2026'!E190</f>
-        <v>8468.42000000001</v>
+        <v>8447.72</v>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1" spans="1:10">
@@ -36211,7 +36213,7 @@
       </c>
       <c r="J27" s="200">
         <f ca="1">'January 2027 - March 2027'!E136</f>
-        <v>9314.43000000001</v>
+        <v>9293.73</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" spans="1:10">
@@ -36230,7 +36232,7 @@
       </c>
       <c r="J28" s="200">
         <f ca="1">'January 2027 - March 2027'!E163</f>
-        <v>9729.44000000001</v>
+        <v>9708.74000000001</v>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1" spans="1:10">
@@ -36249,7 +36251,7 @@
       </c>
       <c r="J29" s="196">
         <f ca="1">'January 2027 - March 2027'!E190</f>
-        <v>10575.45</v>
+        <v>10554.75</v>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1" spans="1:10">
@@ -36271,7 +36273,7 @@
       </c>
       <c r="J30" s="202">
         <f ca="1">'April 2027 - June 2027'!E136</f>
-        <v>11791.45</v>
+        <v>11770.75</v>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1" spans="9:10">
@@ -36281,7 +36283,7 @@
       </c>
       <c r="J31" s="200">
         <f ca="1">'April 2027 - June 2027'!E163</f>
-        <v>13659.45</v>
+        <v>13638.75</v>
       </c>
     </row>
     <row r="32" ht="27.75" customHeight="1" spans="9:10">
@@ -36291,7 +36293,7 @@
       </c>
       <c r="J32" s="200">
         <f ca="1">'April 2027 - June 2027'!E190</f>
-        <v>14875.45</v>
+        <v>14854.75</v>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1" spans="9:10">
@@ -36301,7 +36303,7 @@
       </c>
       <c r="J33" s="200">
         <f ca="1">'July 2027 - September 2027'!E136</f>
-        <v>15450.46</v>
+        <v>15429.76</v>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1" spans="1:10">
@@ -36321,7 +36323,7 @@
       </c>
       <c r="J34" s="200">
         <f ca="1">'July 2027 - September 2027'!E163</f>
-        <v>16136.47</v>
+        <v>16115.77</v>
       </c>
     </row>
     <row r="35" ht="24.75" customHeight="1" spans="1:10">
@@ -36346,7 +36348,7 @@
       </c>
       <c r="J35" s="200">
         <f ca="1">'July 2027 - September 2027'!E190</f>
-        <v>16711.48</v>
+        <v>16690.78</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:10">
@@ -36369,7 +36371,7 @@
       </c>
       <c r="J36" s="200">
         <f ca="1">'October 2027 - December 2027'!E136</f>
-        <v>17557.49</v>
+        <v>17536.79</v>
       </c>
     </row>
     <row r="37" ht="24.75" customHeight="1" spans="1:10">
@@ -36388,7 +36390,7 @@
       </c>
       <c r="J37" s="200">
         <f ca="1">'October 2027 - December 2027'!E163</f>
-        <v>17972.5</v>
+        <v>17951.8</v>
       </c>
     </row>
     <row r="38" ht="20.25" customHeight="1" spans="1:10">
@@ -36407,7 +36409,7 @@
       </c>
       <c r="J38" s="200">
         <f ca="1">'October 2027 - December 2027'!E190</f>
-        <v>18818.51</v>
+        <v>18797.81</v>
       </c>
     </row>
     <row r="39" ht="24.75" customHeight="1" spans="1:10">
@@ -36426,7 +36428,7 @@
       </c>
       <c r="J39" s="200">
         <f ca="1">'January 2028 - March 2028'!E136</f>
-        <v>19443.52</v>
+        <v>19422.82</v>
       </c>
     </row>
     <row r="40" ht="24.75" customHeight="1" spans="1:10">
@@ -36445,7 +36447,7 @@
       </c>
       <c r="J40" s="200">
         <f ca="1">'January 2028 - March 2028'!E163</f>
-        <v>20129.53</v>
+        <v>20108.83</v>
       </c>
     </row>
     <row r="41" ht="24.75" customHeight="1" spans="1:10">
@@ -36464,7 +36466,7 @@
       </c>
       <c r="J41" s="200">
         <f ca="1">'January 2028 - March 2028'!E190</f>
-        <v>20744.54</v>
+        <v>20723.84</v>
       </c>
     </row>
     <row r="42" ht="24.75" customHeight="1" spans="1:10">
@@ -36486,7 +36488,7 @@
       </c>
       <c r="J42" s="200">
         <f ca="1">'April 2028 - June 2028'!E136</f>
-        <v>21590.55</v>
+        <v>21569.85</v>
       </c>
     </row>
     <row r="43" ht="24.75" customHeight="1" spans="9:10">
@@ -36496,7 +36498,7 @@
       </c>
       <c r="J43" s="200">
         <f ca="1">'April 2028 - June 2028'!E163</f>
-        <v>23088.56</v>
+        <v>23067.86</v>
       </c>
     </row>
     <row r="44" ht="24.75" customHeight="1" spans="9:10">
@@ -36506,7 +36508,7 @@
       </c>
       <c r="J44" s="200">
         <f ca="1">'April 2028 - June 2028'!E190</f>
-        <v>23934.57</v>
+        <v>23913.87</v>
       </c>
     </row>
     <row r="45" ht="24.75" customHeight="1" spans="9:10">
@@ -36516,7 +36518,7 @@
       </c>
       <c r="J45" s="200">
         <f ca="1">'July 2028 - September 2028'!E136</f>
-        <v>24559.58</v>
+        <v>24538.88</v>
       </c>
     </row>
     <row r="46" ht="24.75" customHeight="1" spans="1:10">
@@ -36536,7 +36538,7 @@
       </c>
       <c r="J46" s="200">
         <f ca="1">'July 2028 - September 2028'!E163</f>
-        <v>25245.59</v>
+        <v>25224.89</v>
       </c>
     </row>
     <row r="47" ht="24.75" customHeight="1" spans="1:10">
@@ -36561,7 +36563,7 @@
       </c>
       <c r="J47" s="200">
         <f ca="1">'July 2028 - September 2028'!E190</f>
-        <v>25820.6</v>
+        <v>25799.9</v>
       </c>
     </row>
     <row r="48" ht="24.75" customHeight="1" spans="1:10">
@@ -36584,7 +36586,7 @@
       </c>
       <c r="J48" s="200">
         <f ca="1">'October 2028 - December 2028'!E136</f>
-        <v>26666.61</v>
+        <v>26645.91</v>
       </c>
     </row>
     <row r="49" ht="24.75" customHeight="1" spans="1:10">
@@ -36603,7 +36605,7 @@
       </c>
       <c r="J49" s="200">
         <f ca="1">'October 2028 - December 2028'!E163</f>
-        <v>27081.62</v>
+        <v>27060.92</v>
       </c>
     </row>
     <row r="50" ht="24.75" customHeight="1" spans="1:10">
@@ -36622,7 +36624,7 @@
       </c>
       <c r="J50" s="196">
         <f ca="1">'October 2028 - December 2028'!E190</f>
-        <v>27927.63</v>
+        <v>27906.93</v>
       </c>
     </row>
     <row r="51" ht="41.1" customHeight="1" spans="1:7">
@@ -38519,7 +38521,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>78.22</v>
+        <v>57.52</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -38533,7 +38535,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>259.240000000001</v>
+        <v>238.54</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -38547,7 +38549,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>337.460000000001</v>
+        <v>296.06</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -40560,7 +40562,7 @@
       <c r="H128" s="14"/>
       <c r="I128" s="48"/>
     </row>
-    <row r="129" ht="40.5" customHeight="1" spans="1:9">
+    <row r="129" ht="59" customHeight="1" spans="1:9">
       <c r="A129" s="63"/>
       <c r="B129" s="64"/>
       <c r="C129" s="73" t="s">
@@ -40575,7 +40577,7 @@
       <c r="H129" s="14"/>
       <c r="I129" s="48"/>
     </row>
-    <row r="130" ht="153" customHeight="1" spans="1:9">
+    <row r="130" ht="186" customHeight="1" spans="1:9">
       <c r="A130" s="63"/>
       <c r="B130" s="64"/>
       <c r="C130" s="73" t="s">
@@ -40583,7 +40585,7 @@
       </c>
       <c r="D130" s="74"/>
       <c r="E130" s="87">
-        <v>603.5</v>
+        <v>624.2</v>
       </c>
       <c r="F130" s="14"/>
       <c r="G130" s="14"/>
@@ -40667,7 +40669,7 @@
       <c r="D136" s="82"/>
       <c r="E136" s="89">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>78.22</v>
+        <v>57.52</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -40759,7 +40761,7 @@
       <c r="D143" s="58"/>
       <c r="E143" s="89">
         <f ca="1">E136</f>
-        <v>78.22</v>
+        <v>57.52</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -41037,7 +41039,7 @@
       <c r="D163" s="82"/>
       <c r="E163" s="92">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>304.23</v>
+        <v>283.53</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -41128,7 +41130,7 @@
       <c r="D170" s="58"/>
       <c r="E170" s="92">
         <f ca="1">E163</f>
-        <v>304.23</v>
+        <v>283.53</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -41402,7 +41404,7 @@
       <c r="D190" s="82"/>
       <c r="E190" s="92">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>259.240000000001</v>
+        <v>238.54</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -41913,7 +41915,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>78.22</v>
+        <v>57.52</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -41927,7 +41929,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>256.270000000001</v>
+        <v>235.570000000001</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -41941,7 +41943,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>334.490000000001</v>
+        <v>293.090000000001</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -43762,7 +43764,7 @@
       <c r="D116" s="58"/>
       <c r="E116" s="89" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B12")&amp;"'!E190")</f>
-        <v>259.240000000001</v>
+        <v>238.54</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -44036,7 +44038,7 @@
       <c r="D136" s="82"/>
       <c r="E136" s="89">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>305.250000000001</v>
+        <v>284.550000000001</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -44128,7 +44130,7 @@
       <c r="D143" s="58"/>
       <c r="E143" s="89">
         <f ca="1">E136</f>
-        <v>305.250000000001</v>
+        <v>284.550000000001</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -44402,7 +44404,7 @@
       <c r="D163" s="82"/>
       <c r="E163" s="92">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>210.260000000001</v>
+        <v>189.560000000001</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -44494,7 +44496,7 @@
       <c r="D170" s="58"/>
       <c r="E170" s="92">
         <f ca="1">E163</f>
-        <v>210.260000000001</v>
+        <v>189.560000000001</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -44768,7 +44770,7 @@
       <c r="D190" s="82"/>
       <c r="E190" s="92">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>256.270000000001</v>
+        <v>235.570000000001</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -45328,7 +45330,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>78.22</v>
+        <v>57.52</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -45344,7 +45346,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>132.300000000002</v>
+        <v>111.600000000002</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -45360,7 +45362,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>210.520000000002</v>
+        <v>169.120000000002</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -47181,7 +47183,7 @@
       <c r="D116" s="58"/>
       <c r="E116" s="71" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B15")&amp;"'!E190")</f>
-        <v>256.270000000001</v>
+        <v>235.570000000001</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -47455,7 +47457,7 @@
       <c r="D136" s="82"/>
       <c r="E136" s="89">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>211.280000000002</v>
+        <v>190.580000000001</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -47547,7 +47549,7 @@
       <c r="D143" s="58"/>
       <c r="E143" s="89">
         <f ca="1">E136</f>
-        <v>211.280000000002</v>
+        <v>190.580000000001</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -47821,7 +47823,7 @@
       <c r="D163" s="82"/>
       <c r="E163" s="92">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>207.290000000002</v>
+        <v>186.590000000002</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -47913,7 +47915,7 @@
       <c r="D170" s="58"/>
       <c r="E170" s="92">
         <f ca="1">E163</f>
-        <v>207.290000000002</v>
+        <v>186.590000000002</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -48189,7 +48191,7 @@
       <c r="D190" s="82"/>
       <c r="E190" s="92">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>132.300000000002</v>
+        <v>111.600000000002</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -48759,7 +48761,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>78.22</v>
+        <v>57.52</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -48775,7 +48777,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>1556.33</v>
+        <v>1535.63</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -48791,7 +48793,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>1634.55</v>
+        <v>1593.15</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -50612,7 +50614,7 @@
       <c r="D116" s="58"/>
       <c r="E116" s="71" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B18")&amp;"'!E190")</f>
-        <v>132.300000000002</v>
+        <v>111.600000000002</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -50886,7 +50888,7 @@
       <c r="D136" s="82"/>
       <c r="E136" s="89">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>295.310000000002</v>
+        <v>274.610000000002</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -50978,7 +50980,7 @@
       <c r="D143" s="58"/>
       <c r="E143" s="89">
         <f ca="1">E136</f>
-        <v>295.310000000002</v>
+        <v>274.610000000002</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -51250,7 +51252,7 @@
       <c r="D163" s="82"/>
       <c r="E163" s="92">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>710.320000000002</v>
+        <v>689.620000000002</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -51342,7 +51344,7 @@
       <c r="D170" s="58"/>
       <c r="E170" s="92">
         <f ca="1">E163</f>
-        <v>710.320000000002</v>
+        <v>689.620000000002</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -51614,7 +51616,7 @@
       <c r="D190" s="82"/>
       <c r="E190" s="92">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>1556.33</v>
+        <v>1535.63</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -52142,7 +52144,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>78.22</v>
+        <v>57.52</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -52158,7 +52160,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>4525.36</v>
+        <v>4504.66</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -52174,7 +52176,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>4603.58</v>
+        <v>4562.18</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -53999,7 +54001,7 @@
       <c r="D116" s="58"/>
       <c r="E116" s="71" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B21")&amp;"'!E190")</f>
-        <v>1556.33</v>
+        <v>1535.63</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -54271,7 +54273,7 @@
       <c r="D136" s="82"/>
       <c r="E136" s="89">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>2131.34</v>
+        <v>2110.64</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -54363,7 +54365,7 @@
       <c r="D143" s="58"/>
       <c r="E143" s="89">
         <f ca="1">E136</f>
-        <v>2131.34</v>
+        <v>2110.64</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -54635,7 +54637,7 @@
       <c r="D163" s="82"/>
       <c r="E163" s="92">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>3900.35</v>
+        <v>3879.65</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -54727,7 +54729,7 @@
       <c r="D170" s="58"/>
       <c r="E170" s="92">
         <f ca="1">E163</f>
-        <v>3900.35</v>
+        <v>3879.65</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -54999,7 +55001,7 @@
       <c r="D190" s="82"/>
       <c r="E190" s="92">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>4525.36</v>
+        <v>4504.66</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
@@ -55524,7 +55526,7 @@
       </c>
       <c r="C2" s="4" cm="1">
         <f ca="1" t="array" ref="C2">INDIRECT("'"&amp;Main!B9&amp;"'!$C$16")</f>
-        <v>78.22</v>
+        <v>57.52</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
@@ -55540,7 +55542,7 @@
       </c>
       <c r="C3" s="7">
         <f ca="1">E190</f>
-        <v>6632.39</v>
+        <v>6611.69</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
@@ -55556,7 +55558,7 @@
       <c r="B4" s="9"/>
       <c r="C4" s="10">
         <f ca="1">SUM(C2:G3)</f>
-        <v>6710.61000000001</v>
+        <v>6669.21</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
@@ -57379,7 +57381,7 @@
       <c r="D116" s="58"/>
       <c r="E116" s="71" cm="1">
         <f ca="1" t="array" ref="E116">INDIRECT("'"&amp;INDIRECT("Main!B24")&amp;"'!E190")</f>
-        <v>4525.36</v>
+        <v>4504.66</v>
       </c>
       <c r="F116" s="14"/>
       <c r="G116" s="14"/>
@@ -57651,7 +57653,7 @@
       <c r="D136" s="82"/>
       <c r="E136" s="89">
         <f ca="1">(F16+E116)-(SUM(E118:E127)+SUM(E129:E135))</f>
-        <v>5371.37</v>
+        <v>5350.67</v>
       </c>
       <c r="F136" s="14"/>
       <c r="G136" s="14"/>
@@ -57743,7 +57745,7 @@
       <c r="D143" s="58"/>
       <c r="E143" s="89">
         <f ca="1">E136</f>
-        <v>5371.37</v>
+        <v>5350.67</v>
       </c>
       <c r="F143" s="14"/>
       <c r="G143" s="14"/>
@@ -58015,7 +58017,7 @@
       <c r="D163" s="82"/>
       <c r="E163" s="92">
         <f ca="1">(F28+E143)-(SUM(E145:E154)+SUM(E156:E162))</f>
-        <v>5786.38</v>
+        <v>5765.68</v>
       </c>
       <c r="F163" s="14"/>
       <c r="G163" s="14"/>
@@ -58107,7 +58109,7 @@
       <c r="D170" s="58"/>
       <c r="E170" s="92">
         <f ca="1">E163</f>
-        <v>5786.38</v>
+        <v>5765.68</v>
       </c>
       <c r="F170" s="14"/>
       <c r="G170" s="14"/>
@@ -58379,7 +58381,7 @@
       <c r="D190" s="82"/>
       <c r="E190" s="92">
         <f ca="1">(F40+E170)-(SUM(E172:E181)+SUM(E183:E189))</f>
-        <v>6632.39</v>
+        <v>6611.69</v>
       </c>
       <c r="F190" s="14"/>
       <c r="G190" s="14"/>
